--- a/data/DPresults.xlsx
+++ b/data/DPresults.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\segmentation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A432EFD2-26F3-43C0-8F0B-7F505982F230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AABDDB-A7E9-4A93-A1C3-55BEE17A3C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30750" yWindow="975" windowWidth="23250" windowHeight="15225" xr2:uid="{7E3558C8-CB49-46FB-8C25-B70FF8305F7B}"/>
+    <workbookView xWindow="1950" yWindow="255" windowWidth="23250" windowHeight="15225" xr2:uid="{7E3558C8-CB49-46FB-8C25-B70FF8305F7B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="100">
   <si>
     <t>benchmark</t>
   </si>
@@ -334,6 +334,9 @@
   </si>
   <si>
     <t>WBS</t>
+  </si>
+  <si>
+    <t>gap</t>
   </si>
 </sst>
 </file>
@@ -707,13 +710,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F6F3FC8-390D-4018-9A07-1C7FE899F7FD}">
-  <dimension ref="A1:S142"/>
+  <dimension ref="A1:T142"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="9.140625" style="2"/>
+    <col min="6" max="6" width="9.140625" style="1"/>
+    <col min="10" max="10" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="F1" s="1" t="s">
         <v>96</v>
       </c>
@@ -724,9 +729,9 @@
       <c r="N1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="R1" s="1"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -778,9 +783,12 @@
       <c r="Q2" t="s">
         <v>8</v>
       </c>
-      <c r="R2" s="1"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R2" t="s">
+        <v>99</v>
+      </c>
+      <c r="S2" s="1"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -803,10 +811,10 @@
         <v>10</v>
       </c>
       <c r="H3">
-        <v>1501.1341520000001</v>
+        <v>1501.1341522299799</v>
       </c>
       <c r="I3">
-        <v>2.0810374999999999E-2</v>
+        <v>2.0723417001136099E-2</v>
       </c>
       <c r="J3" s="1">
         <v>4485</v>
@@ -815,10 +823,10 @@
         <v>2</v>
       </c>
       <c r="L3">
-        <v>1649.3175290302599</v>
+        <v>1649.31752903027</v>
       </c>
       <c r="M3">
-        <v>1.0024832999988499E-2</v>
+        <v>1.00887919998058E-2</v>
       </c>
       <c r="N3" s="1">
         <v>400</v>
@@ -832,13 +840,17 @@
       <c r="Q3">
         <v>0.27298408299975502</v>
       </c>
-      <c r="R3" s="1"/>
-      <c r="S3">
-        <f t="shared" ref="S3:S66" si="0">IF(G3=K3,1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R3">
+        <f>IF(O3=G3,(P3-H3)/H3,NA())</f>
+        <v>1.7934845798728755E-2</v>
+      </c>
+      <c r="S3" s="1"/>
+      <c r="T3">
+        <f t="shared" ref="T3:T66" si="0">IF(G3=K3,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -861,10 +873,10 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>2579.2644009999999</v>
+        <v>705.13368488428796</v>
       </c>
       <c r="I4">
-        <v>4.7000209000000001E-2</v>
+        <v>4.7328750000815399E-2</v>
       </c>
       <c r="J4" s="1">
         <v>246</v>
@@ -876,7 +888,7 @@
         <v>176.03829513752601</v>
       </c>
       <c r="M4">
-        <v>7.4108299986609997E-4</v>
+        <v>7.4049999966509998E-4</v>
       </c>
       <c r="N4" s="1">
         <v>400</v>
@@ -890,13 +902,17 @@
       <c r="Q4">
         <v>0.16677724999999499</v>
       </c>
-      <c r="R4" s="1"/>
-      <c r="S4">
+      <c r="R4" t="e">
+        <f t="shared" ref="R4:R67" si="1">IF(O4=G4,(P4-H4)/H4,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="S4" s="1"/>
+      <c r="T4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -919,10 +935,10 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>487.94223849999997</v>
+        <v>487.94223846170701</v>
       </c>
       <c r="I5">
-        <v>2.3041458000000001E-2</v>
+        <v>2.2845334000521599E-2</v>
       </c>
       <c r="J5" s="1">
         <v>2646</v>
@@ -931,10 +947,10 @@
         <v>6</v>
       </c>
       <c r="L5">
-        <v>543.243176741257</v>
+        <v>543.24317690561304</v>
       </c>
       <c r="M5">
-        <v>6.0240830002839998E-3</v>
+        <v>6.1009999990346E-3</v>
       </c>
       <c r="N5" s="1">
         <v>400</v>
@@ -948,13 +964,17 @@
       <c r="Q5">
         <v>0.235789332999956</v>
       </c>
-      <c r="R5" s="1"/>
-      <c r="S5">
+      <c r="R5" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S5" s="1"/>
+      <c r="T5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -977,10 +997,10 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>49.368061879999999</v>
+        <v>13.141456302652699</v>
       </c>
       <c r="I6">
-        <v>2.281625E-2</v>
+        <v>2.3687082999458601E-2</v>
       </c>
       <c r="J6" s="1">
         <v>262</v>
@@ -989,10 +1009,10 @@
         <v>5</v>
       </c>
       <c r="L6">
-        <v>11.059216410178699</v>
+        <v>11.0592164106518</v>
       </c>
       <c r="M6">
-        <v>7.8862500004100002E-4</v>
+        <v>8.0366700058219997E-4</v>
       </c>
       <c r="N6" s="1">
         <v>400</v>
@@ -1006,13 +1026,17 @@
       <c r="Q6">
         <v>6.3984458000049899E-2</v>
       </c>
-      <c r="R6" s="1"/>
-      <c r="S6">
+      <c r="R6" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S6" s="1"/>
+      <c r="T6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1035,10 +1059,10 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>1395.3675479999999</v>
+        <v>1395.3675476954299</v>
       </c>
       <c r="I7">
-        <v>2.1902917000000001E-2</v>
+        <v>2.21874170001683E-2</v>
       </c>
       <c r="J7" s="1">
         <v>4217</v>
@@ -1047,10 +1071,10 @@
         <v>2</v>
       </c>
       <c r="L7">
-        <v>1511.32616394251</v>
+        <v>1511.32616394252</v>
       </c>
       <c r="M7">
-        <v>9.6936249997270005E-3</v>
+        <v>9.5327500002895006E-3</v>
       </c>
       <c r="N7" s="1">
         <v>400</v>
@@ -1064,13 +1088,17 @@
       <c r="Q7">
         <v>0.26677937500016902</v>
       </c>
-      <c r="R7" s="1"/>
-      <c r="S7">
+      <c r="R7" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S7" s="1"/>
+      <c r="T7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1093,10 +1121,10 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>1448.042369</v>
+        <v>390.52896885359701</v>
       </c>
       <c r="I8">
-        <v>2.4154666000000002E-2</v>
+        <v>2.4792166999759498E-2</v>
       </c>
       <c r="J8" s="1">
         <v>248</v>
@@ -1105,10 +1133,10 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>55.742676689360799</v>
+        <v>55.742676689361097</v>
       </c>
       <c r="M8">
-        <v>7.4437500006749996E-4</v>
+        <v>7.6970800000699996E-4</v>
       </c>
       <c r="N8" s="1">
         <v>400</v>
@@ -1122,13 +1150,17 @@
       <c r="Q8">
         <v>6.2383167000007199E-2</v>
       </c>
-      <c r="R8" s="1"/>
-      <c r="S8">
+      <c r="R8" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S8" s="1"/>
+      <c r="T8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1151,10 +1183,10 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>918.02557260000003</v>
+        <v>918.02557255422096</v>
       </c>
       <c r="I9">
-        <v>9.0499999999999999E-4</v>
+        <v>9.0537500000199996E-4</v>
       </c>
       <c r="J9" s="1">
         <v>1181</v>
@@ -1163,10 +1195,10 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>992.13092420199996</v>
+        <v>992.13092420200098</v>
       </c>
       <c r="M9">
-        <v>2.6481660001990998E-3</v>
+        <v>2.6804999997693001E-3</v>
       </c>
       <c r="N9" s="1">
         <v>400</v>
@@ -1180,13 +1212,17 @@
       <c r="Q9">
         <v>7.3558666000280895E-2</v>
       </c>
-      <c r="R9" s="1"/>
-      <c r="S9">
+      <c r="R9" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S9" s="1"/>
+      <c r="T9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1209,10 +1245,10 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>4151.0169370000003</v>
+        <v>1389.36164363227</v>
       </c>
       <c r="I10">
-        <v>1.0311249999999999E-3</v>
+        <v>1.0682080010154999E-3</v>
       </c>
       <c r="J10" s="1">
         <v>120</v>
@@ -1224,7 +1260,7 @@
         <v>124.876911202325</v>
       </c>
       <c r="M10">
-        <v>3.764579996641E-4</v>
+        <v>3.7237499964240002E-4</v>
       </c>
       <c r="N10" s="1">
         <v>400</v>
@@ -1238,13 +1274,17 @@
       <c r="Q10">
         <v>3.2044333000158E-2</v>
       </c>
-      <c r="R10" s="1"/>
-      <c r="S10">
+      <c r="R10" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S10" s="1"/>
+      <c r="T10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1267,10 +1307,10 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>602.80629060000001</v>
+        <v>602.80629062495404</v>
       </c>
       <c r="I11">
-        <v>2.3943791999999998E-2</v>
+        <v>2.3292874999242399E-2</v>
       </c>
       <c r="J11" s="1">
         <v>3426</v>
@@ -1279,10 +1319,10 @@
         <v>4</v>
       </c>
       <c r="L11">
-        <v>690.94973737250803</v>
+        <v>690.94973740272997</v>
       </c>
       <c r="M11">
-        <v>7.7816670000174001E-3</v>
+        <v>7.8362910007854E-3</v>
       </c>
       <c r="N11" s="1">
         <v>400</v>
@@ -1296,13 +1336,17 @@
       <c r="Q11">
         <v>0.264848124999844</v>
       </c>
-      <c r="R11" s="1"/>
-      <c r="S11">
+      <c r="R11">
+        <f t="shared" si="1"/>
+        <v>8.0072424963197261E-3</v>
+      </c>
+      <c r="S11" s="1"/>
+      <c r="T11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1325,10 +1369,10 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>76.922474109999996</v>
+        <v>20.548922353263499</v>
       </c>
       <c r="I12">
-        <v>2.5975292000000001E-2</v>
+        <v>2.6259874999595902E-2</v>
       </c>
       <c r="J12" s="1">
         <v>254</v>
@@ -1337,10 +1381,10 @@
         <v>1</v>
       </c>
       <c r="L12">
-        <v>7.7667477324267002</v>
+        <v>7.7667477322999297</v>
       </c>
       <c r="M12">
-        <v>7.690829997955E-4</v>
+        <v>7.5350000042809998E-4</v>
       </c>
       <c r="N12" s="1">
         <v>400</v>
@@ -1354,13 +1398,17 @@
       <c r="Q12">
         <v>6.3844041000265805E-2</v>
       </c>
-      <c r="R12" s="1"/>
-      <c r="S12">
+      <c r="R12" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S12" s="1"/>
+      <c r="T12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1383,10 +1431,10 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>711.06543520000002</v>
+        <v>711.06543522588197</v>
       </c>
       <c r="I13">
-        <v>1.0905839999999999E-3</v>
+        <v>1.1426670007494001E-3</v>
       </c>
       <c r="J13" s="1">
         <v>2015</v>
@@ -1395,10 +1443,10 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>878.61342647986703</v>
+        <v>878.61342647987306</v>
       </c>
       <c r="M13">
-        <v>4.4737920002262E-3</v>
+        <v>4.503084001044E-3</v>
       </c>
       <c r="N13" s="1">
         <v>400</v>
@@ -1412,13 +1460,17 @@
       <c r="Q13">
         <v>0.115329416999884</v>
       </c>
-      <c r="R13" s="1"/>
-      <c r="S13">
+      <c r="R13" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S13" s="1"/>
+      <c r="T13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1441,10 +1493,10 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>669.41007279999997</v>
+        <v>225.45411696258199</v>
       </c>
       <c r="I14">
-        <v>1.193625E-3</v>
+        <v>1.2145410000812E-3</v>
       </c>
       <c r="J14" s="1">
         <v>136</v>
@@ -1453,10 +1505,10 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>28.525661608356199</v>
+        <v>28.5256616083573</v>
       </c>
       <c r="M14">
-        <v>4.2570799996609999E-4</v>
+        <v>4.2691699854910002E-4</v>
       </c>
       <c r="N14" s="1">
         <v>400</v>
@@ -1470,13 +1522,17 @@
       <c r="Q14">
         <v>3.5627416999886898E-2</v>
       </c>
-      <c r="R14" s="1"/>
-      <c r="S14">
+      <c r="R14" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S14" s="1"/>
+      <c r="T14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -1499,10 +1555,10 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>703.73073980000004</v>
+        <v>703.73073976309502</v>
       </c>
       <c r="I15">
-        <v>2.0529709E-2</v>
+        <v>2.0642125000449499E-2</v>
       </c>
       <c r="J15" s="1">
         <v>1950</v>
@@ -1511,10 +1567,10 @@
         <v>8</v>
       </c>
       <c r="L15">
-        <v>721.74215189248798</v>
+        <v>721.74215185574405</v>
       </c>
       <c r="M15">
-        <v>4.5716250001531997E-3</v>
+        <v>4.4752079993485997E-3</v>
       </c>
       <c r="N15" s="1">
         <v>400</v>
@@ -1528,13 +1584,17 @@
       <c r="Q15">
         <v>0.23854741699960799</v>
       </c>
-      <c r="R15" s="1"/>
-      <c r="S15">
+      <c r="R15" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S15" s="1"/>
+      <c r="T15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -1557,10 +1617,10 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>121.8749579</v>
+        <v>34.689657014435099</v>
       </c>
       <c r="I16">
-        <v>2.2914082999999998E-2</v>
+        <v>2.33290420001139E-2</v>
       </c>
       <c r="J16" s="1">
         <v>244</v>
@@ -1569,10 +1629,10 @@
         <v>7</v>
       </c>
       <c r="L16">
-        <v>32.0453458877613</v>
+        <v>32.045345884309199</v>
       </c>
       <c r="M16">
-        <v>7.7662500007130003E-4</v>
+        <v>7.5362499956090003E-4</v>
       </c>
       <c r="N16" s="1">
         <v>400</v>
@@ -1586,13 +1646,17 @@
       <c r="Q16">
         <v>0.11277620800001301</v>
       </c>
-      <c r="R16" s="1"/>
-      <c r="S16">
+      <c r="R16" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S16" s="1"/>
+      <c r="T16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -1615,10 +1679,10 @@
         <v>10</v>
       </c>
       <c r="H17">
-        <v>1174.968738</v>
+        <v>1174.96873752942</v>
       </c>
       <c r="I17">
-        <v>2.2449666E-2</v>
+        <v>2.25255419991299E-2</v>
       </c>
       <c r="J17" s="1">
         <v>3893</v>
@@ -1627,10 +1691,10 @@
         <v>2</v>
       </c>
       <c r="L17">
-        <v>1388.1447966867099</v>
+        <v>1388.1447966866599</v>
       </c>
       <c r="M17">
-        <v>9.0354170001774002E-3</v>
+        <v>9.1152080003666005E-3</v>
       </c>
       <c r="N17" s="1">
         <v>400</v>
@@ -1644,13 +1708,17 @@
       <c r="Q17">
         <v>0.24814691700021199</v>
       </c>
-      <c r="R17" s="1"/>
-      <c r="S17">
+      <c r="R17">
+        <f t="shared" si="1"/>
+        <v>2.8509503529332188E-2</v>
+      </c>
+      <c r="S17" s="1"/>
+      <c r="T17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -1673,10 +1741,10 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>690.36434489999999</v>
+        <v>183.09944673815801</v>
       </c>
       <c r="I18">
-        <v>2.2153583000000001E-2</v>
+        <v>2.25864170006389E-2</v>
       </c>
       <c r="J18" s="1">
         <v>246</v>
@@ -1685,10 +1753,10 @@
         <v>2</v>
       </c>
       <c r="L18">
-        <v>45.505017190990898</v>
+        <v>45.5050171909539</v>
       </c>
       <c r="M18">
-        <v>7.5229100002609998E-4</v>
+        <v>7.6558299952010004E-4</v>
       </c>
       <c r="N18" s="1">
         <v>400</v>
@@ -1702,13 +1770,17 @@
       <c r="Q18">
         <v>0.12165449999974901</v>
       </c>
-      <c r="R18" s="1"/>
-      <c r="S18">
+      <c r="R18" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S18" s="1"/>
+      <c r="T18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -1731,10 +1803,10 @@
         <v>10</v>
       </c>
       <c r="H19">
-        <v>776.78840590000004</v>
+        <v>776.78840586934405</v>
       </c>
       <c r="I19">
-        <v>2.1136333E-2</v>
+        <v>2.1239875000901499E-2</v>
       </c>
       <c r="J19" s="1">
         <v>3376</v>
@@ -1743,10 +1815,10 @@
         <v>2</v>
       </c>
       <c r="L19">
-        <v>921.55344020431801</v>
+        <v>921.55344020151199</v>
       </c>
       <c r="M19">
-        <v>7.7599999999620004E-3</v>
+        <v>7.6976249983999002E-3</v>
       </c>
       <c r="N19" s="1">
         <v>400</v>
@@ -1760,13 +1832,17 @@
       <c r="Q19">
         <v>0.23187733299982899</v>
       </c>
-      <c r="R19" s="1"/>
-      <c r="S19">
+      <c r="R19" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S19" s="1"/>
+      <c r="T19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -1789,10 +1865,10 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>154.96064699999999</v>
+        <v>43.035614517001903</v>
       </c>
       <c r="I20">
-        <v>2.7222290999999999E-2</v>
+        <v>2.35779159993398E-2</v>
       </c>
       <c r="J20" s="1">
         <v>246</v>
@@ -1801,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>14.071543688653501</v>
+        <v>14.071543688649699</v>
       </c>
       <c r="M20">
-        <v>7.7291599973250001E-4</v>
+        <v>7.4991699875680002E-4</v>
       </c>
       <c r="N20" s="1">
         <v>400</v>
@@ -1818,13 +1894,17 @@
       <c r="Q20">
         <v>6.4058417000069298E-2</v>
       </c>
-      <c r="R20" s="1"/>
-      <c r="S20">
+      <c r="R20" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S20" s="1"/>
+      <c r="T20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1847,10 +1927,10 @@
         <v>10</v>
       </c>
       <c r="H21">
-        <v>2233.454385</v>
+        <v>2233.4543852075799</v>
       </c>
       <c r="I21">
-        <v>6.1114166999999997E-2</v>
+        <v>6.0550374999365802E-2</v>
       </c>
       <c r="J21" s="1">
         <v>2554</v>
@@ -1862,7 +1942,7 @@
         <v>2286.6403570822299</v>
       </c>
       <c r="M21">
-        <v>5.7580419997975002E-3</v>
+        <v>5.7242079983552E-3</v>
       </c>
       <c r="N21" s="1">
         <v>400</v>
@@ -1876,13 +1956,17 @@
       <c r="Q21">
         <v>0.23167404199966701</v>
       </c>
-      <c r="R21" s="1"/>
-      <c r="S21">
+      <c r="R21" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S21" s="1"/>
+      <c r="T21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -1905,10 +1989,10 @@
         <v>10</v>
       </c>
       <c r="H22">
-        <v>17482.247859999999</v>
+        <v>4726.1067260092696</v>
       </c>
       <c r="I22">
-        <v>2.9614833E-2</v>
+        <v>2.8701416998956099E-2</v>
       </c>
       <c r="J22" s="1">
         <v>266</v>
@@ -1920,7 +2004,7 @@
         <v>294.075487969275</v>
       </c>
       <c r="M22">
-        <v>8.070419999057E-4</v>
+        <v>8.0600000001140003E-4</v>
       </c>
       <c r="N22" s="1">
         <v>400</v>
@@ -1934,13 +2018,17 @@
       <c r="Q22">
         <v>6.6929708999850804E-2</v>
       </c>
-      <c r="R22" s="1"/>
-      <c r="S22">
+      <c r="R22" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S22" s="1"/>
+      <c r="T22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -1963,10 +2051,10 @@
         <v>10</v>
       </c>
       <c r="H23">
-        <v>1537.8969259999999</v>
+        <v>1537.89692594907</v>
       </c>
       <c r="I23">
-        <v>2.4916166999999999E-2</v>
+        <v>2.5402334000318601E-2</v>
       </c>
       <c r="J23" s="1">
         <v>4286</v>
@@ -1975,10 +2063,10 @@
         <v>1</v>
       </c>
       <c r="L23">
-        <v>1621.9412258868899</v>
+        <v>1621.9412258868799</v>
       </c>
       <c r="M23">
-        <v>9.6722499997667008E-3</v>
+        <v>9.6422500009794004E-3</v>
       </c>
       <c r="N23" s="1">
         <v>400</v>
@@ -1992,13 +2080,17 @@
       <c r="Q23">
         <v>0.245683124999686</v>
       </c>
-      <c r="R23" s="1"/>
-      <c r="S23">
+      <c r="R23" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S23" s="1"/>
+      <c r="T23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -2021,10 +2113,10 @@
         <v>10</v>
       </c>
       <c r="H24">
-        <v>1803.1089609999999</v>
+        <v>497.55302027796102</v>
       </c>
       <c r="I24">
-        <v>2.6360667000000001E-2</v>
+        <v>2.6228792001347701E-2</v>
       </c>
       <c r="J24" s="1">
         <v>258</v>
@@ -2033,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>31.554707791756599</v>
+        <v>31.554707791756801</v>
       </c>
       <c r="M24">
-        <v>7.8245800023060003E-4</v>
+        <v>7.7354199856919997E-4</v>
       </c>
       <c r="N24" s="1">
         <v>400</v>
@@ -2050,13 +2142,17 @@
       <c r="Q24">
         <v>6.6515416000129293E-2</v>
       </c>
-      <c r="R24" s="1"/>
-      <c r="S24">
+      <c r="R24" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S24" s="1"/>
+      <c r="T24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -2079,10 +2175,10 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>1499.625781</v>
+        <v>1499.62578072622</v>
       </c>
       <c r="I25">
-        <v>2.2371833000000001E-2</v>
+        <v>2.24415829998179E-2</v>
       </c>
       <c r="J25" s="1">
         <v>5736</v>
@@ -2094,7 +2190,7 @@
         <v>1618.5261927461199</v>
       </c>
       <c r="M25">
-        <v>1.30585829997471E-2</v>
+        <v>1.2934625001435E-2</v>
       </c>
       <c r="N25" s="1">
         <v>400</v>
@@ -2108,13 +2204,17 @@
       <c r="Q25">
         <v>0.28359795899996199</v>
       </c>
-      <c r="R25" s="1"/>
-      <c r="S25">
+      <c r="R25" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S25" s="1"/>
+      <c r="T25">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -2137,10 +2237,10 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>2230.8470339999999</v>
+        <v>602.60833157756599</v>
       </c>
       <c r="I26">
-        <v>2.3443291000000002E-2</v>
+        <v>2.3885416998382401E-2</v>
       </c>
       <c r="J26" s="1">
         <v>246</v>
@@ -2152,7 +2252,7 @@
         <v>35.710028706881097</v>
       </c>
       <c r="M26">
-        <v>7.4383400033179998E-4</v>
+        <v>7.4612499884089999E-4</v>
       </c>
       <c r="N26" s="1">
         <v>400</v>
@@ -2166,13 +2266,17 @@
       <c r="Q26">
         <v>6.3750917000106697E-2</v>
       </c>
-      <c r="R26" s="1"/>
-      <c r="S26">
+      <c r="R26" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S26" s="1"/>
+      <c r="T26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -2195,10 +2299,10 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>1570.098612</v>
+        <v>1570.0986124132901</v>
       </c>
       <c r="I27">
-        <v>2.0401834000000001E-2</v>
+        <v>2.03480830004991E-2</v>
       </c>
       <c r="J27" s="1">
         <v>2828</v>
@@ -2210,7 +2314,7 @@
         <v>1620.3091390955301</v>
       </c>
       <c r="M27">
-        <v>6.3926249999893998E-3</v>
+        <v>6.2595840008725003E-3</v>
       </c>
       <c r="N27" s="1">
         <v>400</v>
@@ -2224,13 +2328,17 @@
       <c r="Q27">
         <v>0.21492808299990401</v>
       </c>
-      <c r="R27" s="1"/>
-      <c r="S27">
+      <c r="R27" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S27" s="1"/>
+      <c r="T27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -2253,10 +2361,10 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>2827.123466</v>
+        <v>815.418750065057</v>
       </c>
       <c r="I28">
-        <v>2.4025541000000001E-2</v>
+        <v>2.38602499994158E-2</v>
       </c>
       <c r="J28" s="1">
         <v>244</v>
@@ -2265,10 +2373,10 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>55.576376345611301</v>
+        <v>55.576376345611699</v>
       </c>
       <c r="M28">
-        <v>7.3808300021480002E-4</v>
+        <v>7.4733300061779996E-4</v>
       </c>
       <c r="N28" s="1">
         <v>400</v>
@@ -2282,13 +2390,17 @@
       <c r="Q28">
         <v>6.3204916999893598E-2</v>
       </c>
-      <c r="R28" s="1"/>
-      <c r="S28">
+      <c r="R28" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S28" s="1"/>
+      <c r="T28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>9</v>
       </c>
@@ -2311,10 +2423,10 @@
         <v>10</v>
       </c>
       <c r="H29">
-        <v>1516.288022</v>
+        <v>1516.2880216756</v>
       </c>
       <c r="I29">
-        <v>2.9005834000000001E-2</v>
+        <v>2.8862457998911802E-2</v>
       </c>
       <c r="J29" s="1">
         <v>1235</v>
@@ -2323,10 +2435,10 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>1573.14837313369</v>
+        <v>1573.1483731337</v>
       </c>
       <c r="M29">
-        <v>2.8410830000211002E-3</v>
+        <v>2.8499170002760001E-3</v>
       </c>
       <c r="N29" s="1">
         <v>400</v>
@@ -2340,13 +2452,17 @@
       <c r="Q29">
         <v>9.2376625000269996E-2</v>
       </c>
-      <c r="R29" s="1"/>
-      <c r="S29">
+      <c r="R29" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S29" s="1"/>
+      <c r="T29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>9</v>
       </c>
@@ -2369,10 +2485,10 @@
         <v>10</v>
       </c>
       <c r="H30">
-        <v>1475.742933</v>
+        <v>417.76059881302803</v>
       </c>
       <c r="I30">
-        <v>3.0545875E-2</v>
+        <v>3.0643165999208501E-2</v>
       </c>
       <c r="J30" s="1">
         <v>266</v>
@@ -2381,10 +2497,10 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>19.366121041389899</v>
+        <v>19.366121041390201</v>
       </c>
       <c r="M30">
-        <v>8.1291699962089995E-4</v>
+        <v>8.3033299961240005E-4</v>
       </c>
       <c r="N30" s="1">
         <v>400</v>
@@ -2398,13 +2514,17 @@
       <c r="Q30">
         <v>6.9395957999858995E-2</v>
       </c>
-      <c r="R30" s="1"/>
-      <c r="S30">
+      <c r="R30" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S30" s="1"/>
+      <c r="T30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -2427,10 +2547,10 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>1840.097491</v>
+        <v>1840.0974912085201</v>
       </c>
       <c r="I31">
-        <v>2.9298791000000001E-2</v>
+        <v>2.88386659995012E-2</v>
       </c>
       <c r="J31" s="1">
         <v>2391</v>
@@ -2439,10 +2559,10 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>1955.9147773013799</v>
+        <v>1955.9147773013899</v>
       </c>
       <c r="M31">
-        <v>5.3604170002472E-3</v>
+        <v>5.3568749990517001E-3</v>
       </c>
       <c r="N31" s="1">
         <v>400</v>
@@ -2456,13 +2576,17 @@
       <c r="Q31">
         <v>0.53979287499987505</v>
       </c>
-      <c r="R31" s="1"/>
-      <c r="S31">
+      <c r="R31" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S31" s="1"/>
+      <c r="T31">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -2485,10 +2609,10 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>4355.719349</v>
+        <v>1241.41913480218</v>
       </c>
       <c r="I32">
-        <v>3.0907625000000001E-2</v>
+        <v>3.07421249999606E-2</v>
       </c>
       <c r="J32" s="1">
         <v>266</v>
@@ -2497,10 +2621,10 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>73.154615060258607</v>
+        <v>73.154615060258706</v>
       </c>
       <c r="M32">
-        <v>8.0287499986290002E-4</v>
+        <v>7.997500015335E-4</v>
       </c>
       <c r="N32" s="1">
         <v>400</v>
@@ -2514,13 +2638,17 @@
       <c r="Q32">
         <v>6.80429169997296E-2</v>
       </c>
-      <c r="R32" s="1"/>
-      <c r="S32">
+      <c r="R32" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S32" s="1"/>
+      <c r="T32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>9</v>
       </c>
@@ -2543,10 +2671,10 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>1176.58329</v>
+        <v>1176.58328992621</v>
       </c>
       <c r="I33">
-        <v>1.3838334000000001E-2</v>
+        <v>1.3535584001147001E-2</v>
       </c>
       <c r="J33" s="1">
         <v>3231</v>
@@ -2558,7 +2686,7 @@
         <v>1273.0045571595499</v>
       </c>
       <c r="M33">
-        <v>7.3234999999839999E-3</v>
+        <v>7.3171250005543004E-3</v>
       </c>
       <c r="N33" s="1">
         <v>400</v>
@@ -2572,13 +2700,17 @@
       <c r="Q33">
         <v>0.24662879100014801</v>
       </c>
-      <c r="R33" s="1"/>
-      <c r="S33">
+      <c r="R33" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S33" s="1"/>
+      <c r="T33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -2601,10 +2733,10 @@
         <v>10</v>
       </c>
       <c r="H34">
-        <v>1078.7455829999999</v>
+        <v>308.22554380717401</v>
       </c>
       <c r="I34">
-        <v>1.6414874999999999E-2</v>
+        <v>1.6589250000833999E-2</v>
       </c>
       <c r="J34" s="1">
         <v>218</v>
@@ -2613,10 +2745,10 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>24.161143430101198</v>
+        <v>24.161143430101099</v>
       </c>
       <c r="M34">
-        <v>6.7779200026050004E-4</v>
+        <v>6.7116699938189999E-4</v>
       </c>
       <c r="N34" s="1">
         <v>400</v>
@@ -2630,13 +2762,17 @@
       <c r="Q34">
         <v>5.7045458999709801E-2</v>
       </c>
-      <c r="R34" s="1"/>
-      <c r="S34">
+      <c r="R34" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S34" s="1"/>
+      <c r="T34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>9</v>
       </c>
@@ -2659,10 +2795,10 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>612.26053330000002</v>
+        <v>612.26053328434296</v>
       </c>
       <c r="I35">
-        <v>4.2408339999999997E-3</v>
+        <v>4.2301659996154999E-3</v>
       </c>
       <c r="J35" s="1">
         <v>1988</v>
@@ -2671,10 +2807,10 @@
         <v>4</v>
       </c>
       <c r="L35">
-        <v>664.59311704458798</v>
+        <v>664.59311704472304</v>
       </c>
       <c r="M35">
-        <v>4.5308329999896998E-3</v>
+        <v>4.5255000004544004E-3</v>
       </c>
       <c r="N35" s="1">
         <v>400</v>
@@ -2688,13 +2824,17 @@
       <c r="Q35">
         <v>0.15228187499997101</v>
       </c>
-      <c r="R35" s="1"/>
-      <c r="S35">
+      <c r="R35" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S35" s="1"/>
+      <c r="T35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -2717,10 +2857,10 @@
         <v>10</v>
       </c>
       <c r="H36">
-        <v>203.58507560000001</v>
+        <v>63.5907224581129</v>
       </c>
       <c r="I36">
-        <v>4.682833E-3</v>
+        <v>4.6614580005552003E-3</v>
       </c>
       <c r="J36" s="1">
         <v>174</v>
@@ -2729,10 +2869,10 @@
         <v>2</v>
       </c>
       <c r="L36">
-        <v>29.576714183753399</v>
+        <v>29.576714183799201</v>
       </c>
       <c r="M36">
-        <v>5.3483300007420005E-4</v>
+        <v>5.340829993656E-4</v>
       </c>
       <c r="N36" s="1">
         <v>400</v>
@@ -2746,13 +2886,17 @@
       <c r="Q36">
         <v>4.4803540999964697E-2</v>
       </c>
-      <c r="R36" s="1"/>
-      <c r="S36">
+      <c r="R36" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S36" s="1"/>
+      <c r="T36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -2775,10 +2919,10 @@
         <v>10</v>
       </c>
       <c r="H37">
-        <v>1283.6495849999999</v>
+        <v>1283.64958535754</v>
       </c>
       <c r="I37">
-        <v>5.1625749999999998E-2</v>
+        <v>5.0656583000090898E-2</v>
       </c>
       <c r="J37" s="1">
         <v>4915</v>
@@ -2787,10 +2931,10 @@
         <v>2</v>
       </c>
       <c r="L37">
-        <v>1369.37997399241</v>
+        <v>1369.37997399242</v>
       </c>
       <c r="M37">
-        <v>1.1042999999972301E-2</v>
+        <v>1.13620419997459E-2</v>
       </c>
       <c r="N37" s="1">
         <v>400</v>
@@ -2804,13 +2948,17 @@
       <c r="Q37">
         <v>0.27393779200019702</v>
       </c>
-      <c r="R37" s="1"/>
-      <c r="S37">
+      <c r="R37" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S37" s="1"/>
+      <c r="T37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>9</v>
       </c>
@@ -2833,10 +2981,10 @@
         <v>10</v>
       </c>
       <c r="H38">
-        <v>1062.160429</v>
+        <v>283.23366526190603</v>
       </c>
       <c r="I38">
-        <v>2.2440749999999999E-2</v>
+        <v>2.3306749999392098E-2</v>
       </c>
       <c r="J38" s="1">
         <v>246</v>
@@ -2845,10 +2993,10 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>23.855071083061699</v>
+        <v>23.855071083061901</v>
       </c>
       <c r="M38">
-        <v>7.4900000026899998E-4</v>
+        <v>7.3291700027760002E-4</v>
       </c>
       <c r="N38" s="1">
         <v>400</v>
@@ -2862,13 +3010,17 @@
       <c r="Q38">
         <v>6.4518625000346205E-2</v>
       </c>
-      <c r="R38" s="1"/>
-      <c r="S38">
+      <c r="R38" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S38" s="1"/>
+      <c r="T38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>9</v>
       </c>
@@ -2891,10 +3043,10 @@
         <v>10</v>
       </c>
       <c r="H39">
-        <v>1224.2471499999999</v>
+        <v>1224.24714964292</v>
       </c>
       <c r="I39">
-        <v>2.7319916E-2</v>
+        <v>2.7123333999043001E-2</v>
       </c>
       <c r="J39" s="1">
         <v>5912</v>
@@ -2903,10 +3055,10 @@
         <v>2</v>
       </c>
       <c r="L39">
-        <v>1330.14178237888</v>
+        <v>1330.1417823788099</v>
       </c>
       <c r="M39">
-        <v>1.33752090000598E-2</v>
+        <v>1.3548124999942899E-2</v>
       </c>
       <c r="N39" s="1">
         <v>400</v>
@@ -2920,13 +3072,17 @@
       <c r="Q39">
         <v>0.3282644169999</v>
       </c>
-      <c r="R39" s="1"/>
-      <c r="S39">
+      <c r="R39" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S39" s="1"/>
+      <c r="T39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>9</v>
       </c>
@@ -2949,10 +3105,10 @@
         <v>10</v>
       </c>
       <c r="H40">
-        <v>544.03662970000005</v>
+        <v>148.05848912584599</v>
       </c>
       <c r="I40">
-        <v>2.89465E-2</v>
+        <v>2.91035410009499E-2</v>
       </c>
       <c r="J40" s="1">
         <v>266</v>
@@ -2961,10 +3117,10 @@
         <v>1</v>
       </c>
       <c r="L40">
-        <v>32.719573794234201</v>
+        <v>32.719573794235501</v>
       </c>
       <c r="M40">
-        <v>8.0125000022230003E-4</v>
+        <v>8.4695900113720003E-4</v>
       </c>
       <c r="N40" s="1">
         <v>400</v>
@@ -2978,13 +3134,17 @@
       <c r="Q40">
         <v>6.8160041999817594E-2</v>
       </c>
-      <c r="R40" s="1"/>
-      <c r="S40">
+      <c r="R40" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S40" s="1"/>
+      <c r="T40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>9</v>
       </c>
@@ -3007,10 +3167,10 @@
         <v>10</v>
       </c>
       <c r="H41">
-        <v>1772.6469259999999</v>
+        <v>1772.64692567458</v>
       </c>
       <c r="I41">
-        <v>2.7384540999999998E-2</v>
+        <v>2.75220420007826E-2</v>
       </c>
       <c r="J41" s="1">
         <v>1685</v>
@@ -3019,10 +3179,10 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>1906.9925842160301</v>
+        <v>1906.9925842160401</v>
       </c>
       <c r="M41">
-        <v>3.8849580000713999E-3</v>
+        <v>3.7926660006632998E-3</v>
       </c>
       <c r="N41" s="1">
         <v>400</v>
@@ -3036,13 +3196,17 @@
       <c r="Q41">
         <v>0.24056537499973199</v>
       </c>
-      <c r="R41" s="1"/>
-      <c r="S41">
+      <c r="R41" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S41" s="1"/>
+      <c r="T41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>9</v>
       </c>
@@ -3065,10 +3229,10 @@
         <v>10</v>
       </c>
       <c r="H42">
-        <v>4247.8778769999999</v>
+        <v>1102.2227488532201</v>
       </c>
       <c r="I42">
-        <v>2.9687041000000001E-2</v>
+        <v>3.0110792000414201E-2</v>
       </c>
       <c r="J42" s="1">
         <v>266</v>
@@ -3077,10 +3241,10 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>61.726077395808801</v>
+        <v>61.7260773958089</v>
       </c>
       <c r="M42">
-        <v>8.0233300013780005E-4</v>
+        <v>8.0808399980010005E-4</v>
       </c>
       <c r="N42" s="1">
         <v>400</v>
@@ -3094,13 +3258,17 @@
       <c r="Q42">
         <v>6.8534250000084201E-2</v>
       </c>
-      <c r="R42" s="1"/>
-      <c r="S42">
+      <c r="R42" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S42" s="1"/>
+      <c r="T42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -3123,10 +3291,10 @@
         <v>10</v>
       </c>
       <c r="H43">
-        <v>1504.0408440000001</v>
+        <v>1504.0408442484299</v>
       </c>
       <c r="I43">
-        <v>1.7877125000000001E-2</v>
+        <v>1.7659916999036698E-2</v>
       </c>
       <c r="J43" s="1">
         <v>2793</v>
@@ -3135,10 +3303,10 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>1577.0242400668301</v>
+        <v>1577.0242400668201</v>
       </c>
       <c r="M43">
-        <v>6.1153749998083999E-3</v>
+        <v>6.3067089995456002E-3</v>
       </c>
       <c r="N43" s="1">
         <v>400</v>
@@ -3152,13 +3320,17 @@
       <c r="Q43">
         <v>0.25763295799970298</v>
       </c>
-      <c r="R43" s="1"/>
-      <c r="S43">
+      <c r="R43" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S43" s="1"/>
+      <c r="T43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>9</v>
       </c>
@@ -3181,10 +3353,10 @@
         <v>10</v>
       </c>
       <c r="H44">
-        <v>3280.7276430000002</v>
+        <v>908.56816963772303</v>
       </c>
       <c r="I44">
-        <v>1.7504042000000001E-2</v>
+        <v>1.7593417000170999E-2</v>
       </c>
       <c r="J44" s="1">
         <v>230</v>
@@ -3193,10 +3365,10 @@
         <v>0</v>
       </c>
       <c r="L44">
-        <v>45.787848042376197</v>
+        <v>45.787848042375998</v>
       </c>
       <c r="M44">
-        <v>7.0504199993590003E-4</v>
+        <v>7.1470799957749995E-4</v>
       </c>
       <c r="N44" s="1">
         <v>400</v>
@@ -3210,13 +3382,17 @@
       <c r="Q44">
         <v>5.7783624999956297E-2</v>
       </c>
-      <c r="R44" s="1"/>
-      <c r="S44">
+      <c r="R44" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S44" s="1"/>
+      <c r="T44">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>9</v>
       </c>
@@ -3239,10 +3415,10 @@
         <v>8</v>
       </c>
       <c r="H45">
-        <v>915.65598999999997</v>
+        <v>915.65599004713397</v>
       </c>
       <c r="I45">
-        <v>6.0466700000000003E-4</v>
+        <v>6.114589996286E-4</v>
       </c>
       <c r="J45" s="1">
         <v>817</v>
@@ -3254,7 +3430,7 @@
         <v>941.65966425305203</v>
       </c>
       <c r="M45">
-        <v>1.8570000002000001E-3</v>
+        <v>1.8854579993785E-3</v>
       </c>
       <c r="N45" s="1">
         <v>400</v>
@@ -3268,13 +3444,17 @@
       <c r="Q45">
         <v>7.5617417000103104E-2</v>
       </c>
-      <c r="R45" s="1"/>
-      <c r="S45">
+      <c r="R45" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S45" s="1"/>
+      <c r="T45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>9</v>
       </c>
@@ -3297,10 +3477,10 @@
         <v>8</v>
       </c>
       <c r="H46">
-        <v>5385.9802200000004</v>
+        <v>1813.7011639406701</v>
       </c>
       <c r="I46">
-        <v>6.7108300000000005E-4</v>
+        <v>6.7149999995299995E-4</v>
       </c>
       <c r="J46" s="1">
         <v>116</v>
@@ -3312,7 +3492,7 @@
         <v>107.509798893568</v>
       </c>
       <c r="M46">
-        <v>3.8429100004570003E-4</v>
+        <v>3.5845799902739999E-4</v>
       </c>
       <c r="N46" s="1">
         <v>400</v>
@@ -3326,13 +3506,17 @@
       <c r="Q46">
         <v>3.03250410001965E-2</v>
       </c>
-      <c r="R46" s="1"/>
-      <c r="S46">
+      <c r="R46" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S46" s="1"/>
+      <c r="T46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>9</v>
       </c>
@@ -3355,10 +3539,10 @@
         <v>8</v>
       </c>
       <c r="H47">
-        <v>847.27541120000001</v>
+        <v>847.27541123226297</v>
       </c>
       <c r="I47">
-        <v>6.1716699999999995E-4</v>
+        <v>6.0466700051619996E-4</v>
       </c>
       <c r="J47" s="1">
         <v>161</v>
@@ -3370,7 +3554,7 @@
         <v>856.00637356914899</v>
       </c>
       <c r="M47">
-        <v>4.107089998797E-4</v>
+        <v>4.1216699901260002E-4</v>
       </c>
       <c r="N47" s="1">
         <v>400</v>
@@ -3384,13 +3568,17 @@
       <c r="Q47">
         <v>4.1321958000025902E-2</v>
       </c>
-      <c r="R47" s="1"/>
-      <c r="S47">
+      <c r="R47" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S47" s="1"/>
+      <c r="T47">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>9</v>
       </c>
@@ -3413,10 +3601,10 @@
         <v>8</v>
       </c>
       <c r="H48">
-        <v>3053.6218039999999</v>
+        <v>1028.2235594624599</v>
       </c>
       <c r="I48">
-        <v>6.6629099999999995E-4</v>
+        <v>6.7841599957309999E-4</v>
       </c>
       <c r="J48" s="1">
         <v>116</v>
@@ -3428,7 +3616,7 @@
         <v>57.795214403496999</v>
       </c>
       <c r="M48">
-        <v>3.762500000448E-4</v>
+        <v>3.61749998774E-4</v>
       </c>
       <c r="N48" s="1">
         <v>400</v>
@@ -3442,13 +3630,17 @@
       <c r="Q48">
         <v>3.1436750000011601E-2</v>
       </c>
-      <c r="R48" s="1"/>
-      <c r="S48">
+      <c r="R48" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S48" s="1"/>
+      <c r="T48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>9</v>
       </c>
@@ -3471,10 +3663,10 @@
         <v>8</v>
       </c>
       <c r="H49">
-        <v>977.61732859999995</v>
+        <v>977.61732862096596</v>
       </c>
       <c r="I49">
-        <v>6.6229099999999996E-4</v>
+        <v>6.5462500060669995E-4</v>
       </c>
       <c r="J49" s="1">
         <v>335</v>
@@ -3486,7 +3678,7 @@
         <v>993.84988286398197</v>
       </c>
       <c r="M49">
-        <v>8.2429200028850003E-4</v>
+        <v>8.1408400001230002E-4</v>
       </c>
       <c r="N49" s="1">
         <v>400</v>
@@ -3500,13 +3692,17 @@
       <c r="Q49">
         <v>4.1569707999769799E-2</v>
       </c>
-      <c r="R49" s="1"/>
-      <c r="S49">
+      <c r="R49" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S49" s="1"/>
+      <c r="T49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>9</v>
       </c>
@@ -3529,10 +3725,10 @@
         <v>8</v>
       </c>
       <c r="H50">
-        <v>8022.3457319999998</v>
+        <v>2723.22104735638</v>
       </c>
       <c r="I50">
-        <v>6.7537499999999998E-4</v>
+        <v>6.8108400046179996E-4</v>
       </c>
       <c r="J50" s="1">
         <v>116</v>
@@ -3544,7 +3740,7 @@
         <v>156.92562795901699</v>
       </c>
       <c r="M50">
-        <v>3.723329996319E-4</v>
+        <v>3.6700000055129998E-4</v>
       </c>
       <c r="N50" s="1">
         <v>400</v>
@@ -3558,13 +3754,17 @@
       <c r="Q50">
         <v>3.0280957999821102E-2</v>
       </c>
-      <c r="R50" s="1"/>
-      <c r="S50">
+      <c r="R50" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S50" s="1"/>
+      <c r="T50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>9</v>
       </c>
@@ -3587,10 +3787,10 @@
         <v>10</v>
       </c>
       <c r="H51">
-        <v>1375.480908</v>
+        <v>1375.4809083596399</v>
       </c>
       <c r="I51">
-        <v>1.6593666999999999E-2</v>
+        <v>1.6591542000242002E-2</v>
       </c>
       <c r="J51" s="1">
         <v>2717</v>
@@ -3599,10 +3799,10 @@
         <v>1</v>
       </c>
       <c r="L51">
-        <v>1438.3825139215101</v>
+        <v>1438.38251392148</v>
       </c>
       <c r="M51">
-        <v>6.0091249997640001E-3</v>
+        <v>6.1474590002034996E-3</v>
       </c>
       <c r="N51" s="1">
         <v>400</v>
@@ -3616,13 +3816,17 @@
       <c r="Q51">
         <v>0.19026974999997001</v>
       </c>
-      <c r="R51" s="1"/>
-      <c r="S51">
+      <c r="R51" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S51" s="1"/>
+      <c r="T51">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>9</v>
       </c>
@@ -3645,10 +3849,10 @@
         <v>10</v>
       </c>
       <c r="H52">
-        <v>1878.7407940000001</v>
+        <v>522.74138639523801</v>
       </c>
       <c r="I52">
-        <v>1.7546625E-2</v>
+        <v>1.7620208000153001E-2</v>
       </c>
       <c r="J52" s="1">
         <v>230</v>
@@ -3657,10 +3861,10 @@
         <v>0</v>
       </c>
       <c r="L52">
-        <v>41.882475058996</v>
+        <v>41.882475058996398</v>
       </c>
       <c r="M52">
-        <v>6.7870800012309997E-4</v>
+        <v>7.0658399999949998E-4</v>
       </c>
       <c r="N52" s="1">
         <v>400</v>
@@ -3674,13 +3878,17 @@
       <c r="Q52">
         <v>6.0836458000267102E-2</v>
       </c>
-      <c r="R52" s="1"/>
-      <c r="S52">
+      <c r="R52" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S52" s="1"/>
+      <c r="T52">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>9</v>
       </c>
@@ -3703,10 +3911,10 @@
         <v>8</v>
       </c>
       <c r="H53">
-        <v>450.43785839999998</v>
+        <v>450.43785842526103</v>
       </c>
       <c r="I53">
-        <v>9.6949999999999998E-4</v>
+        <v>9.5099999998630004E-4</v>
       </c>
       <c r="J53" s="1">
         <v>1156</v>
@@ -3715,10 +3923,10 @@
         <v>3</v>
       </c>
       <c r="L53">
-        <v>500.57053026860399</v>
+        <v>500.57053026950302</v>
       </c>
       <c r="M53">
-        <v>2.6191249999101E-3</v>
+        <v>2.6201670007138999E-3</v>
       </c>
       <c r="N53" s="1">
         <v>400</v>
@@ -3732,13 +3940,17 @@
       <c r="Q53">
         <v>0.10939058400026599</v>
       </c>
-      <c r="R53" s="1"/>
-      <c r="S53">
+      <c r="R53" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S53" s="1"/>
+      <c r="T53">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>9</v>
       </c>
@@ -3761,10 +3973,10 @@
         <v>8</v>
       </c>
       <c r="H54">
-        <v>155.46395179999999</v>
+        <v>51.543704643035802</v>
       </c>
       <c r="I54">
-        <v>1.020916E-3</v>
+        <v>1.0318749991710999E-3</v>
       </c>
       <c r="J54" s="1">
         <v>121</v>
@@ -3773,10 +3985,10 @@
         <v>3</v>
       </c>
       <c r="L54">
-        <v>30.677626344516099</v>
+        <v>30.677626344310202</v>
       </c>
       <c r="M54">
-        <v>3.8879200019429998E-4</v>
+        <v>3.991670000687E-4</v>
       </c>
       <c r="N54" s="1">
         <v>400</v>
@@ -3790,13 +4002,17 @@
       <c r="Q54">
         <v>5.9309167000264999E-2</v>
       </c>
-      <c r="R54" s="1"/>
-      <c r="S54">
+      <c r="R54" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S54" s="1"/>
+      <c r="T54">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>9</v>
       </c>
@@ -3819,10 +4035,10 @@
         <v>8</v>
       </c>
       <c r="H55">
-        <v>387.41182709999998</v>
+        <v>387.41182708830797</v>
       </c>
       <c r="I55">
-        <v>9.48375E-4</v>
+        <v>9.342080011265E-4</v>
       </c>
       <c r="J55" s="1">
         <v>1503</v>
@@ -3831,10 +4047,10 @@
         <v>1</v>
       </c>
       <c r="L55">
-        <v>458.27952520978698</v>
+        <v>458.27952521002197</v>
       </c>
       <c r="M55">
-        <v>3.3944159999919001E-3</v>
+        <v>3.4212079990538001E-3</v>
       </c>
       <c r="N55" s="1">
         <v>400</v>
@@ -3848,13 +4064,17 @@
       <c r="Q55">
         <v>9.0664708000076602E-2</v>
       </c>
-      <c r="R55" s="1"/>
-      <c r="S55">
+      <c r="R55" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S55" s="1"/>
+      <c r="T55">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -3877,10 +4097,10 @@
         <v>8</v>
       </c>
       <c r="H56">
-        <v>100.1082206</v>
+        <v>33.130250213412602</v>
       </c>
       <c r="I56">
-        <v>1.0068329999999999E-3</v>
+        <v>1.0313750008208E-3</v>
       </c>
       <c r="J56" s="1">
         <v>120</v>
@@ -3889,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="L56">
-        <v>6.1059345123744198</v>
+        <v>6.1059345123766597</v>
       </c>
       <c r="M56">
-        <v>3.7654200013999999E-4</v>
+        <v>3.732080003828E-4</v>
       </c>
       <c r="N56" s="1">
         <v>400</v>
@@ -3906,13 +4126,17 @@
       <c r="Q56">
         <v>3.1468041999687502E-2</v>
       </c>
-      <c r="R56" s="1"/>
-      <c r="S56">
+      <c r="R56" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S56" s="1"/>
+      <c r="T56">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>9</v>
       </c>
@@ -3935,10 +4159,10 @@
         <v>8</v>
       </c>
       <c r="H57">
-        <v>459.9607671</v>
+        <v>459.96076712762903</v>
       </c>
       <c r="I57">
-        <v>9.5229099999999997E-4</v>
+        <v>9.7879199893209992E-4</v>
       </c>
       <c r="J57" s="1">
         <v>1167</v>
@@ -3947,10 +4171,10 @@
         <v>3</v>
       </c>
       <c r="L57">
-        <v>509.03530897026502</v>
+        <v>509.03530897036501</v>
       </c>
       <c r="M57">
-        <v>2.7192080001440999E-3</v>
+        <v>2.6698330002544999E-3</v>
       </c>
       <c r="N57" s="1">
         <v>400</v>
@@ -3964,13 +4188,17 @@
       <c r="Q57">
         <v>8.1516166999790501E-2</v>
       </c>
-      <c r="R57" s="1"/>
-      <c r="S57">
+      <c r="R57" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S57" s="1"/>
+      <c r="T57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>9</v>
       </c>
@@ -3993,10 +4221,10 @@
         <v>8</v>
       </c>
       <c r="H58">
-        <v>185.58329699999999</v>
+        <v>60.886257111228602</v>
       </c>
       <c r="I58">
-        <v>1.0124579999999999E-3</v>
+        <v>1.0450000008859E-3</v>
       </c>
       <c r="J58" s="1">
         <v>120</v>
@@ -4005,10 +4233,10 @@
         <v>0</v>
       </c>
       <c r="L58">
-        <v>17.5004983847715</v>
+        <v>17.500498384772101</v>
       </c>
       <c r="M58">
-        <v>3.8516599988719998E-4</v>
+        <v>3.7545800114449998E-4</v>
       </c>
       <c r="N58" s="1">
         <v>400</v>
@@ -4022,13 +4250,17 @@
       <c r="Q58">
         <v>3.2420416000149999E-2</v>
       </c>
-      <c r="R58" s="1"/>
-      <c r="S58">
+      <c r="R58" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S58" s="1"/>
+      <c r="T58">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>9</v>
       </c>
@@ -4051,10 +4283,10 @@
         <v>8</v>
       </c>
       <c r="H59">
-        <v>540.53443979999997</v>
+        <v>540.53443981439204</v>
       </c>
       <c r="I59">
-        <v>9.2462499999999999E-4</v>
+        <v>9.4416700085269995E-4</v>
       </c>
       <c r="J59" s="1">
         <v>1525</v>
@@ -4063,10 +4295,10 @@
         <v>2</v>
       </c>
       <c r="L59">
-        <v>596.30217754058594</v>
+        <v>596.302177540564</v>
       </c>
       <c r="M59">
-        <v>3.4051669999826E-3</v>
+        <v>3.4311670005990002E-3</v>
       </c>
       <c r="N59" s="1">
         <v>400</v>
@@ -4080,13 +4312,17 @@
       <c r="Q59">
         <v>9.2703209000319406E-2</v>
       </c>
-      <c r="R59" s="1"/>
-      <c r="S59">
+      <c r="R59" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S59" s="1"/>
+      <c r="T59">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>9</v>
       </c>
@@ -4109,10 +4345,10 @@
         <v>8</v>
       </c>
       <c r="H60">
-        <v>336.38084880000002</v>
+        <v>113.349495401045</v>
       </c>
       <c r="I60">
-        <v>1.011458E-3</v>
+        <v>1.0385000005044001E-3</v>
       </c>
       <c r="J60" s="1">
         <v>120</v>
@@ -4121,10 +4357,10 @@
         <v>0</v>
       </c>
       <c r="L60">
-        <v>15.938366781650499</v>
+        <v>15.938366781648799</v>
       </c>
       <c r="M60">
-        <v>3.7833299984409998E-4</v>
+        <v>3.933340012736E-4</v>
       </c>
       <c r="N60" s="1">
         <v>400</v>
@@ -4138,13 +4374,17 @@
       <c r="Q60">
         <v>3.1038916999932501E-2</v>
       </c>
-      <c r="R60" s="1"/>
-      <c r="S60">
+      <c r="R60" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S60" s="1"/>
+      <c r="T60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -4167,10 +4407,10 @@
         <v>10</v>
       </c>
       <c r="H61">
-        <v>1786.9845089999999</v>
+        <v>1786.9845091484799</v>
       </c>
       <c r="I61">
-        <v>1.3727833E-2</v>
+        <v>1.3585499998953299E-2</v>
       </c>
       <c r="J61" s="1">
         <v>475</v>
@@ -4182,7 +4422,7 @@
         <v>1819.1989045335499</v>
       </c>
       <c r="M61">
-        <v>1.1299159996268999E-3</v>
+        <v>1.1531670006661001E-3</v>
       </c>
       <c r="N61" s="1">
         <v>400</v>
@@ -4196,13 +4436,17 @@
       <c r="Q61">
         <v>7.5487624999823297E-2</v>
       </c>
-      <c r="R61" s="1"/>
-      <c r="S61">
+      <c r="R61" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S61" s="1"/>
+      <c r="T61">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>9</v>
       </c>
@@ -4225,10 +4469,10 @@
         <v>10</v>
       </c>
       <c r="H62">
-        <v>13694.39626</v>
+        <v>4000.3929917128598</v>
       </c>
       <c r="I62">
-        <v>1.4310415999999999E-2</v>
+        <v>1.46728340005211E-2</v>
       </c>
       <c r="J62" s="1">
         <v>218</v>
@@ -4240,7 +4484,7 @@
         <v>175.84147826557</v>
       </c>
       <c r="M62">
-        <v>6.566670003849E-4</v>
+        <v>6.6449999940229999E-4</v>
       </c>
       <c r="N62" s="1">
         <v>400</v>
@@ -4254,13 +4498,17 @@
       <c r="Q62">
         <v>5.6404792000193903E-2</v>
       </c>
-      <c r="R62" s="1"/>
-      <c r="S62">
+      <c r="R62" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S62" s="1"/>
+      <c r="T62">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>48</v>
       </c>
@@ -4283,10 +4531,10 @@
         <v>10</v>
       </c>
       <c r="H63">
-        <v>1189.4819689999999</v>
+        <v>1189.48196931864</v>
       </c>
       <c r="I63">
-        <v>1.8218583E-2</v>
+        <v>1.75852499996835E-2</v>
       </c>
       <c r="J63" s="1">
         <v>4071</v>
@@ -4295,10 +4543,10 @@
         <v>2</v>
       </c>
       <c r="L63">
-        <v>1371.61975136555</v>
+        <v>1371.61975136554</v>
       </c>
       <c r="M63">
-        <v>9.2405830000642994E-3</v>
+        <v>9.2457089995150003E-3</v>
       </c>
       <c r="N63" s="1">
         <v>400</v>
@@ -4312,13 +4560,17 @@
       <c r="Q63">
         <v>0.28444370799979801</v>
       </c>
-      <c r="R63" s="1"/>
-      <c r="S63">
+      <c r="R63" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S63" s="1"/>
+      <c r="T63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>48</v>
       </c>
@@ -4341,10 +4593,10 @@
         <v>10</v>
       </c>
       <c r="H64">
-        <v>926.42506890000004</v>
+        <v>243.45017386389</v>
       </c>
       <c r="I64">
-        <v>1.7431292000000001E-2</v>
+        <v>1.75187499989988E-2</v>
       </c>
       <c r="J64" s="1">
         <v>231</v>
@@ -4353,10 +4605,10 @@
         <v>4</v>
       </c>
       <c r="L64">
-        <v>124.08714355459099</v>
+        <v>124.087143554593</v>
       </c>
       <c r="M64">
-        <v>7.5279099974060002E-4</v>
+        <v>7.0791699909019995E-4</v>
       </c>
       <c r="N64" s="1">
         <v>400</v>
@@ -4370,13 +4622,17 @@
       <c r="Q64">
         <v>0.18333408399985199</v>
       </c>
-      <c r="R64" s="1"/>
-      <c r="S64">
+      <c r="R64" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S64" s="1"/>
+      <c r="T64">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>48</v>
       </c>
@@ -4399,10 +4655,10 @@
         <v>10</v>
       </c>
       <c r="H65">
-        <v>1300.2807909999999</v>
+        <v>1300.28079069093</v>
       </c>
       <c r="I65">
-        <v>9.5860000000000008E-3</v>
+        <v>9.5443329992121999E-3</v>
       </c>
       <c r="J65" s="1">
         <v>2647</v>
@@ -4411,10 +4667,10 @@
         <v>4</v>
       </c>
       <c r="L65">
-        <v>1412.4797426438899</v>
+        <v>1412.4797426438799</v>
       </c>
       <c r="M65">
-        <v>5.9792090000883001E-3</v>
+        <v>5.9364999997342004E-3</v>
       </c>
       <c r="N65" s="1">
         <v>400</v>
@@ -4428,13 +4684,17 @@
       <c r="Q65">
         <v>0.21408041699987701</v>
       </c>
-      <c r="R65" s="1"/>
-      <c r="S65">
+      <c r="R65" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S65" s="1"/>
+      <c r="T65">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>48</v>
       </c>
@@ -4457,10 +4717,10 @@
         <v>10</v>
       </c>
       <c r="H66">
-        <v>4647.1598690000001</v>
+        <v>1280.03027432115</v>
       </c>
       <c r="I66">
-        <v>9.9813750000000007E-3</v>
+        <v>1.00625830000353E-2</v>
       </c>
       <c r="J66" s="1">
         <v>200</v>
@@ -4472,7 +4732,7 @@
         <v>418.16057244954999</v>
       </c>
       <c r="M66">
-        <v>6.0095800017729998E-4</v>
+        <v>6.2612500005340005E-4</v>
       </c>
       <c r="N66" s="1">
         <v>400</v>
@@ -4486,13 +4746,17 @@
       <c r="Q66">
         <v>0.152203542000279</v>
       </c>
-      <c r="R66" s="1"/>
-      <c r="S66">
+      <c r="R66" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S66" s="1"/>
+      <c r="T66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>48</v>
       </c>
@@ -4515,10 +4779,10 @@
         <v>10</v>
       </c>
       <c r="H67">
-        <v>931.72350100000006</v>
+        <v>931.723500984363</v>
       </c>
       <c r="I67">
-        <v>1.1068375E-2</v>
+        <v>1.10621669991815E-2</v>
       </c>
       <c r="J67" s="1">
         <v>2394</v>
@@ -4527,10 +4791,10 @@
         <v>1</v>
       </c>
       <c r="L67">
-        <v>985.39166772045405</v>
+        <v>985.39166772190197</v>
       </c>
       <c r="M67">
-        <v>5.2781670001421999E-3</v>
+        <v>5.3026669993413997E-3</v>
       </c>
       <c r="N67" s="1">
         <v>400</v>
@@ -4544,13 +4808,17 @@
       <c r="Q67">
         <v>0.158123624999916</v>
       </c>
-      <c r="R67" s="1"/>
-      <c r="S67">
-        <f t="shared" ref="S67:S130" si="1">IF(G67=K67,1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R67" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S67" s="1"/>
+      <c r="T67">
+        <f t="shared" ref="T67:T130" si="2">IF(G67=K67,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>48</v>
       </c>
@@ -4573,10 +4841,10 @@
         <v>10</v>
       </c>
       <c r="H68">
-        <v>473.91131760000002</v>
+        <v>139.339677348127</v>
       </c>
       <c r="I68">
-        <v>1.1953958000000001E-2</v>
+        <v>1.1937458000829701E-2</v>
       </c>
       <c r="J68" s="1">
         <v>208</v>
@@ -4585,10 +4853,10 @@
         <v>0</v>
       </c>
       <c r="L68">
-        <v>9.5227543280357594</v>
+        <v>9.5227543280621294</v>
       </c>
       <c r="M68">
-        <v>6.2766700011699999E-4</v>
+        <v>6.3308400058300002E-4</v>
       </c>
       <c r="N68" s="1">
         <v>400</v>
@@ -4602,13 +4870,17 @@
       <c r="Q68">
         <v>5.2448833000198598E-2</v>
       </c>
-      <c r="R68" s="1"/>
-      <c r="S68">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R68" t="e">
+        <f t="shared" ref="R68:R131" si="3">IF(O68=G68,(P68-H68)/H68,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="S68" s="1"/>
+      <c r="T68">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>48</v>
       </c>
@@ -4631,10 +4903,10 @@
         <v>10</v>
       </c>
       <c r="H69">
-        <v>1238.0323470000001</v>
+        <v>1238.03234706644</v>
       </c>
       <c r="I69">
-        <v>1.4789708E-2</v>
+        <v>1.46065000008093E-2</v>
       </c>
       <c r="J69" s="1">
         <v>2478</v>
@@ -4643,10 +4915,10 @@
         <v>3</v>
       </c>
       <c r="L69">
-        <v>1401.69122069023</v>
+        <v>1401.69122069022</v>
       </c>
       <c r="M69">
-        <v>5.6300419996659001E-3</v>
+        <v>5.6899169994721003E-3</v>
       </c>
       <c r="N69" s="1">
         <v>400</v>
@@ -4660,13 +4932,17 @@
       <c r="Q69">
         <v>0.19659437500013099</v>
       </c>
-      <c r="R69" s="1"/>
-      <c r="S69">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R69" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S69" s="1"/>
+      <c r="T69">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>48</v>
       </c>
@@ -4689,10 +4965,10 @@
         <v>10</v>
       </c>
       <c r="H70">
-        <v>1677.5588740000001</v>
+        <v>411.48273921183198</v>
       </c>
       <c r="I70">
-        <v>1.5377999999999999E-2</v>
+        <v>1.5521541999987599E-2</v>
       </c>
       <c r="J70" s="1">
         <v>222</v>
@@ -4701,10 +4977,10 @@
         <v>2</v>
       </c>
       <c r="L70">
-        <v>160.285929892909</v>
+        <v>160.28592989290999</v>
       </c>
       <c r="M70">
-        <v>6.9970799995639995E-4</v>
+        <v>6.8883399944750004E-4</v>
       </c>
       <c r="N70" s="1">
         <v>400</v>
@@ -4718,13 +4994,17 @@
       <c r="Q70">
         <v>0.14848445899997301</v>
       </c>
-      <c r="R70" s="1"/>
-      <c r="S70">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R70" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S70" s="1"/>
+      <c r="T70">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>48</v>
       </c>
@@ -4747,10 +5027,10 @@
         <v>10</v>
       </c>
       <c r="H71">
-        <v>5440.7021329999998</v>
+        <v>5440.7021329514901</v>
       </c>
       <c r="I71">
-        <v>2.4579465420000002</v>
+        <v>2.48874450000039</v>
       </c>
       <c r="J71" s="1">
         <v>22120</v>
@@ -4759,10 +5039,10 @@
         <v>25</v>
       </c>
       <c r="L71">
-        <v>4440.2728923075701</v>
+        <v>4440.2728923094701</v>
       </c>
       <c r="M71">
-        <v>5.5036792000009799E-2</v>
+        <v>5.5187291000038302E-2</v>
       </c>
       <c r="N71" s="1">
         <v>400</v>
@@ -4776,13 +5056,17 @@
       <c r="Q71">
         <v>2.9134759580001601</v>
       </c>
-      <c r="R71" s="1"/>
-      <c r="S71">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R71" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S71" s="1"/>
+      <c r="T71">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>48</v>
       </c>
@@ -4805,10 +5089,10 @@
         <v>10</v>
       </c>
       <c r="H72">
-        <v>309.4748654</v>
+        <v>27.6105030652989</v>
       </c>
       <c r="I72">
-        <v>2.7569609580000001</v>
+        <v>2.6532067499992902</v>
       </c>
       <c r="J72" s="1">
         <v>1455</v>
@@ -4817,10 +5101,10 @@
         <v>15</v>
       </c>
       <c r="L72">
-        <v>51.859168812200103</v>
+        <v>51.859168811490903</v>
       </c>
       <c r="M72">
-        <v>4.5194999997874999E-3</v>
+        <v>4.5707910012423997E-3</v>
       </c>
       <c r="N72" s="1">
         <v>400</v>
@@ -4834,13 +5118,17 @@
       <c r="Q72">
         <v>0.71025987499979204</v>
       </c>
-      <c r="R72" s="1"/>
-      <c r="S72">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R72" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S72" s="1"/>
+      <c r="T72">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>48</v>
       </c>
@@ -4863,10 +5151,10 @@
         <v>10</v>
       </c>
       <c r="H73">
-        <v>1327.7351430000001</v>
+        <v>1327.73514340783</v>
       </c>
       <c r="I73">
-        <v>2.3429249999999999E-2</v>
+        <v>2.3380915999950899E-2</v>
       </c>
       <c r="J73" s="1">
         <v>3083</v>
@@ -4875,10 +5163,10 @@
         <v>3</v>
       </c>
       <c r="L73">
-        <v>1415.3597817375501</v>
+        <v>1415.3597817375601</v>
       </c>
       <c r="M73">
-        <v>6.9876249999650999E-3</v>
+        <v>7.0712079996155001E-3</v>
       </c>
       <c r="N73" s="1">
         <v>400</v>
@@ -4892,13 +5180,17 @@
       <c r="Q73">
         <v>0.25321458300004401</v>
       </c>
-      <c r="R73" s="1"/>
-      <c r="S73">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R73">
+        <f t="shared" si="3"/>
+        <v>1.3622657032957798E-2</v>
+      </c>
+      <c r="S73" s="1"/>
+      <c r="T73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>48</v>
       </c>
@@ -4921,10 +5213,10 @@
         <v>10</v>
       </c>
       <c r="H74">
-        <v>1230.2837019999999</v>
+        <v>278.01964572696102</v>
       </c>
       <c r="I74">
-        <v>2.3317999999999998E-2</v>
+        <v>2.36000830009288E-2</v>
       </c>
       <c r="J74" s="1">
         <v>250</v>
@@ -4936,7 +5228,7 @@
         <v>47.766076107605699</v>
       </c>
       <c r="M74">
-        <v>7.5849999984710001E-4</v>
+        <v>7.5141600063939997E-4</v>
       </c>
       <c r="N74" s="1">
         <v>400</v>
@@ -4950,13 +5242,17 @@
       <c r="Q74">
         <v>6.4283041999715296E-2</v>
       </c>
-      <c r="R74" s="1"/>
-      <c r="S74">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R74" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S74" s="1"/>
+      <c r="T74">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>48</v>
       </c>
@@ -4979,10 +5275,10 @@
         <v>10</v>
       </c>
       <c r="H75">
-        <v>518.3483162</v>
+        <v>518.34831617008797</v>
       </c>
       <c r="I75">
-        <v>1.1279707999999999E-2</v>
+        <v>1.1779959000705199E-2</v>
       </c>
       <c r="J75" s="1">
         <v>2063</v>
@@ -4991,10 +5287,10 @@
         <v>4</v>
       </c>
       <c r="L75">
-        <v>668.45667378719997</v>
+        <v>668.45667378733106</v>
       </c>
       <c r="M75">
-        <v>4.7922920002746996E-3</v>
+        <v>4.7998749996622002E-3</v>
       </c>
       <c r="N75" s="1">
         <v>400</v>
@@ -5008,13 +5304,17 @@
       <c r="Q75">
         <v>0.18443308299993</v>
       </c>
-      <c r="R75" s="1"/>
-      <c r="S75">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R75" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S75" s="1"/>
+      <c r="T75">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>48</v>
       </c>
@@ -5037,10 +5337,10 @@
         <v>10</v>
       </c>
       <c r="H76">
-        <v>154.0470608</v>
+        <v>37.780207245815397</v>
       </c>
       <c r="I76">
-        <v>1.2283417E-2</v>
+        <v>1.2403624999933501E-2</v>
       </c>
       <c r="J76" s="1">
         <v>212</v>
@@ -5049,10 +5349,10 @@
         <v>6</v>
       </c>
       <c r="L76">
-        <v>50.4349404625166</v>
+        <v>50.434940462628198</v>
       </c>
       <c r="M76">
-        <v>6.6950000018550001E-4</v>
+        <v>6.5466700107199996E-4</v>
       </c>
       <c r="N76" s="1">
         <v>400</v>
@@ -5066,13 +5366,17 @@
       <c r="Q76">
         <v>0.117447874999925</v>
       </c>
-      <c r="R76" s="1"/>
-      <c r="S76">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R76" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S76" s="1"/>
+      <c r="T76">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>48</v>
       </c>
@@ -5095,10 +5399,10 @@
         <v>10</v>
       </c>
       <c r="H77">
-        <v>1335.609952</v>
+        <v>1335.6099523795999</v>
       </c>
       <c r="I77">
-        <v>1.6823874999999999E-2</v>
+        <v>1.7157791999125E-2</v>
       </c>
       <c r="J77" s="1">
         <v>2116</v>
@@ -5107,10 +5411,10 @@
         <v>5</v>
       </c>
       <c r="L77">
-        <v>1461.7521017950301</v>
+        <v>1461.7521017951999</v>
       </c>
       <c r="M77">
-        <v>4.8094580001816004E-3</v>
+        <v>4.7672919990872998E-3</v>
       </c>
       <c r="N77" s="1">
         <v>400</v>
@@ -5124,13 +5428,17 @@
       <c r="Q77">
         <v>0.20745704199998699</v>
       </c>
-      <c r="R77" s="1"/>
-      <c r="S77">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R77" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S77" s="1"/>
+      <c r="T77">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>48</v>
       </c>
@@ -5153,10 +5461,10 @@
         <v>10</v>
       </c>
       <c r="H78">
-        <v>3155.5928319999998</v>
+        <v>781.14457615011997</v>
       </c>
       <c r="I78">
-        <v>1.5732040999999999E-2</v>
+        <v>1.5989916999387701E-2</v>
       </c>
       <c r="J78" s="1">
         <v>224</v>
@@ -5165,10 +5473,10 @@
         <v>4</v>
       </c>
       <c r="L78">
-        <v>546.70127664732797</v>
+        <v>546.70127664785105</v>
       </c>
       <c r="M78">
-        <v>7.2429200008620001E-4</v>
+        <v>7.0254099955489998E-4</v>
       </c>
       <c r="N78" s="1">
         <v>400</v>
@@ -5182,13 +5490,17 @@
       <c r="Q78">
         <v>0.15224995800008401</v>
       </c>
-      <c r="R78" s="1"/>
-      <c r="S78">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R78" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S78" s="1"/>
+      <c r="T78">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>48</v>
       </c>
@@ -5211,10 +5523,10 @@
         <v>10</v>
       </c>
       <c r="H79">
-        <v>690.47822580000002</v>
+        <v>690.47822581320702</v>
       </c>
       <c r="I79">
-        <v>1.1667583E-2</v>
+        <v>1.21261250005773E-2</v>
       </c>
       <c r="J79" s="1">
         <v>2674</v>
@@ -5223,10 +5535,10 @@
         <v>2</v>
       </c>
       <c r="L79">
-        <v>813.83722281174903</v>
+        <v>813.83722281161795</v>
       </c>
       <c r="M79">
-        <v>6.0170000001562004E-3</v>
+        <v>6.1164580001786002E-3</v>
       </c>
       <c r="N79" s="1">
         <v>400</v>
@@ -5240,13 +5552,17 @@
       <c r="Q79">
         <v>0.190566042000227</v>
       </c>
-      <c r="R79" s="1"/>
-      <c r="S79">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R79" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S79" s="1"/>
+      <c r="T79">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>48</v>
       </c>
@@ -5269,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="H80">
-        <v>160.6315783</v>
+        <v>46.984978331236299</v>
       </c>
       <c r="I80">
-        <v>1.2676750000000001E-2</v>
+        <v>1.27968750002764E-2</v>
       </c>
       <c r="J80" s="1">
         <v>212</v>
@@ -5281,10 +5597,10 @@
         <v>0</v>
       </c>
       <c r="L80">
-        <v>10.855460221071599</v>
+        <v>10.855460221071199</v>
       </c>
       <c r="M80">
-        <v>6.3720800017100004E-4</v>
+        <v>6.3795799906070003E-4</v>
       </c>
       <c r="N80" s="1">
         <v>400</v>
@@ -5298,13 +5614,17 @@
       <c r="Q80">
         <v>5.42672500000662E-2</v>
       </c>
-      <c r="R80" s="1"/>
-      <c r="S80">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R80" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S80" s="1"/>
+      <c r="T80">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>48</v>
       </c>
@@ -5327,10 +5647,10 @@
         <v>10</v>
       </c>
       <c r="H81">
-        <v>6334.8321569999998</v>
+        <v>6334.8321570067501</v>
       </c>
       <c r="I81">
-        <v>2.7280549999999999</v>
+        <v>2.5048156669999999</v>
       </c>
       <c r="J81" s="1">
         <v>30032</v>
@@ -5339,10 +5659,10 @@
         <v>16</v>
       </c>
       <c r="L81">
-        <v>5857.1387547762997</v>
+        <v>5857.1387548229204</v>
       </c>
       <c r="M81">
-        <v>7.2193749999769297E-2</v>
+        <v>7.1511624999402501E-2</v>
       </c>
       <c r="N81" s="1">
         <v>400</v>
@@ -5356,13 +5676,17 @@
       <c r="Q81">
         <v>2.69349258300007</v>
       </c>
-      <c r="R81" s="1"/>
-      <c r="S81">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R81" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S81" s="1"/>
+      <c r="T81">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>48</v>
       </c>
@@ -5385,10 +5709,10 @@
         <v>10</v>
       </c>
       <c r="H82">
-        <v>545.41072829999996</v>
+        <v>46.950659417740503</v>
       </c>
       <c r="I82">
-        <v>2.6286477920000002</v>
+        <v>2.61326641699997</v>
       </c>
       <c r="J82" s="1">
         <v>1454</v>
@@ -5397,10 +5721,10 @@
         <v>0</v>
       </c>
       <c r="L82">
-        <v>25.176102248208299</v>
+        <v>25.176102248208199</v>
       </c>
       <c r="M82">
-        <v>4.2838340000343998E-3</v>
+        <v>4.4033329995727E-3</v>
       </c>
       <c r="N82" s="1">
         <v>400</v>
@@ -5414,13 +5738,17 @@
       <c r="Q82">
         <v>0.73086650000004705</v>
       </c>
-      <c r="R82" s="1"/>
-      <c r="S82">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R82" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S82" s="1"/>
+      <c r="T82">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>48</v>
       </c>
@@ -5443,10 +5771,10 @@
         <v>10</v>
       </c>
       <c r="H83">
-        <v>1298.749777</v>
+        <v>1298.74977702859</v>
       </c>
       <c r="I83">
-        <v>4.1141333000000002E-2</v>
+        <v>4.1746083999896599E-2</v>
       </c>
       <c r="J83" s="1">
         <v>5477</v>
@@ -5455,10 +5783,10 @@
         <v>4</v>
       </c>
       <c r="L83">
-        <v>1417.41236637675</v>
+        <v>1417.4123663767</v>
       </c>
       <c r="M83">
-        <v>1.28483329999653E-2</v>
+        <v>1.26722090008115E-2</v>
       </c>
       <c r="N83" s="1">
         <v>400</v>
@@ -5472,13 +5800,17 @@
       <c r="Q83">
         <v>0.36215595900011899</v>
       </c>
-      <c r="R83" s="1"/>
-      <c r="S83">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R83" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S83" s="1"/>
+      <c r="T83">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>48</v>
       </c>
@@ -5501,10 +5833,10 @@
         <v>10</v>
       </c>
       <c r="H84">
-        <v>393.34323940000002</v>
+        <v>98.178665337066406</v>
       </c>
       <c r="I84">
-        <v>4.3626708E-2</v>
+        <v>4.3787542001154998E-2</v>
       </c>
       <c r="J84" s="1">
         <v>303</v>
@@ -5513,10 +5845,10 @@
         <v>1</v>
       </c>
       <c r="L84">
-        <v>43.455069017885599</v>
+        <v>43.455069017886203</v>
       </c>
       <c r="M84">
-        <v>9.296250000261E-4</v>
+        <v>9.2241699894649997E-4</v>
       </c>
       <c r="N84" s="1">
         <v>400</v>
@@ -5530,13 +5862,17 @@
       <c r="Q84">
         <v>0.14835104200028501</v>
       </c>
-      <c r="R84" s="1"/>
-      <c r="S84">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R84" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S84" s="1"/>
+      <c r="T84">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>48</v>
       </c>
@@ -5559,10 +5895,10 @@
         <v>10</v>
       </c>
       <c r="H85">
-        <v>965.12750270000004</v>
+        <v>965.12750272286098</v>
       </c>
       <c r="I85">
-        <v>1.5701625E-2</v>
+        <v>1.44393330010643E-2</v>
       </c>
       <c r="J85" s="1">
         <v>2024</v>
@@ -5571,10 +5907,10 @@
         <v>5</v>
       </c>
       <c r="L85">
-        <v>1059.5716455999</v>
+        <v>1059.57164559994</v>
       </c>
       <c r="M85">
-        <v>4.7528750001219998E-3</v>
+        <v>4.6762500005569996E-3</v>
       </c>
       <c r="N85" s="1">
         <v>400</v>
@@ -5588,13 +5924,17 @@
       <c r="Q85">
         <v>0.189811333000307</v>
       </c>
-      <c r="R85" s="1"/>
-      <c r="S85">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R85">
+        <f t="shared" si="3"/>
+        <v>3.0253729106677896E-2</v>
+      </c>
+      <c r="S85" s="1"/>
+      <c r="T85">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>48</v>
       </c>
@@ -5617,10 +5957,10 @@
         <v>10</v>
       </c>
       <c r="H86">
-        <v>526.73852629999999</v>
+        <v>133.33143692173601</v>
       </c>
       <c r="I86">
-        <v>1.5688917E-2</v>
+        <v>1.53465830007917E-2</v>
       </c>
       <c r="J86" s="1">
         <v>222</v>
@@ -5629,10 +5969,10 @@
         <v>4</v>
       </c>
       <c r="L86">
-        <v>88.469596112966997</v>
+        <v>88.469596112994793</v>
       </c>
       <c r="M86">
-        <v>7.3354200003449997E-4</v>
+        <v>7.0929100002100004E-4</v>
       </c>
       <c r="N86" s="1">
         <v>400</v>
@@ -5646,13 +5986,17 @@
       <c r="Q86">
         <v>0.14625358300008801</v>
       </c>
-      <c r="R86" s="1"/>
-      <c r="S86">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R86" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S86" s="1"/>
+      <c r="T86">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>48</v>
       </c>
@@ -5675,10 +6019,10 @@
         <v>10</v>
       </c>
       <c r="H87">
-        <v>1615.664336</v>
+        <v>1615.66433617185</v>
       </c>
       <c r="I87">
-        <v>1.2925459E-2</v>
+        <v>1.2730582999210999E-2</v>
       </c>
       <c r="J87" s="1">
         <v>769</v>
@@ -5690,7 +6034,7 @@
         <v>1634.5698089182299</v>
       </c>
       <c r="M87">
-        <v>1.780250000138E-3</v>
+        <v>1.775415999873E-3</v>
       </c>
       <c r="N87" s="1">
         <v>400</v>
@@ -5704,13 +6048,17 @@
       <c r="Q87">
         <v>0.131512166999982</v>
       </c>
-      <c r="R87" s="1"/>
-      <c r="S87">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R87" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S87" s="1"/>
+      <c r="T87">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>48</v>
       </c>
@@ -5733,10 +6081,10 @@
         <v>10</v>
       </c>
       <c r="H88">
-        <v>6795.6456550000003</v>
+        <v>2126.2918803257098</v>
       </c>
       <c r="I88">
-        <v>1.3232541E-2</v>
+        <v>1.32818749989382E-2</v>
       </c>
       <c r="J88" s="1">
         <v>214</v>
@@ -5745,10 +6093,10 @@
         <v>0</v>
       </c>
       <c r="L88">
-        <v>92.190011850326997</v>
+        <v>92.190011850326599</v>
       </c>
       <c r="M88">
-        <v>6.7975000001750001E-4</v>
+        <v>6.4641599965390003E-4</v>
       </c>
       <c r="N88" s="1">
         <v>400</v>
@@ -5762,13 +6110,17 @@
       <c r="Q88">
         <v>5.4346875000192002E-2</v>
       </c>
-      <c r="R88" s="1"/>
-      <c r="S88">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R88" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S88" s="1"/>
+      <c r="T88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>48</v>
       </c>
@@ -5791,10 +6143,10 @@
         <v>10</v>
       </c>
       <c r="H89">
-        <v>1693.439576</v>
+        <v>1693.43957576093</v>
       </c>
       <c r="I89">
-        <v>3.3573875000000003E-2</v>
+        <v>3.3439708000514601E-2</v>
       </c>
       <c r="J89" s="1">
         <v>4371</v>
@@ -5803,10 +6155,10 @@
         <v>3</v>
       </c>
       <c r="L89">
-        <v>1848.80154283244</v>
+        <v>1848.80154283243</v>
       </c>
       <c r="M89">
-        <v>9.9895839998680007E-3</v>
+        <v>1.0029082999608301E-2</v>
       </c>
       <c r="N89" s="1">
         <v>400</v>
@@ -5820,13 +6172,17 @@
       <c r="Q89">
         <v>0.304965208999874</v>
       </c>
-      <c r="R89" s="1"/>
-      <c r="S89">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R89" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S89" s="1"/>
+      <c r="T89">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>48</v>
       </c>
@@ -5849,10 +6205,10 @@
         <v>10</v>
       </c>
       <c r="H90">
-        <v>3493.5262240000002</v>
+        <v>601.24608871710302</v>
       </c>
       <c r="I90">
-        <v>3.8219749999999997E-2</v>
+        <v>3.6575750000338303E-2</v>
       </c>
       <c r="J90" s="1">
         <v>284</v>
@@ -5864,7 +6220,7 @@
         <v>344.14980110208199</v>
       </c>
       <c r="M90">
-        <v>8.7100000018830003E-4</v>
+        <v>8.4733299991050001E-4</v>
       </c>
       <c r="N90" s="1">
         <v>400</v>
@@ -5878,13 +6234,17 @@
       <c r="Q90">
         <v>0.164598750000095</v>
       </c>
-      <c r="R90" s="1"/>
-      <c r="S90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R90" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S90" s="1"/>
+      <c r="T90">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>48</v>
       </c>
@@ -5907,10 +6267,10 @@
         <v>10</v>
       </c>
       <c r="H91">
-        <v>7675.3270039999998</v>
+        <v>7675.3270040017096</v>
       </c>
       <c r="I91">
-        <v>2.625108167</v>
+        <v>2.5470750000004001</v>
       </c>
       <c r="J91" s="1">
         <v>44306</v>
@@ -5919,10 +6279,10 @@
         <v>9</v>
       </c>
       <c r="L91">
-        <v>7675.3270039996796</v>
+        <v>7675.3270040017096</v>
       </c>
       <c r="M91">
-        <v>0.101928915999906</v>
+        <v>0.10297012499904599</v>
       </c>
       <c r="N91" s="1">
         <v>400</v>
@@ -5936,13 +6296,17 @@
       <c r="Q91">
         <v>2.79242370800011</v>
       </c>
-      <c r="R91" s="1"/>
-      <c r="S91">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R91" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S91" s="1"/>
+      <c r="T91">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>48</v>
       </c>
@@ -5965,10 +6329,10 @@
         <v>10</v>
       </c>
       <c r="H92">
-        <v>1270.4301210000001</v>
+        <v>144.17979866435201</v>
       </c>
       <c r="I92">
-        <v>2.541782167</v>
+        <v>2.5610721670000198</v>
       </c>
       <c r="J92" s="1">
         <v>1452</v>
@@ -5977,10 +6341,10 @@
         <v>0</v>
       </c>
       <c r="L92">
-        <v>43.292122264550002</v>
+        <v>43.292122264550699</v>
       </c>
       <c r="M92">
-        <v>4.4031249999534E-3</v>
+        <v>4.2252499988535003E-3</v>
       </c>
       <c r="N92" s="1">
         <v>400</v>
@@ -5994,13 +6358,17 @@
       <c r="Q92">
         <v>0.36309829099991398</v>
       </c>
-      <c r="R92" s="1"/>
-      <c r="S92">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R92" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S92" s="1"/>
+      <c r="T92">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>48</v>
       </c>
@@ -6023,10 +6391,10 @@
         <v>10</v>
       </c>
       <c r="H93">
-        <v>1922.403086</v>
+        <v>1922.4030860863099</v>
       </c>
       <c r="I93">
-        <v>7.1781165999999993E-2</v>
+        <v>7.3760666000453001E-2</v>
       </c>
       <c r="J93" s="1">
         <v>8341</v>
@@ -6038,7 +6406,7 @@
         <v>2140.5476767314999</v>
       </c>
       <c r="M93">
-        <v>1.8502665999676499E-2</v>
+        <v>1.8690457998672999E-2</v>
       </c>
       <c r="N93" s="1">
         <v>400</v>
@@ -6052,13 +6420,17 @@
       <c r="Q93">
         <v>0.343501833000118</v>
       </c>
-      <c r="R93" s="1"/>
-      <c r="S93">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R93" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S93" s="1"/>
+      <c r="T93">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>48</v>
       </c>
@@ -6081,10 +6453,10 @@
         <v>10</v>
       </c>
       <c r="H94">
-        <v>2605.0427880000002</v>
+        <v>676.33554143159995</v>
       </c>
       <c r="I94">
-        <v>4.5883124999999997E-2</v>
+        <v>4.6103167000183E-2</v>
       </c>
       <c r="J94" s="1">
         <v>306</v>
@@ -6093,10 +6465,10 @@
         <v>0</v>
       </c>
       <c r="L94">
-        <v>52.6639759855465</v>
+        <v>52.663975985546401</v>
       </c>
       <c r="M94">
-        <v>9.1204199998170003E-4</v>
+        <v>9.2208399837540001E-4</v>
       </c>
       <c r="N94" s="1">
         <v>400</v>
@@ -6110,13 +6482,17 @@
       <c r="Q94">
         <v>0.179851625000083</v>
       </c>
-      <c r="R94" s="1"/>
-      <c r="S94">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R94" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S94" s="1"/>
+      <c r="T94">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>48</v>
       </c>
@@ -6139,10 +6515,10 @@
         <v>10</v>
       </c>
       <c r="H95">
-        <v>1642.535337</v>
+        <v>1642.53533727271</v>
       </c>
       <c r="I95">
-        <v>1.7984291999999999E-2</v>
+        <v>1.7988915999012499E-2</v>
       </c>
       <c r="J95" s="1">
         <v>2636</v>
@@ -6154,7 +6530,7 @@
         <v>1716.9244751204401</v>
       </c>
       <c r="M95">
-        <v>6.1015000001133999E-3</v>
+        <v>6.0456669998529E-3</v>
       </c>
       <c r="N95" s="1">
         <v>400</v>
@@ -6168,13 +6544,17 @@
       <c r="Q95">
         <v>0.25130312500004898</v>
       </c>
-      <c r="R95" s="1"/>
-      <c r="S95">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R95" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S95" s="1"/>
+      <c r="T95">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>48</v>
       </c>
@@ -6197,10 +6577,10 @@
         <v>10</v>
       </c>
       <c r="H96">
-        <v>6166.3759630000004</v>
+        <v>1600.3477926399801</v>
       </c>
       <c r="I96">
-        <v>1.741875E-2</v>
+        <v>1.7575583999132501E-2</v>
       </c>
       <c r="J96" s="1">
         <v>230</v>
@@ -6212,7 +6592,7 @@
         <v>228.198733552666</v>
       </c>
       <c r="M96">
-        <v>6.9312499999789996E-4</v>
+        <v>6.9699999949069996E-4</v>
       </c>
       <c r="N96" s="1">
         <v>400</v>
@@ -6226,13 +6606,17 @@
       <c r="Q96">
         <v>0.105672666999907</v>
       </c>
-      <c r="R96" s="1"/>
-      <c r="S96">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R96" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S96" s="1"/>
+      <c r="T96">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>48</v>
       </c>
@@ -6255,10 +6639,10 @@
         <v>10</v>
       </c>
       <c r="H97">
-        <v>517.32380030000002</v>
+        <v>517.32380025205202</v>
       </c>
       <c r="I97">
-        <v>1.5006042000000001E-2</v>
+        <v>1.5243874999214301E-2</v>
       </c>
       <c r="J97" s="1">
         <v>1940</v>
@@ -6267,10 +6651,10 @@
         <v>4</v>
       </c>
       <c r="L97">
-        <v>611.77363789901301</v>
+        <v>611.77363789921003</v>
       </c>
       <c r="M97">
-        <v>4.4660419998763003E-3</v>
+        <v>4.4632089993682997E-3</v>
       </c>
       <c r="N97" s="1">
         <v>400</v>
@@ -6284,13 +6668,17 @@
       <c r="Q97">
         <v>0.233867207999992</v>
       </c>
-      <c r="R97" s="1"/>
-      <c r="S97">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R97" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S97" s="1"/>
+      <c r="T97">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>48</v>
       </c>
@@ -6313,10 +6701,10 @@
         <v>10</v>
       </c>
       <c r="H98">
-        <v>82.069483230000003</v>
+        <v>21.9758937463675</v>
       </c>
       <c r="I98">
-        <v>1.3274833999999999E-2</v>
+        <v>1.3504500000635701E-2</v>
       </c>
       <c r="J98" s="1">
         <v>214</v>
@@ -6325,10 +6713,10 @@
         <v>1</v>
       </c>
       <c r="L98">
-        <v>7.3441115753497703</v>
+        <v>7.3441115753513699</v>
       </c>
       <c r="M98">
-        <v>6.7924999984820004E-4</v>
+        <v>6.5629200071270002E-4</v>
       </c>
       <c r="N98" s="1">
         <v>400</v>
@@ -6342,13 +6730,17 @@
       <c r="Q98">
         <v>5.5338334000225503E-2</v>
       </c>
-      <c r="R98" s="1"/>
-      <c r="S98">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R98" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S98" s="1"/>
+      <c r="T98">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>48</v>
       </c>
@@ -6371,10 +6763,10 @@
         <v>10</v>
       </c>
       <c r="H99">
-        <v>275.7716428</v>
+        <v>275.77164276639797</v>
       </c>
       <c r="I99">
-        <v>1.8690374999999999E-2</v>
+        <v>1.90152089999173E-2</v>
       </c>
       <c r="J99" s="1">
         <v>1929</v>
@@ -6383,10 +6775,10 @@
         <v>8</v>
       </c>
       <c r="L99">
-        <v>286.71840156412497</v>
+        <v>286.71840157676098</v>
       </c>
       <c r="M99">
-        <v>4.5039169999653997E-3</v>
+        <v>4.5352090000959997E-3</v>
       </c>
       <c r="N99" s="1">
         <v>400</v>
@@ -6400,13 +6792,17 @@
       <c r="Q99">
         <v>0.218287000000145</v>
       </c>
-      <c r="R99" s="1"/>
-      <c r="S99">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R99" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S99" s="1"/>
+      <c r="T99">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>48</v>
       </c>
@@ -6429,10 +6825,10 @@
         <v>10</v>
       </c>
       <c r="H100">
-        <v>24.235058160000001</v>
+        <v>6.3210067981650502</v>
       </c>
       <c r="I100">
-        <v>1.7334624999999999E-2</v>
+        <v>1.7674709000857498E-2</v>
       </c>
       <c r="J100" s="1">
         <v>262</v>
@@ -6441,10 +6837,10 @@
         <v>5</v>
       </c>
       <c r="L100">
-        <v>5.6075204928964997</v>
+        <v>5.6075204929450102</v>
       </c>
       <c r="M100">
-        <v>8.0091700010590005E-4</v>
+        <v>7.9166600153250004E-4</v>
       </c>
       <c r="N100" s="1">
         <v>400</v>
@@ -6458,13 +6854,17 @@
       <c r="Q100">
         <v>0.104198167000049</v>
       </c>
-      <c r="R100" s="1"/>
-      <c r="S100">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R100" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S100" s="1"/>
+      <c r="T100">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>48</v>
       </c>
@@ -6487,10 +6887,10 @@
         <v>10</v>
       </c>
       <c r="H101">
-        <v>7621.7787989999997</v>
+        <v>7621.7787993363199</v>
       </c>
       <c r="I101">
-        <v>3.7652732919999998</v>
+        <v>3.8025400839997001</v>
       </c>
       <c r="J101" s="1">
         <v>22877</v>
@@ -6499,10 +6899,10 @@
         <v>34</v>
       </c>
       <c r="L101">
-        <v>5666.6210357091104</v>
+        <v>5666.6210366209798</v>
       </c>
       <c r="M101">
-        <v>5.8308624999881403E-2</v>
+        <v>5.83667080009036E-2</v>
       </c>
       <c r="N101" s="1">
         <v>400</v>
@@ -6516,13 +6916,17 @@
       <c r="Q101">
         <v>3.3223813749996198</v>
       </c>
-      <c r="R101" s="1"/>
-      <c r="S101">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R101" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S101" s="1"/>
+      <c r="T101">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>48</v>
       </c>
@@ -6545,10 +6949,10 @@
         <v>10</v>
       </c>
       <c r="H102">
-        <v>869.17090299999995</v>
+        <v>68.391035456461196</v>
       </c>
       <c r="I102">
-        <v>3.9414505000000002</v>
+        <v>3.9219677500004702</v>
       </c>
       <c r="J102" s="1">
         <v>1718</v>
@@ -6557,10 +6961,10 @@
         <v>26</v>
       </c>
       <c r="L102">
-        <v>188.30204144529699</v>
+        <v>188.30204150458701</v>
       </c>
       <c r="M102">
-        <v>5.4500419996657001E-3</v>
+        <v>5.4688330001226E-3</v>
       </c>
       <c r="N102" s="1">
         <v>400</v>
@@ -6574,13 +6978,17 @@
       <c r="Q102">
         <v>1.44918491699991</v>
       </c>
-      <c r="R102" s="1"/>
-      <c r="S102">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R102" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S102" s="1"/>
+      <c r="T102">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>48</v>
       </c>
@@ -6603,10 +7011,10 @@
         <v>10</v>
       </c>
       <c r="H103">
-        <v>1334.0476180000001</v>
+        <v>1334.0476184132399</v>
       </c>
       <c r="I103">
-        <v>8.3857500000000008E-3</v>
+        <v>8.6948329990263994E-3</v>
       </c>
       <c r="J103" s="1">
         <v>2882</v>
@@ -6618,7 +7026,7 @@
         <v>1496.2857787288799</v>
       </c>
       <c r="M103">
-        <v>6.5296660000058E-3</v>
+        <v>6.4778329997352002E-3</v>
       </c>
       <c r="N103" s="1">
         <v>400</v>
@@ -6632,13 +7040,17 @@
       <c r="Q103">
         <v>0.16401224999981401</v>
       </c>
-      <c r="R103" s="1"/>
-      <c r="S103">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R103" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S103" s="1"/>
+      <c r="T103">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>48</v>
       </c>
@@ -6661,10 +7073,10 @@
         <v>10</v>
       </c>
       <c r="H104">
-        <v>4401.8303100000003</v>
+        <v>1266.58576081827</v>
       </c>
       <c r="I104">
-        <v>8.9891659999999998E-3</v>
+        <v>9.2424579997896009E-3</v>
       </c>
       <c r="J104" s="1">
         <v>196</v>
@@ -6676,7 +7088,7 @@
         <v>181.44301899822199</v>
       </c>
       <c r="M104">
-        <v>6.017910000082E-4</v>
+        <v>6.0170799952170004E-4</v>
       </c>
       <c r="N104" s="1">
         <v>400</v>
@@ -6690,13 +7102,17 @@
       <c r="Q104">
         <v>4.9911916999917497E-2</v>
       </c>
-      <c r="R104" s="1"/>
-      <c r="S104">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R104" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S104" s="1"/>
+      <c r="T104">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>48</v>
       </c>
@@ -6719,10 +7135,10 @@
         <v>10</v>
       </c>
       <c r="H105">
-        <v>1074.390909</v>
+        <v>1074.39090906209</v>
       </c>
       <c r="I105">
-        <v>7.4187910000000001E-3</v>
+        <v>7.3594999994384003E-3</v>
       </c>
       <c r="J105" s="1">
         <v>2480</v>
@@ -6731,10 +7147,10 @@
         <v>2</v>
       </c>
       <c r="L105">
-        <v>1158.33857010323</v>
+        <v>1158.33857010322</v>
       </c>
       <c r="M105">
-        <v>5.4337090000444004E-3</v>
+        <v>5.5822920003265001E-3</v>
       </c>
       <c r="N105" s="1">
         <v>400</v>
@@ -6748,13 +7164,17 @@
       <c r="Q105">
         <v>0.157255207999696</v>
       </c>
-      <c r="R105" s="1"/>
-      <c r="S105">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R105" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S105" s="1"/>
+      <c r="T105">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>48</v>
       </c>
@@ -6777,10 +7197,10 @@
         <v>10</v>
       </c>
       <c r="H106">
-        <v>1312.958572</v>
+        <v>370.95796179889498</v>
       </c>
       <c r="I106">
-        <v>7.74575E-3</v>
+        <v>7.8649580009367993E-3</v>
       </c>
       <c r="J106" s="1">
         <v>190</v>
@@ -6789,10 +7209,10 @@
         <v>0</v>
       </c>
       <c r="L106">
-        <v>39.913512995688002</v>
+        <v>39.913512995688102</v>
       </c>
       <c r="M106">
-        <v>5.8433300000609997E-4</v>
+        <v>6.2350000007420001E-4</v>
       </c>
       <c r="N106" s="1">
         <v>400</v>
@@ -6806,13 +7226,17 @@
       <c r="Q106">
         <v>4.9229124999783297E-2</v>
       </c>
-      <c r="R106" s="1"/>
-      <c r="S106">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R106" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S106" s="1"/>
+      <c r="T106">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>48</v>
       </c>
@@ -6835,10 +7259,10 @@
         <v>10</v>
       </c>
       <c r="H107">
-        <v>1415.224307</v>
+        <v>1415.2243072554099</v>
       </c>
       <c r="I107">
-        <v>7.2781249999999999E-3</v>
+        <v>7.3283330002595001E-3</v>
       </c>
       <c r="J107" s="1">
         <v>2743</v>
@@ -6850,7 +7274,7 @@
         <v>1526.8630593258899</v>
       </c>
       <c r="M107">
-        <v>6.1562920000142003E-3</v>
+        <v>6.3494590012850996E-3</v>
       </c>
       <c r="N107" s="1">
         <v>400</v>
@@ -6864,13 +7288,17 @@
       <c r="Q107">
         <v>0.17317312499972101</v>
       </c>
-      <c r="R107" s="1"/>
-      <c r="S107">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R107" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S107" s="1"/>
+      <c r="T107">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>48</v>
       </c>
@@ -6893,10 +7321,10 @@
         <v>10</v>
       </c>
       <c r="H108">
-        <v>7350.1171029999996</v>
+        <v>2216.8803313418798</v>
       </c>
       <c r="I108">
-        <v>7.7514589999999996E-3</v>
+        <v>7.8615410002384999E-3</v>
       </c>
       <c r="J108" s="1">
         <v>190</v>
@@ -6908,7 +7336,7 @@
         <v>246.87412328324501</v>
       </c>
       <c r="M108">
-        <v>5.8583400004860004E-4</v>
+        <v>5.7733399989949997E-4</v>
       </c>
       <c r="N108" s="1">
         <v>400</v>
@@ -6922,13 +7350,17 @@
       <c r="Q108">
         <v>8.8207582999984796E-2</v>
       </c>
-      <c r="R108" s="1"/>
-      <c r="S108">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R108" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S108" s="1"/>
+      <c r="T108">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>48</v>
       </c>
@@ -6951,10 +7383,10 @@
         <v>10</v>
       </c>
       <c r="H109">
-        <v>774.64378810000005</v>
+        <v>774.64378807948503</v>
       </c>
       <c r="I109">
-        <v>7.2939579999999997E-3</v>
+        <v>7.3723330006031998E-3</v>
       </c>
       <c r="J109" s="1">
         <v>2240</v>
@@ -6963,10 +7395,10 @@
         <v>4</v>
       </c>
       <c r="L109">
-        <v>841.78181360818303</v>
+        <v>841.78181360803296</v>
       </c>
       <c r="M109">
-        <v>5.056500000137E-3</v>
+        <v>5.1075829996989003E-3</v>
       </c>
       <c r="N109" s="1">
         <v>400</v>
@@ -6980,13 +7412,17 @@
       <c r="Q109">
         <v>0.17343179099998399</v>
       </c>
-      <c r="R109" s="1"/>
-      <c r="S109">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R109" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S109" s="1"/>
+      <c r="T109">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>48</v>
       </c>
@@ -7009,10 +7445,10 @@
         <v>10</v>
       </c>
       <c r="H110">
-        <v>347.00019930000002</v>
+        <v>100.041473366574</v>
       </c>
       <c r="I110">
-        <v>7.8049169999999998E-3</v>
+        <v>7.9517920003127004E-3</v>
       </c>
       <c r="J110" s="1">
         <v>190</v>
@@ -7021,10 +7457,10 @@
         <v>2</v>
       </c>
       <c r="L110">
-        <v>47.035346974327702</v>
+        <v>47.035346974325599</v>
       </c>
       <c r="M110">
-        <v>5.9254200004939998E-4</v>
+        <v>6.0233299882379995E-4</v>
       </c>
       <c r="N110" s="1">
         <v>400</v>
@@ -7038,13 +7474,17 @@
       <c r="Q110">
         <v>4.8555583000052097E-2</v>
       </c>
-      <c r="R110" s="1"/>
-      <c r="S110">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R110" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S110" s="1"/>
+      <c r="T110">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>48</v>
       </c>
@@ -7067,10 +7507,10 @@
         <v>10</v>
       </c>
       <c r="H111">
-        <v>7671.1611359999997</v>
+        <v>7671.1611359237604</v>
       </c>
       <c r="I111">
-        <v>2.4715584590000002</v>
+        <v>2.4850994580010499</v>
       </c>
       <c r="J111" s="1">
         <v>44319</v>
@@ -7079,10 +7519,10 @@
         <v>8</v>
       </c>
       <c r="L111">
-        <v>7705.1575888203597</v>
+        <v>7705.1575888161797</v>
       </c>
       <c r="M111">
-        <v>0.100736708000113</v>
+        <v>0.101176124999255</v>
       </c>
       <c r="N111" s="1">
         <v>400</v>
@@ -7096,13 +7536,17 @@
       <c r="Q111">
         <v>2.6376498750000699</v>
       </c>
-      <c r="R111" s="1"/>
-      <c r="S111">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R111" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S111" s="1"/>
+      <c r="T111">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>48</v>
       </c>
@@ -7125,10 +7569,10 @@
         <v>10</v>
       </c>
       <c r="H112">
-        <v>1199.6087210000001</v>
+        <v>167.17021201364599</v>
       </c>
       <c r="I112">
-        <v>2.5977135840000001</v>
+        <v>2.6352581249993801</v>
       </c>
       <c r="J112" s="1">
         <v>1452</v>
@@ -7137,10 +7581,10 @@
         <v>0</v>
       </c>
       <c r="L112">
-        <v>35.111863265897099</v>
+        <v>35.111863265892701</v>
       </c>
       <c r="M112">
-        <v>4.2780829999172999E-3</v>
+        <v>4.3562920000113003E-3</v>
       </c>
       <c r="N112" s="1">
         <v>400</v>
@@ -7154,13 +7598,17 @@
       <c r="Q112">
         <v>0.36071208400016902</v>
       </c>
-      <c r="R112" s="1"/>
-      <c r="S112">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R112" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S112" s="1"/>
+      <c r="T112">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>48</v>
       </c>
@@ -7183,10 +7631,10 @@
         <v>10</v>
       </c>
       <c r="H113">
-        <v>1476.2756119999999</v>
+        <v>1476.27561241121</v>
       </c>
       <c r="I113">
-        <v>5.6217166999999998E-2</v>
+        <v>5.6542667000030598E-2</v>
       </c>
       <c r="J113" s="1">
         <v>5402</v>
@@ -7195,10 +7643,10 @@
         <v>6</v>
       </c>
       <c r="L113">
-        <v>1553.7848638046401</v>
+        <v>1553.7848638042999</v>
       </c>
       <c r="M113">
-        <v>1.5856291000091002E-2</v>
+        <v>1.25853329991514E-2</v>
       </c>
       <c r="N113" s="1">
         <v>400</v>
@@ -7212,13 +7660,17 @@
       <c r="Q113">
         <v>0.41035629200041501</v>
       </c>
-      <c r="R113" s="1"/>
-      <c r="S113">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R113" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S113" s="1"/>
+      <c r="T113">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>48</v>
       </c>
@@ -7241,10 +7693,10 @@
         <v>10</v>
       </c>
       <c r="H114">
-        <v>511.0910088</v>
+        <v>115.245823407811</v>
       </c>
       <c r="I114">
-        <v>6.0552165999999998E-2</v>
+        <v>6.1424458001056302E-2</v>
       </c>
       <c r="J114" s="1">
         <v>338</v>
@@ -7253,10 +7705,10 @@
         <v>0</v>
       </c>
       <c r="L114">
-        <v>14.466011216986301</v>
+        <v>14.4660112169864</v>
       </c>
       <c r="M114">
-        <v>1.0029999998550001E-3</v>
+        <v>1.0060839995276001E-3</v>
       </c>
       <c r="N114" s="1">
         <v>400</v>
@@ -7270,13 +7722,17 @@
       <c r="Q114">
         <v>8.3525084000029795E-2</v>
       </c>
-      <c r="R114" s="1"/>
-      <c r="S114">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R114" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S114" s="1"/>
+      <c r="T114">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>48</v>
       </c>
@@ -7299,10 +7755,10 @@
         <v>10</v>
       </c>
       <c r="H115">
-        <v>1553.176033</v>
+        <v>1553.17603289257</v>
       </c>
       <c r="I115">
-        <v>5.4262334000000002E-2</v>
+        <v>5.4170375000467098E-2</v>
       </c>
       <c r="J115" s="1">
         <v>6475</v>
@@ -7314,7 +7770,7 @@
         <v>1676.8045600518401</v>
       </c>
       <c r="M115">
-        <v>1.4901458999702299E-2</v>
+        <v>1.4806999999564099E-2</v>
       </c>
       <c r="N115" s="1">
         <v>400</v>
@@ -7328,13 +7784,17 @@
       <c r="Q115">
         <v>0.376424208000116</v>
       </c>
-      <c r="R115" s="1"/>
-      <c r="S115">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R115">
+        <f t="shared" si="3"/>
+        <v>1.1107871589532442E-2</v>
+      </c>
+      <c r="S115" s="1"/>
+      <c r="T115">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>48</v>
       </c>
@@ -7357,10 +7817,10 @@
         <v>10</v>
       </c>
       <c r="H116">
-        <v>668.27540290000002</v>
+        <v>128.786431472667</v>
       </c>
       <c r="I116">
-        <v>5.6370249999999997E-2</v>
+        <v>5.73184160002711E-2</v>
       </c>
       <c r="J116" s="1">
         <v>332</v>
@@ -7369,10 +7829,10 @@
         <v>0</v>
       </c>
       <c r="L116">
-        <v>27.463453212112601</v>
+        <v>27.463453212112501</v>
       </c>
       <c r="M116">
-        <v>9.9649999992829997E-4</v>
+        <v>9.9341699933569992E-4</v>
       </c>
       <c r="N116" s="1">
         <v>400</v>
@@ -7386,13 +7846,17 @@
       <c r="Q116">
         <v>8.4417250000115004E-2</v>
       </c>
-      <c r="R116" s="1"/>
-      <c r="S116">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R116" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S116" s="1"/>
+      <c r="T116">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>48</v>
       </c>
@@ -7415,10 +7879,10 @@
         <v>10</v>
       </c>
       <c r="H117">
-        <v>989.08860589999995</v>
+        <v>989.08860591427504</v>
       </c>
       <c r="I117">
-        <v>1.5871208000000001E-2</v>
+        <v>1.56105000005482E-2</v>
       </c>
       <c r="J117" s="1">
         <v>4256</v>
@@ -7427,10 +7891,10 @@
         <v>3</v>
       </c>
       <c r="L117">
-        <v>1073.5211729928401</v>
+        <v>1073.5211729928601</v>
       </c>
       <c r="M117">
-        <v>9.7840840003300001E-3</v>
+        <v>9.6866250005405007E-3</v>
       </c>
       <c r="N117" s="1">
         <v>400</v>
@@ -7444,13 +7908,17 @@
       <c r="Q117">
         <v>0.28683883299981899</v>
       </c>
-      <c r="R117" s="1"/>
-      <c r="S117">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R117" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S117" s="1"/>
+      <c r="T117">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>48</v>
       </c>
@@ -7473,10 +7941,10 @@
         <v>10</v>
       </c>
       <c r="H118">
-        <v>528.69465790000004</v>
+        <v>142.29827236113701</v>
       </c>
       <c r="I118">
-        <v>1.5140125000000001E-2</v>
+        <v>1.53073330002371E-2</v>
       </c>
       <c r="J118" s="1">
         <v>222</v>
@@ -7485,10 +7953,10 @@
         <v>2</v>
       </c>
       <c r="L118">
-        <v>22.332284112649202</v>
+        <v>22.332284112650999</v>
       </c>
       <c r="M118">
-        <v>7.2858299972719997E-4</v>
+        <v>6.9558300128839999E-4</v>
       </c>
       <c r="N118" s="1">
         <v>400</v>
@@ -7502,13 +7970,17 @@
       <c r="Q118">
         <v>0.109649208000064</v>
       </c>
-      <c r="R118" s="1"/>
-      <c r="S118">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R118" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S118" s="1"/>
+      <c r="T118">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>48</v>
       </c>
@@ -7531,10 +8003,10 @@
         <v>10</v>
       </c>
       <c r="H119">
-        <v>512.30950919999998</v>
+        <v>512.30950924021204</v>
       </c>
       <c r="I119">
-        <v>1.6861167E-2</v>
+        <v>1.6786041998784602E-2</v>
       </c>
       <c r="J119" s="1">
         <v>2549</v>
@@ -7543,10 +8015,10 @@
         <v>6</v>
       </c>
       <c r="L119">
-        <v>599.15468542427095</v>
+        <v>599.15468542375697</v>
       </c>
       <c r="M119">
-        <v>5.8194999996885001E-3</v>
+        <v>5.8954169999195999E-3</v>
       </c>
       <c r="N119" s="1">
         <v>400</v>
@@ -7560,13 +8032,17 @@
       <c r="Q119">
         <v>0.20702670799983</v>
       </c>
-      <c r="R119" s="1"/>
-      <c r="S119">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R119">
+        <f t="shared" si="3"/>
+        <v>0.11884022015918522</v>
+      </c>
+      <c r="S119" s="1"/>
+      <c r="T119">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>48</v>
       </c>
@@ -7589,10 +8065,10 @@
         <v>10</v>
       </c>
       <c r="H120">
-        <v>91.653270800000001</v>
+        <v>22.499136017949802</v>
       </c>
       <c r="I120">
-        <v>1.5140083E-2</v>
+        <v>1.52427920002082E-2</v>
       </c>
       <c r="J120" s="1">
         <v>231</v>
@@ -7601,10 +8077,10 @@
         <v>8</v>
       </c>
       <c r="L120">
-        <v>25.418307739129201</v>
+        <v>25.418307739140499</v>
       </c>
       <c r="M120">
-        <v>7.1637499968339995E-4</v>
+        <v>7.4354100070190003E-4</v>
       </c>
       <c r="N120" s="1">
         <v>400</v>
@@ -7618,13 +8094,17 @@
       <c r="Q120">
         <v>5.7954207999955501E-2</v>
       </c>
-      <c r="R120" s="1"/>
-      <c r="S120">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R120" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S120" s="1"/>
+      <c r="T120">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>48</v>
       </c>
@@ -7647,10 +8127,10 @@
         <v>10</v>
       </c>
       <c r="H121">
-        <v>5609.7369339999996</v>
+        <v>5609.7369338859198</v>
       </c>
       <c r="I121">
-        <v>2.216167209</v>
+        <v>2.2448151669996101</v>
       </c>
       <c r="J121" s="1">
         <v>18293</v>
@@ -7659,10 +8139,10 @@
         <v>27</v>
       </c>
       <c r="L121">
-        <v>4685.8555701530604</v>
+        <v>4685.8555701611704</v>
       </c>
       <c r="M121">
-        <v>4.4188291999944299E-2</v>
+        <v>4.4345540998619898E-2</v>
       </c>
       <c r="N121" s="1">
         <v>400</v>
@@ -7676,13 +8156,17 @@
       <c r="Q121">
         <v>2.4590465410001299</v>
       </c>
-      <c r="R121" s="1"/>
-      <c r="S121">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R121" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S121" s="1"/>
+      <c r="T121">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>48</v>
       </c>
@@ -7705,10 +8189,10 @@
         <v>10</v>
       </c>
       <c r="H122">
-        <v>544.00896569999998</v>
+        <v>57.455558031181397</v>
       </c>
       <c r="I122">
-        <v>2.3190533329999998</v>
+        <v>2.32647041699965</v>
       </c>
       <c r="J122" s="1">
         <v>1381</v>
@@ -7717,10 +8201,10 @@
         <v>10</v>
       </c>
       <c r="L122">
-        <v>70.301732663673903</v>
+        <v>70.301732663863604</v>
       </c>
       <c r="M122">
-        <v>4.4069579998904001E-3</v>
+        <v>4.3157090003659998E-3</v>
       </c>
       <c r="N122" s="1">
         <v>400</v>
@@ -7734,13 +8218,17 @@
       <c r="Q122">
         <v>1.1796033339996901</v>
       </c>
-      <c r="R122" s="1"/>
-      <c r="S122">
-        <f t="shared" si="1"/>
+      <c r="R122" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S122" s="1"/>
+      <c r="T122">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>85</v>
       </c>
@@ -7763,10 +8251,10 @@
         <v>10</v>
       </c>
       <c r="H123">
-        <v>237.495992</v>
+        <v>237.49599195056999</v>
       </c>
       <c r="I123">
-        <v>0.16787804100000001</v>
+        <v>0.17698612499953001</v>
       </c>
       <c r="J123" s="1">
         <v>9120</v>
@@ -7775,10 +8263,10 @@
         <v>6</v>
       </c>
       <c r="L123">
-        <v>341.68928982698498</v>
+        <v>341.68928982818898</v>
       </c>
       <c r="M123">
-        <v>2.1882000000005002E-2</v>
+        <v>2.04869579993101E-2</v>
       </c>
       <c r="N123" s="1">
         <v>400</v>
@@ -7792,13 +8280,17 @@
       <c r="Q123">
         <v>0.65202587499970799</v>
       </c>
-      <c r="R123" s="1"/>
-      <c r="S123">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R123" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S123" s="1"/>
+      <c r="T123">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>85</v>
       </c>
@@ -7821,10 +8313,10 @@
         <v>10</v>
       </c>
       <c r="H124">
-        <v>13.702467690000001</v>
+        <v>2.6444225106603598</v>
       </c>
       <c r="I124">
-        <v>0.15436045800000001</v>
+        <v>0.15549454200117899</v>
       </c>
       <c r="J124" s="1">
         <v>484</v>
@@ -7833,10 +8325,10 @@
         <v>0</v>
       </c>
       <c r="L124">
-        <v>0.51316327665538497</v>
+        <v>0.51316327665553096</v>
       </c>
       <c r="M124">
-        <v>1.4095410001573E-3</v>
+        <v>1.3788329997623E-3</v>
       </c>
       <c r="N124" s="1">
         <v>400</v>
@@ -7850,13 +8342,17 @@
       <c r="Q124">
         <v>0.122825334000026</v>
       </c>
-      <c r="R124" s="1"/>
-      <c r="S124">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R124" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S124" s="1"/>
+      <c r="T124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>85</v>
       </c>
@@ -7879,10 +8375,10 @@
         <v>10</v>
       </c>
       <c r="H125">
-        <v>509.4885711</v>
+        <v>509.48857112803501</v>
       </c>
       <c r="I125">
-        <v>0.19206483299999999</v>
+        <v>0.19948004199977701</v>
       </c>
       <c r="J125" s="1">
         <v>9470</v>
@@ -7891,10 +8387,10 @@
         <v>7</v>
       </c>
       <c r="L125">
-        <v>573.133585572539</v>
+        <v>573.13358557472395</v>
       </c>
       <c r="M125">
-        <v>2.13952919998519E-2</v>
+        <v>2.15393329999642E-2</v>
       </c>
       <c r="N125" s="1">
         <v>400</v>
@@ -7908,13 +8404,17 @@
       <c r="Q125">
         <v>0.75518312500025697</v>
       </c>
-      <c r="R125" s="1"/>
-      <c r="S125">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R125" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S125" s="1"/>
+      <c r="T125">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>85</v>
       </c>
@@ -7937,10 +8437,10 @@
         <v>10</v>
       </c>
       <c r="H126">
-        <v>19.52475102</v>
+        <v>4.03804049163492</v>
       </c>
       <c r="I126">
-        <v>0.17541220799999999</v>
+        <v>0.179928333000134</v>
       </c>
       <c r="J126" s="1">
         <v>508</v>
@@ -7949,10 +8449,10 @@
         <v>0</v>
       </c>
       <c r="L126">
-        <v>0.55770480110249698</v>
+        <v>0.55770480110248</v>
       </c>
       <c r="M126">
-        <v>1.4461249998021001E-3</v>
+        <v>1.4672079996671001E-3</v>
       </c>
       <c r="N126" s="1">
         <v>400</v>
@@ -7966,13 +8466,17 @@
       <c r="Q126">
         <v>0.12633383299998899</v>
       </c>
-      <c r="R126" s="1"/>
-      <c r="S126">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R126" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S126" s="1"/>
+      <c r="T126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>85</v>
       </c>
@@ -7995,10 +8499,10 @@
         <v>10</v>
       </c>
       <c r="H127">
-        <v>-718.84661719999997</v>
+        <v>-718.84661716963603</v>
       </c>
       <c r="I127">
-        <v>0.171678417</v>
+        <v>0.17840450000039701</v>
       </c>
       <c r="J127" s="1">
         <v>6436</v>
@@ -8007,10 +8511,10 @@
         <v>6</v>
       </c>
       <c r="L127">
-        <v>-651.70088755677602</v>
+        <v>-651.70088755723998</v>
       </c>
       <c r="M127">
-        <v>1.47702499998558E-2</v>
+        <v>1.8090666999341899E-2</v>
       </c>
       <c r="N127" s="1">
         <v>400</v>
@@ -8024,13 +8528,17 @@
       <c r="Q127">
         <v>0.630409290999978</v>
       </c>
-      <c r="R127" s="1"/>
-      <c r="S127">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R127" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S127" s="1"/>
+      <c r="T127">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>85</v>
       </c>
@@ -8053,10 +8561,10 @@
         <v>10</v>
       </c>
       <c r="H128">
-        <v>1.8027588290000001</v>
+        <v>0.36288176229595598</v>
       </c>
       <c r="I128">
-        <v>0.155208542</v>
+        <v>0.15874199999961999</v>
       </c>
       <c r="J128" s="1">
         <v>484</v>
@@ -8065,10 +8573,10 @@
         <v>0</v>
       </c>
       <c r="L128">
-        <v>8.7045744624383706E-2</v>
+        <v>8.7045744624384996E-2</v>
       </c>
       <c r="M128">
-        <v>1.4102499999353001E-3</v>
+        <v>1.3988749997224E-3</v>
       </c>
       <c r="N128" s="1">
         <v>400</v>
@@ -8082,13 +8590,17 @@
       <c r="Q128">
         <v>0.120075874999656</v>
       </c>
-      <c r="R128" s="1"/>
-      <c r="S128">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R128" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S128" s="1"/>
+      <c r="T128">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>85</v>
       </c>
@@ -8111,10 +8623,10 @@
         <v>10</v>
       </c>
       <c r="H129">
-        <v>-554.27495569999996</v>
+        <v>-554.27495568354902</v>
       </c>
       <c r="I129">
-        <v>0.17336829200000001</v>
+        <v>0.17979979099982299</v>
       </c>
       <c r="J129" s="1">
         <v>8079</v>
@@ -8123,10 +8635,10 @@
         <v>5</v>
       </c>
       <c r="L129">
-        <v>-417.955732940291</v>
+        <v>-417.95573293753</v>
       </c>
       <c r="M129">
-        <v>1.8519291999837099E-2</v>
+        <v>1.8318124999495901E-2</v>
       </c>
       <c r="N129" s="1">
         <v>400</v>
@@ -8140,13 +8652,17 @@
       <c r="Q129">
         <v>0.60547320800014803</v>
       </c>
-      <c r="R129" s="1"/>
-      <c r="S129">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R129" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S129" s="1"/>
+      <c r="T129">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>85</v>
       </c>
@@ -8169,10 +8685,10 @@
         <v>10</v>
       </c>
       <c r="H130">
-        <v>2.4611752070000001</v>
+        <v>0.48962739096646901</v>
       </c>
       <c r="I130">
-        <v>0.15435416699999999</v>
+        <v>0.15651754099963</v>
       </c>
       <c r="J130" s="1">
         <v>484</v>
@@ -8181,10 +8697,10 @@
         <v>0</v>
       </c>
       <c r="L130">
-        <v>9.9297726530855696E-2</v>
+        <v>9.9297726530906405E-2</v>
       </c>
       <c r="M130">
-        <v>1.4105830000516999E-3</v>
+        <v>1.3861669995094E-3</v>
       </c>
       <c r="N130" s="1">
         <v>400</v>
@@ -8198,13 +8714,17 @@
       <c r="Q130">
         <v>0.124272667000241</v>
       </c>
-      <c r="R130" s="1"/>
-      <c r="S130">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R130" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S130" s="1"/>
+      <c r="T130">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>85</v>
       </c>
@@ -8227,10 +8747,10 @@
         <v>10</v>
       </c>
       <c r="H131">
-        <v>-426.1731714</v>
+        <v>-426.17317138350597</v>
       </c>
       <c r="I131">
-        <v>0.17652116700000001</v>
+        <v>0.174524416999702</v>
       </c>
       <c r="J131" s="1">
         <v>11039</v>
@@ -8239,10 +8759,10 @@
         <v>4</v>
       </c>
       <c r="L131">
-        <v>-271.06305628880699</v>
+        <v>-271.06305628852903</v>
       </c>
       <c r="M131">
-        <v>2.5113290999797699E-2</v>
+        <v>2.45851250001578E-2</v>
       </c>
       <c r="N131" s="1">
         <v>400</v>
@@ -8256,13 +8776,17 @@
       <c r="Q131">
         <v>0.65139420800005599</v>
       </c>
-      <c r="R131" s="1"/>
-      <c r="S131">
-        <f t="shared" ref="S131:S142" si="2">IF(G131=K131,1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R131" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S131" s="1"/>
+      <c r="T131">
+        <f t="shared" ref="T131:T142" si="4">IF(G131=K131,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>85</v>
       </c>
@@ -8285,10 +8809,10 @@
         <v>10</v>
       </c>
       <c r="H132">
-        <v>3.1774969670000002</v>
+        <v>0.71463241557530399</v>
       </c>
       <c r="I132">
-        <v>0.15444487500000001</v>
+        <v>0.15579900000011501</v>
       </c>
       <c r="J132" s="1">
         <v>484</v>
@@ -8297,10 +8821,10 @@
         <v>0</v>
       </c>
       <c r="L132">
-        <v>8.67449942990592E-2</v>
+        <v>8.6744994299066E-2</v>
       </c>
       <c r="M132">
-        <v>1.4051250000193E-3</v>
+        <v>1.3917080013925E-3</v>
       </c>
       <c r="N132" s="1">
         <v>400</v>
@@ -8314,13 +8838,17 @@
       <c r="Q132">
         <v>0.120990667000114</v>
       </c>
-      <c r="R132" s="1"/>
-      <c r="S132">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R132" t="e">
+        <f t="shared" ref="R132:R142" si="5">IF(O132=G132,(P132-H132)/H132,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="S132" s="1"/>
+      <c r="T132">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>85</v>
       </c>
@@ -8343,10 +8871,10 @@
         <v>10</v>
       </c>
       <c r="H133">
-        <v>-411.60512030000001</v>
+        <v>-411.60512030099397</v>
       </c>
       <c r="I133">
-        <v>0.164423708</v>
+        <v>0.16562833299940299</v>
       </c>
       <c r="J133" s="1">
         <v>8620</v>
@@ -8355,10 +8883,10 @@
         <v>7</v>
       </c>
       <c r="L133">
-        <v>-345.29886121925102</v>
+        <v>-345.298861218497</v>
       </c>
       <c r="M133">
-        <v>1.9615957999576401E-2</v>
+        <v>1.9361624999874E-2</v>
       </c>
       <c r="N133" s="1">
         <v>400</v>
@@ -8372,13 +8900,17 @@
       <c r="Q133">
         <v>0.72859187499989198</v>
       </c>
-      <c r="R133" s="1"/>
-      <c r="S133">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R133" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S133" s="1"/>
+      <c r="T133">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>85</v>
       </c>
@@ -8401,10 +8933,10 @@
         <v>10</v>
       </c>
       <c r="H134">
-        <v>3.1941901509999999</v>
+        <v>0.67534196107888</v>
       </c>
       <c r="I134">
-        <v>0.17386124999999999</v>
+        <v>0.17467441600092501</v>
       </c>
       <c r="J134" s="1">
         <v>508</v>
@@ -8413,10 +8945,10 @@
         <v>0</v>
       </c>
       <c r="L134">
-        <v>7.6634605726909499E-2</v>
+        <v>7.66346057269119E-2</v>
       </c>
       <c r="M134">
-        <v>1.4836250002190001E-3</v>
+        <v>1.4427080004679E-3</v>
       </c>
       <c r="N134" s="1">
         <v>400</v>
@@ -8430,13 +8962,17 @@
       <c r="Q134">
         <v>0.12785075000010601</v>
       </c>
-      <c r="R134" s="1"/>
-      <c r="S134">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R134" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S134" s="1"/>
+      <c r="T134">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>85</v>
       </c>
@@ -8459,10 +8995,10 @@
         <v>10</v>
       </c>
       <c r="H135">
-        <v>94.308233659999999</v>
+        <v>94.308233664354603</v>
       </c>
       <c r="I135">
-        <v>0.14859900000000001</v>
+        <v>0.148520208000263</v>
       </c>
       <c r="J135" s="1">
         <v>8882</v>
@@ -8471,10 +9007,10 @@
         <v>5</v>
       </c>
       <c r="L135">
-        <v>213.33504255447801</v>
+        <v>213.33504255518099</v>
       </c>
       <c r="M135">
-        <v>2.0500999999967399E-2</v>
+        <v>2.00979580004059E-2</v>
       </c>
       <c r="N135" s="1">
         <v>400</v>
@@ -8488,13 +9024,17 @@
       <c r="Q135">
         <v>0.70501200000035102</v>
       </c>
-      <c r="R135" s="1"/>
-      <c r="S135">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R135" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S135" s="1"/>
+      <c r="T135">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>85</v>
       </c>
@@ -8517,10 +9057,10 @@
         <v>10</v>
       </c>
       <c r="H136">
-        <v>9.0028920190000008</v>
+        <v>1.9209836508743301</v>
       </c>
       <c r="I136">
-        <v>0.1800255</v>
+        <v>0.181083915998897</v>
       </c>
       <c r="J136" s="1">
         <v>484</v>
@@ -8529,10 +9069,10 @@
         <v>0</v>
       </c>
       <c r="L136">
-        <v>0.29300027570883003</v>
+        <v>0.29300027570884102</v>
       </c>
       <c r="M136">
-        <v>1.4090829999986001E-3</v>
+        <v>1.3975420006318E-3</v>
       </c>
       <c r="N136" s="1">
         <v>400</v>
@@ -8546,13 +9086,17 @@
       <c r="Q136">
         <v>0.12448458399967401</v>
       </c>
-      <c r="R136" s="1"/>
-      <c r="S136">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R136" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S136" s="1"/>
+      <c r="T136">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>85</v>
       </c>
@@ -8575,10 +9119,10 @@
         <v>10</v>
       </c>
       <c r="H137">
-        <v>121.3456291</v>
+        <v>121.345629111354</v>
       </c>
       <c r="I137">
-        <v>0.150528</v>
+        <v>0.14911933299845201</v>
       </c>
       <c r="J137" s="1">
         <v>8684</v>
@@ -8587,10 +9131,10 @@
         <v>5</v>
       </c>
       <c r="L137">
-        <v>238.99533726930801</v>
+        <v>238.995337271127</v>
       </c>
       <c r="M137">
-        <v>1.9610333999935298E-2</v>
+        <v>1.9321042000228699E-2</v>
       </c>
       <c r="N137" s="1">
         <v>400</v>
@@ -8604,13 +9148,17 @@
       <c r="Q137">
         <v>0.63089312499960204</v>
       </c>
-      <c r="R137" s="1"/>
-      <c r="S137">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R137" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S137" s="1"/>
+      <c r="T137">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>85</v>
       </c>
@@ -8633,10 +9181,10 @@
         <v>10</v>
       </c>
       <c r="H138">
-        <v>9.9527734559999992</v>
+        <v>1.9739321314465901</v>
       </c>
       <c r="I138">
-        <v>0.18364675</v>
+        <v>0.18409754200001699</v>
       </c>
       <c r="J138" s="1">
         <v>484</v>
@@ -8645,10 +9193,10 @@
         <v>0</v>
       </c>
       <c r="L138">
-        <v>0.395294481437517</v>
+        <v>0.39529448143753099</v>
       </c>
       <c r="M138">
-        <v>1.4463749998867E-3</v>
+        <v>1.4193329989211001E-3</v>
       </c>
       <c r="N138" s="1">
         <v>400</v>
@@ -8662,13 +9210,17 @@
       <c r="Q138">
         <v>0.12427366699967</v>
       </c>
-      <c r="R138" s="1"/>
-      <c r="S138">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R138" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S138" s="1"/>
+      <c r="T138">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>85</v>
       </c>
@@ -8691,10 +9243,10 @@
         <v>10</v>
       </c>
       <c r="H139">
-        <v>-487.78510779999999</v>
+        <v>-487.78510779767998</v>
       </c>
       <c r="I139">
-        <v>0.151398583</v>
+        <v>0.14993870800026299</v>
       </c>
       <c r="J139" s="1">
         <v>10260</v>
@@ -8703,10 +9255,10 @@
         <v>6</v>
       </c>
       <c r="L139">
-        <v>-390.94840042491001</v>
+        <v>-390.94840042505098</v>
       </c>
       <c r="M139">
-        <v>2.3251291999713399E-2</v>
+        <v>2.3314500000196799E-2</v>
       </c>
       <c r="N139" s="1">
         <v>400</v>
@@ -8720,13 +9272,17 @@
       <c r="Q139">
         <v>0.70432870800004799</v>
       </c>
-      <c r="R139" s="1"/>
-      <c r="S139">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R139" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S139" s="1"/>
+      <c r="T139">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>85</v>
       </c>
@@ -8749,10 +9305,10 @@
         <v>10</v>
       </c>
       <c r="H140">
-        <v>2.6194674930000001</v>
+        <v>0.589659790018496</v>
       </c>
       <c r="I140">
-        <v>0.194986417</v>
+        <v>0.18454125000061999</v>
       </c>
       <c r="J140" s="1">
         <v>484</v>
@@ -8761,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="L140">
-        <v>8.0408618615302394E-2</v>
+        <v>8.0408618615301894E-2</v>
       </c>
       <c r="M140">
-        <v>1.4073749998714999E-3</v>
+        <v>1.4290830004028E-3</v>
       </c>
       <c r="N140" s="1">
         <v>400</v>
@@ -8778,13 +9334,17 @@
       <c r="Q140">
         <v>0.125591583000186</v>
       </c>
-      <c r="R140" s="1"/>
-      <c r="S140">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R140" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S140" s="1"/>
+      <c r="T140">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>85</v>
       </c>
@@ -8807,10 +9367,10 @@
         <v>10</v>
       </c>
       <c r="H141">
-        <v>-313.5496852</v>
+        <v>-313.549685215029</v>
       </c>
       <c r="I141">
-        <v>0.167326958</v>
+        <v>0.165621416999783</v>
       </c>
       <c r="J141" s="1">
         <v>11746</v>
@@ -8819,10 +9379,10 @@
         <v>5</v>
       </c>
       <c r="L141">
-        <v>-184.124804728811</v>
+        <v>-184.12480472781601</v>
       </c>
       <c r="M141">
-        <v>2.6578999999855999E-2</v>
+        <v>2.6730167001005601E-2</v>
       </c>
       <c r="N141" s="1">
         <v>400</v>
@@ -8836,13 +9396,17 @@
       <c r="Q141">
         <v>0.76504129200020499</v>
       </c>
-      <c r="R141" s="1"/>
-      <c r="S141">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R141" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S141" s="1"/>
+      <c r="T141">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>85</v>
       </c>
@@ -8865,10 +9429,10 @@
         <v>10</v>
       </c>
       <c r="H142">
-        <v>3.9552091300000001</v>
+        <v>0.75070763448813305</v>
       </c>
       <c r="I142">
-        <v>0.20867654199999999</v>
+        <v>0.20352366699989899</v>
       </c>
       <c r="J142" s="1">
         <v>508</v>
@@ -8877,10 +9441,10 @@
         <v>0</v>
       </c>
       <c r="L142">
-        <v>0.13155207093633101</v>
+        <v>0.131552070936343</v>
       </c>
       <c r="M142">
-        <v>1.50279100034822E-3</v>
+        <v>1.51266700049745E-3</v>
       </c>
       <c r="N142" s="1">
         <v>400</v>
@@ -8894,14 +9458,18 @@
       <c r="Q142">
         <v>0.12702475000014599</v>
       </c>
-      <c r="R142" s="1"/>
-      <c r="S142">
-        <f t="shared" si="2"/>
+      <c r="R142" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S142" s="1"/>
+      <c r="T142">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="S3:S142">
+  <conditionalFormatting sqref="T3:T142">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>

--- a/data/DPresults.xlsx
+++ b/data/DPresults.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\segmentation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AABDDB-A7E9-4A93-A1C3-55BEE17A3C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE264C7-7AF5-457C-8509-38E363B5E6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="255" windowWidth="23250" windowHeight="15225" xr2:uid="{7E3558C8-CB49-46FB-8C25-B70FF8305F7B}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="18372" windowHeight="12888" xr2:uid="{7E3558C8-CB49-46FB-8C25-B70FF8305F7B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -414,9 +414,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -454,7 +454,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -560,7 +560,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -702,7 +702,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -711,14 +711,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F6F3FC8-390D-4018-9A07-1C7FE899F7FD}">
   <dimension ref="A1:T142"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="9.140625" style="2"/>
-    <col min="6" max="6" width="9.140625" style="1"/>
-    <col min="10" max="10" width="9.140625" style="1"/>
+    <col min="5" max="5" width="9.109375" style="2"/>
+    <col min="6" max="6" width="9.109375" style="1"/>
+    <col min="10" max="10" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="F1" s="1" t="s">
         <v>96</v>
       </c>
@@ -731,7 +731,7 @@
       </c>
       <c r="S1" s="1"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -759,7 +759,7 @@
       <c r="I2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>5</v>
       </c>
       <c r="K2" t="s">
@@ -771,7 +771,7 @@
       <c r="M2" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" t="s">
         <v>5</v>
       </c>
       <c r="O2" t="s">
@@ -788,7 +788,7 @@
       </c>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -804,7 +804,7 @@
       <c r="E3" s="2">
         <v>134</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3">
         <v>4534</v>
       </c>
       <c r="G3">
@@ -814,21 +814,21 @@
         <v>1501.1341522299799</v>
       </c>
       <c r="I3">
-        <v>2.0723417001136099E-2</v>
-      </c>
-      <c r="J3" s="1">
+        <v>2.1276082999975101E-2</v>
+      </c>
+      <c r="J3">
         <v>4485</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <v>1649.31752903027</v>
       </c>
       <c r="M3">
-        <v>1.00887919998058E-2</v>
-      </c>
-      <c r="N3" s="1">
+        <v>1.01045419996808E-2</v>
+      </c>
+      <c r="N3">
         <v>400</v>
       </c>
       <c r="O3">
@@ -838,7 +838,7 @@
         <v>1528.05676177343</v>
       </c>
       <c r="Q3">
-        <v>0.27298408299975502</v>
+        <v>0.273011874998701</v>
       </c>
       <c r="R3">
         <f>IF(O3=G3,(P3-H3)/H3,NA())</f>
@@ -850,7 +850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -866,41 +866,41 @@
       <c r="E4" s="2">
         <v>134</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4">
         <v>4534</v>
       </c>
       <c r="G4">
         <v>10</v>
       </c>
       <c r="H4">
-        <v>705.13368488428796</v>
+        <v>3291883.60418437</v>
       </c>
       <c r="I4">
-        <v>4.7328750000815399E-2</v>
-      </c>
-      <c r="J4" s="1">
+        <v>4.7866375000012298E-2</v>
+      </c>
+      <c r="J4">
         <v>246</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L4">
-        <v>176.03829513752601</v>
+        <v>3264695.3541827798</v>
       </c>
       <c r="M4">
-        <v>7.4049999966509998E-4</v>
-      </c>
-      <c r="N4" s="1">
+        <v>8.3350000022609999E-4</v>
+      </c>
+      <c r="N4">
         <v>400</v>
       </c>
       <c r="O4">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="P4">
-        <v>349.06519600649898</v>
+        <v>3657932.2330549699</v>
       </c>
       <c r="Q4">
-        <v>0.16677724999999499</v>
+        <v>0.23888441700000801</v>
       </c>
       <c r="R4" t="e">
         <f t="shared" ref="R4:R67" si="1">IF(O4=G4,(P4-H4)/H4,NA())</f>
@@ -912,7 +912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -928,7 +928,7 @@
       <c r="E5" s="2">
         <v>135</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5">
         <v>4648</v>
       </c>
       <c r="G5">
@@ -938,21 +938,21 @@
         <v>487.94223846170701</v>
       </c>
       <c r="I5">
-        <v>2.2845334000521599E-2</v>
-      </c>
-      <c r="J5" s="1">
+        <v>2.2873916999742502E-2</v>
+      </c>
+      <c r="J5">
         <v>2646</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>543.24317690561304</v>
       </c>
       <c r="M5">
-        <v>6.1009999990346E-3</v>
-      </c>
-      <c r="N5" s="1">
+        <v>5.9356250003474997E-3</v>
+      </c>
+      <c r="N5">
         <v>400</v>
       </c>
       <c r="O5">
@@ -962,7 +962,7 @@
         <v>517.26024044328005</v>
       </c>
       <c r="Q5">
-        <v>0.235789332999956</v>
+        <v>0.22914933299943999</v>
       </c>
       <c r="R5" t="e">
         <f t="shared" si="1"/>
@@ -974,7 +974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -990,41 +990,41 @@
       <c r="E6" s="2">
         <v>135</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6">
         <v>4648</v>
       </c>
       <c r="G6">
         <v>10</v>
       </c>
       <c r="H6">
-        <v>13.141456302652699</v>
+        <v>1114.9842308963</v>
       </c>
       <c r="I6">
-        <v>2.3687082999458601E-2</v>
-      </c>
-      <c r="J6" s="1">
-        <v>262</v>
+        <v>2.3841500000344198E-2</v>
+      </c>
+      <c r="J6">
+        <v>511</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L6">
-        <v>11.0592164106518</v>
+        <v>937.07291010139102</v>
       </c>
       <c r="M6">
-        <v>8.0366700058219997E-4</v>
-      </c>
-      <c r="N6" s="1">
+        <v>1.6085000006569E-3</v>
+      </c>
+      <c r="N6">
         <v>400</v>
       </c>
       <c r="O6">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="P6">
-        <v>8.0276827392361803</v>
+        <v>1063.39703097763</v>
       </c>
       <c r="Q6">
-        <v>6.3984458000049899E-2</v>
+        <v>0.21516633300052401</v>
       </c>
       <c r="R6" t="e">
         <f t="shared" si="1"/>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1052,7 +1052,7 @@
       <c r="E7" s="2">
         <v>135</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7">
         <v>4648</v>
       </c>
       <c r="G7">
@@ -1062,21 +1062,21 @@
         <v>1395.3675476954299</v>
       </c>
       <c r="I7">
-        <v>2.21874170001683E-2</v>
-      </c>
-      <c r="J7" s="1">
+        <v>2.1617624999635099E-2</v>
+      </c>
+      <c r="J7">
         <v>4217</v>
       </c>
       <c r="K7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7">
         <v>1511.32616394252</v>
       </c>
       <c r="M7">
-        <v>9.5327500002895006E-3</v>
-      </c>
-      <c r="N7" s="1">
+        <v>9.7446670006319999E-3</v>
+      </c>
+      <c r="N7">
         <v>400</v>
       </c>
       <c r="O7">
@@ -1086,7 +1086,7 @@
         <v>1454.69206297967</v>
       </c>
       <c r="Q7">
-        <v>0.26677937500016902</v>
+        <v>0.25809791600113302</v>
       </c>
       <c r="R7" t="e">
         <f t="shared" si="1"/>
@@ -1098,7 +1098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1114,41 +1114,41 @@
       <c r="E8" s="2">
         <v>135</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8">
         <v>4648</v>
       </c>
       <c r="G8">
         <v>10</v>
       </c>
       <c r="H8">
-        <v>390.52896885359701</v>
+        <v>924219.09539905202</v>
       </c>
       <c r="I8">
-        <v>2.4792166999759498E-2</v>
-      </c>
-      <c r="J8" s="1">
+        <v>3.0476790998363801E-2</v>
+      </c>
+      <c r="J8">
         <v>248</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L8">
-        <v>55.742676689361097</v>
+        <v>951613.16704728606</v>
       </c>
       <c r="M8">
-        <v>7.6970800000699996E-4</v>
-      </c>
-      <c r="N8" s="1">
+        <v>8.4045800031160001E-4</v>
+      </c>
+      <c r="N8">
         <v>400</v>
       </c>
       <c r="O8">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P8">
-        <v>55.742676689360799</v>
+        <v>1053883.0514851999</v>
       </c>
       <c r="Q8">
-        <v>6.2383167000007199E-2</v>
+        <v>0.216250458001013</v>
       </c>
       <c r="R8" t="e">
         <f t="shared" si="1"/>
@@ -1160,7 +1160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1176,7 +1176,7 @@
       <c r="E9" s="2">
         <v>71</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9">
         <v>232</v>
       </c>
       <c r="G9">
@@ -1186,21 +1186,21 @@
         <v>918.02557255422096</v>
       </c>
       <c r="I9">
-        <v>9.0537500000199996E-4</v>
-      </c>
-      <c r="J9" s="1">
+        <v>9.0904200078509995E-4</v>
+      </c>
+      <c r="J9">
         <v>1181</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
         <v>992.13092420200098</v>
       </c>
       <c r="M9">
-        <v>2.6804999997693001E-3</v>
-      </c>
-      <c r="N9" s="1">
+        <v>2.6373330001661002E-3</v>
+      </c>
+      <c r="N9">
         <v>400</v>
       </c>
       <c r="O9">
@@ -1210,7 +1210,7 @@
         <v>954.95621745246206</v>
       </c>
       <c r="Q9">
-        <v>7.3558666000280895E-2</v>
+        <v>7.3109540999212103E-2</v>
       </c>
       <c r="R9" t="e">
         <f t="shared" si="1"/>
@@ -1222,7 +1222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1238,45 +1238,45 @@
       <c r="E10" s="2">
         <v>71</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10">
         <v>232</v>
       </c>
       <c r="G10">
         <v>8</v>
       </c>
       <c r="H10">
-        <v>1389.36164363227</v>
+        <v>6643658.8530804999</v>
       </c>
       <c r="I10">
-        <v>1.0682080010154999E-3</v>
-      </c>
-      <c r="J10" s="1">
+        <v>1.0638330004439E-3</v>
+      </c>
+      <c r="J10">
         <v>120</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L10">
-        <v>124.876911202325</v>
+        <v>6480045.90698162</v>
       </c>
       <c r="M10">
-        <v>3.7237499964240002E-4</v>
-      </c>
-      <c r="N10" s="1">
+        <v>4.1354200038759998E-4</v>
+      </c>
+      <c r="N10">
         <v>400</v>
       </c>
       <c r="O10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>124.876911202325</v>
+        <v>6776618.6884527104</v>
       </c>
       <c r="Q10">
-        <v>3.2044333000158E-2</v>
-      </c>
-      <c r="R10" t="e">
+        <v>8.5063165999599705E-2</v>
+      </c>
+      <c r="R10">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>2.0013043762859725E-2</v>
       </c>
       <c r="S10" s="1"/>
       <c r="T10">
@@ -1284,7 +1284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1300,7 +1300,7 @@
       <c r="E11" s="2">
         <v>138</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11">
         <v>4996</v>
       </c>
       <c r="G11">
@@ -1310,21 +1310,21 @@
         <v>602.80629062495404</v>
       </c>
       <c r="I11">
-        <v>2.3292874999242399E-2</v>
-      </c>
-      <c r="J11" s="1">
+        <v>2.3305833999984302E-2</v>
+      </c>
+      <c r="J11">
         <v>3426</v>
       </c>
       <c r="K11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>690.94973740272997</v>
       </c>
       <c r="M11">
-        <v>7.8362910007854E-3</v>
-      </c>
-      <c r="N11" s="1">
+        <v>7.8262080005514992E-3</v>
+      </c>
+      <c r="N11">
         <v>400</v>
       </c>
       <c r="O11">
@@ -1334,7 +1334,7 @@
         <v>607.63310677229504</v>
       </c>
       <c r="Q11">
-        <v>0.264848124999844</v>
+        <v>0.26223562499944802</v>
       </c>
       <c r="R11">
         <f t="shared" si="1"/>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1362,41 +1362,41 @@
       <c r="E12" s="2">
         <v>138</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12">
         <v>4996</v>
       </c>
       <c r="G12">
         <v>10</v>
       </c>
       <c r="H12">
-        <v>20.548922353263499</v>
+        <v>2387.47930311658</v>
       </c>
       <c r="I12">
-        <v>2.6259874999595902E-2</v>
-      </c>
-      <c r="J12" s="1">
-        <v>254</v>
+        <v>2.69768749985814E-2</v>
+      </c>
+      <c r="J12">
+        <v>350</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L12">
-        <v>7.7667477322999297</v>
+        <v>2462.8623400946599</v>
       </c>
       <c r="M12">
-        <v>7.5350000042809998E-4</v>
-      </c>
-      <c r="N12" s="1">
+        <v>1.1290829988865E-3</v>
+      </c>
+      <c r="N12">
         <v>400</v>
       </c>
       <c r="O12">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P12">
-        <v>5.6642866408381698</v>
+        <v>3499.8299061505099</v>
       </c>
       <c r="Q12">
-        <v>6.3844041000265805E-2</v>
+        <v>0.21437287500157201</v>
       </c>
       <c r="R12" t="e">
         <f t="shared" si="1"/>
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1424,7 +1424,7 @@
       <c r="E13" s="2">
         <v>79</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13">
         <v>268</v>
       </c>
       <c r="G13">
@@ -1434,21 +1434,21 @@
         <v>711.06543522588197</v>
       </c>
       <c r="I13">
-        <v>1.1426670007494001E-3</v>
-      </c>
-      <c r="J13" s="1">
+        <v>1.0847909998118999E-3</v>
+      </c>
+      <c r="J13">
         <v>2015</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
         <v>878.61342647987306</v>
       </c>
       <c r="M13">
-        <v>4.503084001044E-3</v>
-      </c>
-      <c r="N13" s="1">
+        <v>4.5579580000776002E-3</v>
+      </c>
+      <c r="N13">
         <v>400</v>
       </c>
       <c r="O13">
@@ -1458,7 +1458,7 @@
         <v>719.26289168688402</v>
       </c>
       <c r="Q13">
-        <v>0.115329416999884</v>
+        <v>0.113979916999596</v>
       </c>
       <c r="R13" t="e">
         <f t="shared" si="1"/>
@@ -1470,7 +1470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1486,41 +1486,41 @@
       <c r="E14" s="2">
         <v>79</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14">
         <v>268</v>
       </c>
       <c r="G14">
         <v>9</v>
       </c>
       <c r="H14">
-        <v>225.45411696258199</v>
+        <v>157946.58719552401</v>
       </c>
       <c r="I14">
-        <v>1.2145410000812E-3</v>
-      </c>
-      <c r="J14" s="1">
+        <v>1.2610840003617E-3</v>
+      </c>
+      <c r="J14">
         <v>136</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>28.5256616083573</v>
+        <v>149956.68149431501</v>
       </c>
       <c r="M14">
-        <v>4.2691699854910002E-4</v>
-      </c>
-      <c r="N14" s="1">
+        <v>4.5704100011780002E-4</v>
+      </c>
+      <c r="N14">
         <v>400</v>
       </c>
       <c r="O14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>28.525661608356199</v>
+        <v>151160.19674152101</v>
       </c>
       <c r="Q14">
-        <v>3.5627416999886898E-2</v>
+        <v>0.108852375000424</v>
       </c>
       <c r="R14" t="e">
         <f t="shared" si="1"/>
@@ -1532,7 +1532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -1548,7 +1548,7 @@
       <c r="E15" s="2">
         <v>133</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15">
         <v>4421</v>
       </c>
       <c r="G15">
@@ -1558,21 +1558,21 @@
         <v>703.73073976309502</v>
       </c>
       <c r="I15">
-        <v>2.0642125000449499E-2</v>
-      </c>
-      <c r="J15" s="1">
+        <v>2.0649416001106102E-2</v>
+      </c>
+      <c r="J15">
         <v>1950</v>
       </c>
       <c r="K15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L15">
         <v>721.74215185574405</v>
       </c>
       <c r="M15">
-        <v>4.4752079993485997E-3</v>
-      </c>
-      <c r="N15" s="1">
+        <v>4.3689169997378E-3</v>
+      </c>
+      <c r="N15">
         <v>400</v>
       </c>
       <c r="O15">
@@ -1582,7 +1582,7 @@
         <v>698.85870064003404</v>
       </c>
       <c r="Q15">
-        <v>0.23854741699960799</v>
+        <v>0.238617166998665</v>
       </c>
       <c r="R15" t="e">
         <f t="shared" si="1"/>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -1610,41 +1610,41 @@
       <c r="E16" s="2">
         <v>133</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16">
         <v>4421</v>
       </c>
       <c r="G16">
         <v>10</v>
       </c>
       <c r="H16">
-        <v>34.689657014435099</v>
+        <v>6000.1572239919597</v>
       </c>
       <c r="I16">
-        <v>2.33290420001139E-2</v>
-      </c>
-      <c r="J16" s="1">
-        <v>244</v>
+        <v>2.3693958999501701E-2</v>
+      </c>
+      <c r="J16">
+        <v>276</v>
       </c>
       <c r="K16">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L16">
-        <v>32.045345884309199</v>
+        <v>5553.78114520095</v>
       </c>
       <c r="M16">
-        <v>7.5362499956090003E-4</v>
-      </c>
-      <c r="N16" s="1">
+        <v>9.247910002159E-4</v>
+      </c>
+      <c r="N16">
         <v>400</v>
       </c>
       <c r="O16">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="P16">
-        <v>31.0074467978569</v>
+        <v>15191.921344561801</v>
       </c>
       <c r="Q16">
-        <v>0.11277620800001301</v>
+        <v>0.200822499999048</v>
       </c>
       <c r="R16" t="e">
         <f t="shared" si="1"/>
@@ -1656,7 +1656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -1672,7 +1672,7 @@
       <c r="E17" s="2">
         <v>134</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17">
         <v>4534</v>
       </c>
       <c r="G17">
@@ -1682,21 +1682,21 @@
         <v>1174.96873752942</v>
       </c>
       <c r="I17">
-        <v>2.25255419991299E-2</v>
-      </c>
-      <c r="J17" s="1">
+        <v>2.2214708998944802E-2</v>
+      </c>
+      <c r="J17">
         <v>3893</v>
       </c>
       <c r="K17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L17">
         <v>1388.1447966866599</v>
       </c>
       <c r="M17">
-        <v>9.1152080003666005E-3</v>
-      </c>
-      <c r="N17" s="1">
+        <v>8.8288329989154E-3</v>
+      </c>
+      <c r="N17">
         <v>400</v>
       </c>
       <c r="O17">
@@ -1706,7 +1706,7 @@
         <v>1208.46651289887</v>
       </c>
       <c r="Q17">
-        <v>0.24814691700021199</v>
+        <v>0.24752441700002201</v>
       </c>
       <c r="R17">
         <f t="shared" si="1"/>
@@ -1718,7 +1718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -1734,41 +1734,41 @@
       <c r="E18" s="2">
         <v>134</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18">
         <v>4534</v>
       </c>
       <c r="G18">
         <v>10</v>
       </c>
       <c r="H18">
-        <v>183.09944673815801</v>
+        <v>226370.607949675</v>
       </c>
       <c r="I18">
-        <v>2.25864170006389E-2</v>
-      </c>
-      <c r="J18" s="1">
-        <v>246</v>
+        <v>2.3137083000619799E-2</v>
+      </c>
+      <c r="J18">
+        <v>247</v>
       </c>
       <c r="K18">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L18">
-        <v>45.5050171909539</v>
+        <v>188523.36896550801</v>
       </c>
       <c r="M18">
-        <v>7.6558299952010004E-4</v>
-      </c>
-      <c r="N18" s="1">
+        <v>8.302919995912E-4</v>
+      </c>
+      <c r="N18">
         <v>400</v>
       </c>
       <c r="O18">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="P18">
-        <v>59.557802436641602</v>
+        <v>259986.081504028</v>
       </c>
       <c r="Q18">
-        <v>0.12165449999974901</v>
+        <v>0.232344959000329</v>
       </c>
       <c r="R18" t="e">
         <f t="shared" si="1"/>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -1796,7 +1796,7 @@
       <c r="E19" s="2">
         <v>134</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19">
         <v>4534</v>
       </c>
       <c r="G19">
@@ -1806,21 +1806,21 @@
         <v>776.78840586934405</v>
       </c>
       <c r="I19">
-        <v>2.1239875000901499E-2</v>
-      </c>
-      <c r="J19" s="1">
+        <v>2.1054291000837101E-2</v>
+      </c>
+      <c r="J19">
         <v>3376</v>
       </c>
       <c r="K19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L19">
         <v>921.55344020151199</v>
       </c>
       <c r="M19">
-        <v>7.6976249983999002E-3</v>
-      </c>
-      <c r="N19" s="1">
+        <v>7.4567079991538004E-3</v>
+      </c>
+      <c r="N19">
         <v>400</v>
       </c>
       <c r="O19">
@@ -1830,7 +1830,7 @@
         <v>819.59416134298203</v>
       </c>
       <c r="Q19">
-        <v>0.23187733299982899</v>
+        <v>0.23458150000078601</v>
       </c>
       <c r="R19" t="e">
         <f t="shared" si="1"/>
@@ -1842,7 +1842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -1858,53 +1858,53 @@
       <c r="E20" s="2">
         <v>134</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20">
         <v>4534</v>
       </c>
       <c r="G20">
         <v>10</v>
       </c>
       <c r="H20">
-        <v>43.035614517001903</v>
+        <v>9634.4429360633894</v>
       </c>
       <c r="I20">
-        <v>2.35779159993398E-2</v>
-      </c>
-      <c r="J20" s="1">
-        <v>246</v>
+        <v>2.4322541999936199E-2</v>
+      </c>
+      <c r="J20">
+        <v>249</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>14.071543688649699</v>
+        <v>9634.4429360633894</v>
       </c>
       <c r="M20">
-        <v>7.4991699875680002E-4</v>
-      </c>
-      <c r="N20" s="1">
+        <v>8.3649999942280004E-4</v>
+      </c>
+      <c r="N20">
         <v>400</v>
       </c>
       <c r="O20">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>14.071543688653501</v>
+        <v>14852.3926812921</v>
       </c>
       <c r="Q20">
-        <v>6.4058417000069298E-2</v>
-      </c>
-      <c r="R20" t="e">
+        <v>0.17983762499898101</v>
+      </c>
+      <c r="R20">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>0.54159330018936747</v>
       </c>
       <c r="S20" s="1"/>
       <c r="T20">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1920,7 +1920,7 @@
       <c r="E21" s="2">
         <v>144</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21">
         <v>5719</v>
       </c>
       <c r="G21">
@@ -1930,21 +1930,21 @@
         <v>2233.4543852075799</v>
       </c>
       <c r="I21">
-        <v>6.0550374999365802E-2</v>
-      </c>
-      <c r="J21" s="1">
+        <v>5.8840249999775503E-2</v>
+      </c>
+      <c r="J21">
         <v>2554</v>
       </c>
       <c r="K21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21">
         <v>2286.6403570822299</v>
       </c>
       <c r="M21">
-        <v>5.7242079983552E-3</v>
-      </c>
-      <c r="N21" s="1">
+        <v>5.7266250005340996E-3</v>
+      </c>
+      <c r="N21">
         <v>400</v>
       </c>
       <c r="O21">
@@ -1954,7 +1954,7 @@
         <v>2265.09273903135</v>
       </c>
       <c r="Q21">
-        <v>0.23167404199966701</v>
+        <v>0.23318591600036501</v>
       </c>
       <c r="R21" t="e">
         <f t="shared" si="1"/>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -1982,41 +1982,41 @@
       <c r="E22" s="2">
         <v>144</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22">
         <v>5719</v>
       </c>
       <c r="G22">
         <v>10</v>
       </c>
       <c r="H22">
-        <v>4726.1067260092696</v>
+        <v>182954105.31889799</v>
       </c>
       <c r="I22">
-        <v>2.8701416998956099E-2</v>
-      </c>
-      <c r="J22" s="1">
+        <v>3.0361249999259599E-2</v>
+      </c>
+      <c r="J22">
         <v>266</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>294.075487969275</v>
+        <v>190695010.94303101</v>
       </c>
       <c r="M22">
-        <v>8.0600000001140003E-4</v>
-      </c>
-      <c r="N22" s="1">
+        <v>8.7608300054849999E-4</v>
+      </c>
+      <c r="N22">
         <v>400</v>
       </c>
       <c r="O22">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P22">
-        <v>294.075487969275</v>
+        <v>175519073.41646901</v>
       </c>
       <c r="Q22">
-        <v>6.6929708999850804E-2</v>
+        <v>0.228206124998905</v>
       </c>
       <c r="R22" t="e">
         <f t="shared" si="1"/>
@@ -2028,7 +2028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -2044,7 +2044,7 @@
       <c r="E23" s="2">
         <v>140</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23">
         <v>5233</v>
       </c>
       <c r="G23">
@@ -2054,21 +2054,21 @@
         <v>1537.89692594907</v>
       </c>
       <c r="I23">
-        <v>2.5402334000318601E-2</v>
-      </c>
-      <c r="J23" s="1">
+        <v>2.5195249998432701E-2</v>
+      </c>
+      <c r="J23">
         <v>4286</v>
       </c>
       <c r="K23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23">
         <v>1621.9412258868799</v>
       </c>
       <c r="M23">
-        <v>9.6422500009794004E-3</v>
-      </c>
-      <c r="N23" s="1">
+        <v>9.6805420016606997E-3</v>
+      </c>
+      <c r="N23">
         <v>400</v>
       </c>
       <c r="O23">
@@ -2078,7 +2078,7 @@
         <v>1569.1642478953299</v>
       </c>
       <c r="Q23">
-        <v>0.245683124999686</v>
+        <v>0.24038816699976401</v>
       </c>
       <c r="R23" t="e">
         <f t="shared" si="1"/>
@@ -2090,7 +2090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -2106,41 +2106,41 @@
       <c r="E24" s="2">
         <v>140</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24">
         <v>5233</v>
       </c>
       <c r="G24">
         <v>10</v>
       </c>
       <c r="H24">
-        <v>497.55302027796102</v>
+        <v>2213908.6669605402</v>
       </c>
       <c r="I24">
-        <v>2.6228792001347701E-2</v>
-      </c>
-      <c r="J24" s="1">
+        <v>2.7301166999677599E-2</v>
+      </c>
+      <c r="J24">
         <v>258</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L24">
-        <v>31.554707791756801</v>
+        <v>2372766.52117051</v>
       </c>
       <c r="M24">
-        <v>7.7354199856919997E-4</v>
-      </c>
-      <c r="N24" s="1">
+        <v>8.6754200128779995E-4</v>
+      </c>
+      <c r="N24">
         <v>400</v>
       </c>
       <c r="O24">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="P24">
-        <v>31.554707791756599</v>
+        <v>2816845.8883493901</v>
       </c>
       <c r="Q24">
-        <v>6.6515416000129293E-2</v>
+        <v>0.30374391599980299</v>
       </c>
       <c r="R24" t="e">
         <f t="shared" si="1"/>
@@ -2152,7 +2152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -2168,7 +2168,7 @@
       <c r="E25" s="2">
         <v>134</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25">
         <v>4534</v>
       </c>
       <c r="G25">
@@ -2178,21 +2178,21 @@
         <v>1499.62578072622</v>
       </c>
       <c r="I25">
-        <v>2.24415829998179E-2</v>
-      </c>
-      <c r="J25" s="1">
+        <v>2.2363333000612301E-2</v>
+      </c>
+      <c r="J25">
         <v>5736</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25">
         <v>1618.5261927461199</v>
       </c>
       <c r="M25">
-        <v>1.2934625001435E-2</v>
-      </c>
-      <c r="N25" s="1">
+        <v>1.28785830002016E-2</v>
+      </c>
+      <c r="N25">
         <v>400</v>
       </c>
       <c r="O25">
@@ -2202,7 +2202,7 @@
         <v>1545.9045904730499</v>
       </c>
       <c r="Q25">
-        <v>0.28359795899996199</v>
+        <v>0.28461966699978802</v>
       </c>
       <c r="R25" t="e">
         <f t="shared" si="1"/>
@@ -2214,7 +2214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -2230,41 +2230,41 @@
       <c r="E26" s="2">
         <v>134</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26">
         <v>4534</v>
       </c>
       <c r="G26">
         <v>10</v>
       </c>
       <c r="H26">
-        <v>602.60833157756599</v>
+        <v>2228276.9251216701</v>
       </c>
       <c r="I26">
-        <v>2.3885416998382401E-2</v>
-      </c>
-      <c r="J26" s="1">
+        <v>2.4905708000005598E-2</v>
+      </c>
+      <c r="J26">
         <v>246</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>35.710028706881097</v>
+        <v>2311432.5687494399</v>
       </c>
       <c r="M26">
-        <v>7.4612499884089999E-4</v>
-      </c>
-      <c r="N26" s="1">
+        <v>8.1795799997049997E-4</v>
+      </c>
+      <c r="N26">
         <v>400</v>
       </c>
       <c r="O26">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P26">
-        <v>35.710028706881097</v>
+        <v>2643346.9277064698</v>
       </c>
       <c r="Q26">
-        <v>6.3750917000106697E-2</v>
+        <v>0.292090208000445</v>
       </c>
       <c r="R26" t="e">
         <f t="shared" si="1"/>
@@ -2276,7 +2276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -2292,7 +2292,7 @@
       <c r="E27" s="2">
         <v>133</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27">
         <v>4421</v>
       </c>
       <c r="G27">
@@ -2302,21 +2302,21 @@
         <v>1570.0986124132901</v>
       </c>
       <c r="I27">
-        <v>2.03480830004991E-2</v>
-      </c>
-      <c r="J27" s="1">
+        <v>2.0584749998306499E-2</v>
+      </c>
+      <c r="J27">
         <v>2828</v>
       </c>
       <c r="K27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27">
         <v>1620.3091390955301</v>
       </c>
       <c r="M27">
-        <v>6.2595840008725003E-3</v>
-      </c>
-      <c r="N27" s="1">
+        <v>6.1874160001024999E-3</v>
+      </c>
+      <c r="N27">
         <v>400</v>
       </c>
       <c r="O27">
@@ -2326,7 +2326,7 @@
         <v>1598.0351815039201</v>
       </c>
       <c r="Q27">
-        <v>0.21492808299990401</v>
+        <v>0.22066254200035401</v>
       </c>
       <c r="R27" t="e">
         <f t="shared" si="1"/>
@@ -2338,7 +2338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -2354,41 +2354,41 @@
       <c r="E28" s="2">
         <v>133</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28">
         <v>4421</v>
       </c>
       <c r="G28">
         <v>10</v>
       </c>
       <c r="H28">
-        <v>815.418750065057</v>
+        <v>3584658.3395960801</v>
       </c>
       <c r="I28">
-        <v>2.38602499994158E-2</v>
-      </c>
-      <c r="J28" s="1">
+        <v>2.48443750006117E-2</v>
+      </c>
+      <c r="J28">
         <v>244</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L28">
-        <v>55.576376345611699</v>
+        <v>3597766.1408201801</v>
       </c>
       <c r="M28">
-        <v>7.4733300061779996E-4</v>
-      </c>
-      <c r="N28" s="1">
+        <v>8.4045800031160001E-4</v>
+      </c>
+      <c r="N28">
         <v>400</v>
       </c>
       <c r="O28">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P28">
-        <v>55.576376345611301</v>
+        <v>4033111.50763444</v>
       </c>
       <c r="Q28">
-        <v>6.3204916999893598E-2</v>
+        <v>0.19914470799994799</v>
       </c>
       <c r="R28" t="e">
         <f t="shared" si="1"/>
@@ -2400,7 +2400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>9</v>
       </c>
@@ -2416,7 +2416,7 @@
       <c r="E29" s="2">
         <v>144</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29">
         <v>5719</v>
       </c>
       <c r="G29">
@@ -2426,21 +2426,21 @@
         <v>1516.2880216756</v>
       </c>
       <c r="I29">
-        <v>2.8862457998911802E-2</v>
-      </c>
-      <c r="J29" s="1">
+        <v>2.8915916000187201E-2</v>
+      </c>
+      <c r="J29">
         <v>1235</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29">
         <v>1573.1483731337</v>
       </c>
       <c r="M29">
-        <v>2.8499170002760001E-3</v>
-      </c>
-      <c r="N29" s="1">
+        <v>2.8401250001479001E-3</v>
+      </c>
+      <c r="N29">
         <v>400</v>
       </c>
       <c r="O29">
@@ -2450,7 +2450,7 @@
         <v>1573.14837313369</v>
       </c>
       <c r="Q29">
-        <v>9.2376625000269996E-2</v>
+        <v>9.5158291998813996E-2</v>
       </c>
       <c r="R29" t="e">
         <f t="shared" si="1"/>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>9</v>
       </c>
@@ -2478,41 +2478,41 @@
       <c r="E30" s="2">
         <v>144</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30">
         <v>5719</v>
       </c>
       <c r="G30">
         <v>10</v>
       </c>
       <c r="H30">
-        <v>417.76059881302803</v>
+        <v>952866.58221787401</v>
       </c>
       <c r="I30">
-        <v>3.0643165999208501E-2</v>
-      </c>
-      <c r="J30" s="1">
+        <v>3.1878249999863301E-2</v>
+      </c>
+      <c r="J30">
         <v>266</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L30">
-        <v>19.366121041390201</v>
+        <v>1146653.6967803501</v>
       </c>
       <c r="M30">
-        <v>8.3033299961240005E-4</v>
-      </c>
-      <c r="N30" s="1">
+        <v>9.2412500089260005E-4</v>
+      </c>
+      <c r="N30">
         <v>400</v>
       </c>
       <c r="O30">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="P30">
-        <v>19.366121041389899</v>
+        <v>1332758.73247823</v>
       </c>
       <c r="Q30">
-        <v>6.9395957999858995E-2</v>
+        <v>0.336707082999055</v>
       </c>
       <c r="R30" t="e">
         <f t="shared" si="1"/>
@@ -2524,7 +2524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -2540,7 +2540,7 @@
       <c r="E31" s="2">
         <v>144</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31">
         <v>5719</v>
       </c>
       <c r="G31">
@@ -2550,21 +2550,21 @@
         <v>1840.0974912085201</v>
       </c>
       <c r="I31">
-        <v>2.88386659995012E-2</v>
-      </c>
-      <c r="J31" s="1">
+        <v>2.95023750004475E-2</v>
+      </c>
+      <c r="J31">
         <v>2391</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31">
         <v>1955.9147773013899</v>
       </c>
       <c r="M31">
-        <v>5.3568749990517001E-3</v>
-      </c>
-      <c r="N31" s="1">
+        <v>5.3024579992779E-3</v>
+      </c>
+      <c r="N31">
         <v>400</v>
       </c>
       <c r="O31">
@@ -2574,7 +2574,7 @@
         <v>1834.58395273052</v>
       </c>
       <c r="Q31">
-        <v>0.53979287499987505</v>
+        <v>0.53097791699838104</v>
       </c>
       <c r="R31" t="e">
         <f t="shared" si="1"/>
@@ -2586,7 +2586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -2602,41 +2602,41 @@
       <c r="E32" s="2">
         <v>144</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32">
         <v>5719</v>
       </c>
       <c r="G32">
         <v>10</v>
       </c>
       <c r="H32">
-        <v>1241.41913480218</v>
+        <v>10080373.477198901</v>
       </c>
       <c r="I32">
-        <v>3.07421249999606E-2</v>
-      </c>
-      <c r="J32" s="1">
+        <v>3.2689334000678999E-2</v>
+      </c>
+      <c r="J32">
         <v>266</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L32">
-        <v>73.154615060258706</v>
+        <v>8908754.3435883392</v>
       </c>
       <c r="M32">
-        <v>7.997500015335E-4</v>
-      </c>
-      <c r="N32" s="1">
+        <v>9.0362500122860004E-4</v>
+      </c>
+      <c r="N32">
         <v>400</v>
       </c>
       <c r="O32">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="P32">
-        <v>73.154615060258607</v>
+        <v>11781451.2897735</v>
       </c>
       <c r="Q32">
-        <v>6.80429169997296E-2</v>
+        <v>0.438247624999348</v>
       </c>
       <c r="R32" t="e">
         <f t="shared" si="1"/>
@@ -2648,7 +2648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>9</v>
       </c>
@@ -2664,7 +2664,7 @@
       <c r="E33" s="2">
         <v>120</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33">
         <v>3043</v>
       </c>
       <c r="G33">
@@ -2674,21 +2674,21 @@
         <v>1176.58328992621</v>
       </c>
       <c r="I33">
-        <v>1.3535584001147001E-2</v>
-      </c>
-      <c r="J33" s="1">
+        <v>1.38335409992578E-2</v>
+      </c>
+      <c r="J33">
         <v>3231</v>
       </c>
       <c r="K33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33">
         <v>1273.0045571595499</v>
       </c>
       <c r="M33">
-        <v>7.3171250005543004E-3</v>
-      </c>
-      <c r="N33" s="1">
+        <v>7.2224590003315001E-3</v>
+      </c>
+      <c r="N33">
         <v>400</v>
       </c>
       <c r="O33">
@@ -2698,7 +2698,7 @@
         <v>1200.8838065617099</v>
       </c>
       <c r="Q33">
-        <v>0.24662879100014801</v>
+        <v>0.235946167000292</v>
       </c>
       <c r="R33" t="e">
         <f t="shared" si="1"/>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -2726,41 +2726,41 @@
       <c r="E34" s="2">
         <v>120</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34">
         <v>3043</v>
       </c>
       <c r="G34">
         <v>10</v>
       </c>
       <c r="H34">
-        <v>308.22554380717401</v>
+        <v>565622.57390661503</v>
       </c>
       <c r="I34">
-        <v>1.6589250000833999E-2</v>
-      </c>
-      <c r="J34" s="1">
+        <v>1.7345917000056901E-2</v>
+      </c>
+      <c r="J34">
         <v>218</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L34">
-        <v>24.161143430101099</v>
+        <v>578816.78131747199</v>
       </c>
       <c r="M34">
-        <v>6.7116699938189999E-4</v>
-      </c>
-      <c r="N34" s="1">
+        <v>7.4520799898889997E-4</v>
+      </c>
+      <c r="N34">
         <v>400</v>
       </c>
       <c r="O34">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P34">
-        <v>24.161143430101198</v>
+        <v>616295.47259936598</v>
       </c>
       <c r="Q34">
-        <v>5.7045458999709801E-2</v>
+        <v>0.26412804199935602</v>
       </c>
       <c r="R34" t="e">
         <f t="shared" si="1"/>
@@ -2772,7 +2772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>9</v>
       </c>
@@ -2788,7 +2788,7 @@
       <c r="E35" s="2">
         <v>98</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35">
         <v>1096</v>
       </c>
       <c r="G35">
@@ -2798,21 +2798,21 @@
         <v>612.26053328434296</v>
       </c>
       <c r="I35">
-        <v>4.2301659996154999E-3</v>
-      </c>
-      <c r="J35" s="1">
+        <v>4.2211250001855001E-3</v>
+      </c>
+      <c r="J35">
         <v>1988</v>
       </c>
       <c r="K35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L35">
         <v>664.59311704472304</v>
       </c>
       <c r="M35">
-        <v>4.5255000004544004E-3</v>
-      </c>
-      <c r="N35" s="1">
+        <v>4.5141670016164001E-3</v>
+      </c>
+      <c r="N35">
         <v>400</v>
       </c>
       <c r="O35">
@@ -2822,7 +2822,7 @@
         <v>635.75275702848705</v>
       </c>
       <c r="Q35">
-        <v>0.15228187499997101</v>
+        <v>0.14603741599967099</v>
       </c>
       <c r="R35" t="e">
         <f t="shared" si="1"/>
@@ -2834,7 +2834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -2850,41 +2850,41 @@
       <c r="E36" s="2">
         <v>98</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36">
         <v>1096</v>
       </c>
       <c r="G36">
         <v>10</v>
       </c>
       <c r="H36">
-        <v>63.5907224581129</v>
+        <v>15757.4565066956</v>
       </c>
       <c r="I36">
-        <v>4.6614580005552003E-3</v>
-      </c>
-      <c r="J36" s="1">
-        <v>174</v>
+        <v>4.8775830000522E-3</v>
+      </c>
+      <c r="J36">
+        <v>177</v>
       </c>
       <c r="K36">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L36">
-        <v>29.576714183799201</v>
+        <v>15450.383316872199</v>
       </c>
       <c r="M36">
-        <v>5.340829993656E-4</v>
-      </c>
-      <c r="N36" s="1">
+        <v>6.44874999125E-4</v>
+      </c>
+      <c r="N36">
         <v>400</v>
       </c>
       <c r="O36">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P36">
-        <v>25.430689006450802</v>
+        <v>18559.617249197399</v>
       </c>
       <c r="Q36">
-        <v>4.4803540999964697E-2</v>
+        <v>0.11156062500049301</v>
       </c>
       <c r="R36" t="e">
         <f t="shared" si="1"/>
@@ -2896,7 +2896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -2912,7 +2912,7 @@
       <c r="E37" s="2">
         <v>134</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37">
         <v>4534</v>
       </c>
       <c r="G37">
@@ -2922,21 +2922,21 @@
         <v>1283.64958535754</v>
       </c>
       <c r="I37">
-        <v>5.0656583000090898E-2</v>
-      </c>
-      <c r="J37" s="1">
+        <v>5.1373166001212597E-2</v>
+      </c>
+      <c r="J37">
         <v>4915</v>
       </c>
       <c r="K37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L37">
         <v>1369.37997399242</v>
       </c>
       <c r="M37">
-        <v>1.13620419997459E-2</v>
-      </c>
-      <c r="N37" s="1">
+        <v>1.113658399845E-2</v>
+      </c>
+      <c r="N37">
         <v>400</v>
       </c>
       <c r="O37">
@@ -2946,7 +2946,7 @@
         <v>1319.33975467812</v>
       </c>
       <c r="Q37">
-        <v>0.27393779200019702</v>
+        <v>0.27548683299937599</v>
       </c>
       <c r="R37" t="e">
         <f t="shared" si="1"/>
@@ -2958,7 +2958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>9</v>
       </c>
@@ -2974,41 +2974,41 @@
       <c r="E38" s="2">
         <v>134</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38">
         <v>4534</v>
       </c>
       <c r="G38">
         <v>10</v>
       </c>
       <c r="H38">
-        <v>283.23366526190603</v>
+        <v>494244.47502621397</v>
       </c>
       <c r="I38">
-        <v>2.3306749999392098E-2</v>
-      </c>
-      <c r="J38" s="1">
+        <v>2.33319159997336E-2</v>
+      </c>
+      <c r="J38">
         <v>246</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L38">
-        <v>23.855071083061901</v>
+        <v>504384.53274662601</v>
       </c>
       <c r="M38">
-        <v>7.3291700027760002E-4</v>
-      </c>
-      <c r="N38" s="1">
+        <v>8.3566699868240001E-4</v>
+      </c>
+      <c r="N38">
         <v>400</v>
       </c>
       <c r="O38">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P38">
-        <v>23.855071083061699</v>
+        <v>541071.97422536695</v>
       </c>
       <c r="Q38">
-        <v>6.4518625000346205E-2</v>
+        <v>0.261256415999014</v>
       </c>
       <c r="R38" t="e">
         <f t="shared" si="1"/>
@@ -3017,10 +3017,10 @@
       <c r="S38" s="1"/>
       <c r="T38">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>9</v>
       </c>
@@ -3036,7 +3036,7 @@
       <c r="E39" s="2">
         <v>144</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39">
         <v>5719</v>
       </c>
       <c r="G39">
@@ -3046,21 +3046,21 @@
         <v>1224.24714964292</v>
       </c>
       <c r="I39">
-        <v>2.7123333999043001E-2</v>
-      </c>
-      <c r="J39" s="1">
+        <v>2.73035829995933E-2</v>
+      </c>
+      <c r="J39">
         <v>5912</v>
       </c>
       <c r="K39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L39">
         <v>1330.1417823788099</v>
       </c>
       <c r="M39">
-        <v>1.3548124999942899E-2</v>
-      </c>
-      <c r="N39" s="1">
+        <v>1.3225458000306301E-2</v>
+      </c>
+      <c r="N39">
         <v>400</v>
       </c>
       <c r="O39">
@@ -3070,7 +3070,7 @@
         <v>1238.1691372530199</v>
       </c>
       <c r="Q39">
-        <v>0.3282644169999</v>
+        <v>0.32052087499869197</v>
       </c>
       <c r="R39" t="e">
         <f t="shared" si="1"/>
@@ -3082,7 +3082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>9</v>
       </c>
@@ -3098,41 +3098,41 @@
       <c r="E40" s="2">
         <v>144</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40">
         <v>5719</v>
       </c>
       <c r="G40">
         <v>10</v>
       </c>
       <c r="H40">
-        <v>148.05848912584599</v>
+        <v>154548.02973146201</v>
       </c>
       <c r="I40">
-        <v>2.91035410009499E-2</v>
-      </c>
-      <c r="J40" s="1">
-        <v>266</v>
+        <v>2.9977916999996499E-2</v>
+      </c>
+      <c r="J40">
+        <v>268</v>
       </c>
       <c r="K40">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L40">
-        <v>32.719573794235501</v>
+        <v>158055.471609595</v>
       </c>
       <c r="M40">
-        <v>8.4695900113720003E-4</v>
-      </c>
-      <c r="N40" s="1">
+        <v>1.0133329997188E-3</v>
+      </c>
+      <c r="N40">
         <v>400</v>
       </c>
       <c r="O40">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="P40">
-        <v>17.356273300478399</v>
+        <v>180426.91137606499</v>
       </c>
       <c r="Q40">
-        <v>6.8160041999817594E-2</v>
+        <v>0.28119079200041502</v>
       </c>
       <c r="R40" t="e">
         <f t="shared" si="1"/>
@@ -3144,7 +3144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>9</v>
       </c>
@@ -3160,7 +3160,7 @@
       <c r="E41" s="2">
         <v>144</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41">
         <v>5719</v>
       </c>
       <c r="G41">
@@ -3170,21 +3170,21 @@
         <v>1772.64692567458</v>
       </c>
       <c r="I41">
-        <v>2.75220420007826E-2</v>
-      </c>
-      <c r="J41" s="1">
+        <v>2.73349170001893E-2</v>
+      </c>
+      <c r="J41">
         <v>1685</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41">
         <v>1906.9925842160401</v>
       </c>
       <c r="M41">
-        <v>3.7926660006632998E-3</v>
-      </c>
-      <c r="N41" s="1">
+        <v>3.6908330002916002E-3</v>
+      </c>
+      <c r="N41">
         <v>400</v>
       </c>
       <c r="O41">
@@ -3194,7 +3194,7 @@
         <v>1781.3594327082101</v>
       </c>
       <c r="Q41">
-        <v>0.24056537499973199</v>
+        <v>0.24054808399887401</v>
       </c>
       <c r="R41" t="e">
         <f t="shared" si="1"/>
@@ -3206,7 +3206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>9</v>
       </c>
@@ -3222,41 +3222,41 @@
       <c r="E42" s="2">
         <v>144</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F42">
         <v>5719</v>
       </c>
       <c r="G42">
         <v>10</v>
       </c>
       <c r="H42">
-        <v>1102.2227488532201</v>
+        <v>10301621.8973394</v>
       </c>
       <c r="I42">
-        <v>3.0110792000414201E-2</v>
-      </c>
-      <c r="J42" s="1">
+        <v>3.1151500001214999E-2</v>
+      </c>
+      <c r="J42">
         <v>266</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L42">
-        <v>61.7260773958089</v>
+        <v>11968590.3256057</v>
       </c>
       <c r="M42">
-        <v>8.0808399980010005E-4</v>
-      </c>
-      <c r="N42" s="1">
+        <v>9.8362499920759991E-4</v>
+      </c>
+      <c r="N42">
         <v>400</v>
       </c>
       <c r="O42">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="P42">
-        <v>61.726077395808701</v>
+        <v>12145614.6703711</v>
       </c>
       <c r="Q42">
-        <v>6.8534250000084201E-2</v>
+        <v>0.28888941700097298</v>
       </c>
       <c r="R42" t="e">
         <f t="shared" si="1"/>
@@ -3268,7 +3268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -3284,7 +3284,7 @@
       <c r="E43" s="2">
         <v>126</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F43">
         <v>3658</v>
       </c>
       <c r="G43">
@@ -3294,21 +3294,21 @@
         <v>1504.0408442484299</v>
       </c>
       <c r="I43">
-        <v>1.7659916999036698E-2</v>
-      </c>
-      <c r="J43" s="1">
+        <v>1.78087500007677E-2</v>
+      </c>
+      <c r="J43">
         <v>2793</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43">
         <v>1577.0242400668201</v>
       </c>
       <c r="M43">
-        <v>6.3067089995456002E-3</v>
-      </c>
-      <c r="N43" s="1">
+        <v>6.1859159995946997E-3</v>
+      </c>
+      <c r="N43">
         <v>400</v>
       </c>
       <c r="O43">
@@ -3318,7 +3318,7 @@
         <v>1531.6239044956701</v>
       </c>
       <c r="Q43">
-        <v>0.25763295799970298</v>
+        <v>0.26188520800133103</v>
       </c>
       <c r="R43" t="e">
         <f t="shared" si="1"/>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>9</v>
       </c>
@@ -3346,45 +3346,45 @@
       <c r="E44" s="2">
         <v>126</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F44">
         <v>3658</v>
       </c>
       <c r="G44">
         <v>10</v>
       </c>
       <c r="H44">
-        <v>908.56816963772303</v>
+        <v>4823474.99959986</v>
       </c>
       <c r="I44">
-        <v>1.7593417000170999E-2</v>
-      </c>
-      <c r="J44" s="1">
+        <v>1.8168124999647199E-2</v>
+      </c>
+      <c r="J44">
         <v>230</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L44">
-        <v>45.787848042375998</v>
+        <v>4420867.0524611296</v>
       </c>
       <c r="M44">
-        <v>7.1470799957749995E-4</v>
-      </c>
-      <c r="N44" s="1">
+        <v>7.6729099964719999E-4</v>
+      </c>
+      <c r="N44">
         <v>400</v>
       </c>
       <c r="O44">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P44">
-        <v>45.787848042376197</v>
+        <v>5256292.5589608196</v>
       </c>
       <c r="Q44">
-        <v>5.7783624999956297E-2</v>
-      </c>
-      <c r="R44" t="e">
+        <v>0.19276204200104899</v>
+      </c>
+      <c r="R44">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>8.9731481845943997E-2</v>
       </c>
       <c r="S44" s="1"/>
       <c r="T44">
@@ -3392,7 +3392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>9</v>
       </c>
@@ -3408,7 +3408,7 @@
       <c r="E45" s="2">
         <v>69</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F45">
         <v>138</v>
       </c>
       <c r="G45">
@@ -3418,21 +3418,21 @@
         <v>915.65599004713397</v>
       </c>
       <c r="I45">
-        <v>6.114589996286E-4</v>
-      </c>
-      <c r="J45" s="1">
+        <v>6.0470800053730005E-4</v>
+      </c>
+      <c r="J45">
         <v>817</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45">
         <v>941.65966425305203</v>
       </c>
       <c r="M45">
-        <v>1.8854579993785E-3</v>
-      </c>
-      <c r="N45" s="1">
+        <v>1.9147500006511001E-3</v>
+      </c>
+      <c r="N45">
         <v>400</v>
       </c>
       <c r="O45">
@@ -3442,7 +3442,7 @@
         <v>924.19287834171098</v>
       </c>
       <c r="Q45">
-        <v>7.5617417000103104E-2</v>
+        <v>7.8482249999069595E-2</v>
       </c>
       <c r="R45" t="e">
         <f t="shared" si="1"/>
@@ -3454,7 +3454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>9</v>
       </c>
@@ -3470,41 +3470,41 @@
       <c r="E46" s="2">
         <v>69</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F46">
         <v>138</v>
       </c>
       <c r="G46">
         <v>8</v>
       </c>
       <c r="H46">
-        <v>1813.7011639406701</v>
+        <v>13856866.945568999</v>
       </c>
       <c r="I46">
-        <v>6.7149999995299995E-4</v>
-      </c>
-      <c r="J46" s="1">
+        <v>6.9891700150029996E-4</v>
+      </c>
+      <c r="J46">
         <v>116</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46">
-        <v>107.509798893568</v>
+        <v>6624753.6796798697</v>
       </c>
       <c r="M46">
-        <v>3.5845799902739999E-4</v>
-      </c>
-      <c r="N46" s="1">
+        <v>3.964169991377E-4</v>
+      </c>
+      <c r="N46">
         <v>400</v>
       </c>
       <c r="O46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P46">
-        <v>107.509798893568</v>
+        <v>9239132.7511802204</v>
       </c>
       <c r="Q46">
-        <v>3.03250410001965E-2</v>
+        <v>7.45229160002054E-2</v>
       </c>
       <c r="R46" t="e">
         <f t="shared" si="1"/>
@@ -3516,7 +3516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>9</v>
       </c>
@@ -3532,7 +3532,7 @@
       <c r="E47" s="2">
         <v>69</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F47">
         <v>138</v>
       </c>
       <c r="G47">
@@ -3542,21 +3542,21 @@
         <v>847.27541123226297</v>
       </c>
       <c r="I47">
-        <v>6.0466700051619996E-4</v>
-      </c>
-      <c r="J47" s="1">
+        <v>6.0958300127820001E-4</v>
+      </c>
+      <c r="J47">
         <v>161</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47">
         <v>856.00637356914899</v>
       </c>
       <c r="M47">
-        <v>4.1216699901260002E-4</v>
-      </c>
-      <c r="N47" s="1">
+        <v>4.2516699977560002E-4</v>
+      </c>
+      <c r="N47">
         <v>400</v>
       </c>
       <c r="O47">
@@ -3566,7 +3566,7 @@
         <v>856.00637356914899</v>
       </c>
       <c r="Q47">
-        <v>4.1321958000025902E-2</v>
+        <v>4.14049579994753E-2</v>
       </c>
       <c r="R47" t="e">
         <f t="shared" si="1"/>
@@ -3578,7 +3578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>9</v>
       </c>
@@ -3594,41 +3594,41 @@
       <c r="E48" s="2">
         <v>69</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F48">
         <v>138</v>
       </c>
       <c r="G48">
         <v>8</v>
       </c>
       <c r="H48">
-        <v>1028.2235594624599</v>
+        <v>3980739.4069506298</v>
       </c>
       <c r="I48">
-        <v>6.7841599957309999E-4</v>
-      </c>
-      <c r="J48" s="1">
+        <v>7.059580002533E-4</v>
+      </c>
+      <c r="J48">
         <v>116</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48">
-        <v>57.795214403496999</v>
+        <v>1914508.92144346</v>
       </c>
       <c r="M48">
-        <v>3.61749998774E-4</v>
-      </c>
-      <c r="N48" s="1">
+        <v>4.0550000085199999E-4</v>
+      </c>
+      <c r="N48">
         <v>400</v>
       </c>
       <c r="O48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P48">
-        <v>57.795214403496999</v>
+        <v>3114042.6652768902</v>
       </c>
       <c r="Q48">
-        <v>3.1436750000011601E-2</v>
+        <v>5.8588292000422301E-2</v>
       </c>
       <c r="R48" t="e">
         <f t="shared" si="1"/>
@@ -3640,7 +3640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>9</v>
       </c>
@@ -3656,7 +3656,7 @@
       <c r="E49" s="2">
         <v>69</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F49">
         <v>138</v>
       </c>
       <c r="G49">
@@ -3666,21 +3666,21 @@
         <v>977.61732862096596</v>
       </c>
       <c r="I49">
-        <v>6.5462500060669995E-4</v>
-      </c>
-      <c r="J49" s="1">
+        <v>6.3633299942010004E-4</v>
+      </c>
+      <c r="J49">
         <v>335</v>
       </c>
       <c r="K49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49">
         <v>993.84988286398197</v>
       </c>
       <c r="M49">
-        <v>8.1408400001230002E-4</v>
-      </c>
-      <c r="N49" s="1">
+        <v>8.0666699977880005E-4</v>
+      </c>
+      <c r="N49">
         <v>400</v>
       </c>
       <c r="O49">
@@ -3690,7 +3690,7 @@
         <v>993.84988286398197</v>
       </c>
       <c r="Q49">
-        <v>4.1569707999769799E-2</v>
+        <v>4.3659625000145703E-2</v>
       </c>
       <c r="R49" t="e">
         <f t="shared" si="1"/>
@@ -3702,7 +3702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>9</v>
       </c>
@@ -3718,41 +3718,41 @@
       <c r="E50" s="2">
         <v>69</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F50">
         <v>138</v>
       </c>
       <c r="G50">
         <v>8</v>
       </c>
       <c r="H50">
-        <v>2723.22104735638</v>
+        <v>27627101.0071069</v>
       </c>
       <c r="I50">
-        <v>6.8108400046179996E-4</v>
-      </c>
-      <c r="J50" s="1">
+        <v>6.9587500001940005E-4</v>
+      </c>
+      <c r="J50">
         <v>116</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50">
-        <v>156.92562795901699</v>
+        <v>14114366.3766068</v>
       </c>
       <c r="M50">
-        <v>3.6700000055129998E-4</v>
-      </c>
-      <c r="N50" s="1">
+        <v>3.9174999983510001E-4</v>
+      </c>
+      <c r="N50">
         <v>400</v>
       </c>
       <c r="O50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P50">
-        <v>156.92562795901699</v>
+        <v>19021975.947312899</v>
       </c>
       <c r="Q50">
-        <v>3.0280957999821102E-2</v>
+        <v>6.3336666999020894E-2</v>
       </c>
       <c r="R50" t="e">
         <f t="shared" si="1"/>
@@ -3764,7 +3764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>9</v>
       </c>
@@ -3780,7 +3780,7 @@
       <c r="E51" s="2">
         <v>126</v>
       </c>
-      <c r="F51" s="1">
+      <c r="F51">
         <v>3658</v>
       </c>
       <c r="G51">
@@ -3790,21 +3790,21 @@
         <v>1375.4809083596399</v>
       </c>
       <c r="I51">
-        <v>1.6591542000242002E-2</v>
-      </c>
-      <c r="J51" s="1">
+        <v>1.6450416998850401E-2</v>
+      </c>
+      <c r="J51">
         <v>2717</v>
       </c>
       <c r="K51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L51">
         <v>1438.38251392148</v>
       </c>
       <c r="M51">
-        <v>6.1474590002034996E-3</v>
-      </c>
-      <c r="N51" s="1">
+        <v>6.0331659988150004E-3</v>
+      </c>
+      <c r="N51">
         <v>400</v>
       </c>
       <c r="O51">
@@ -3814,7 +3814,7 @@
         <v>1398.88497804077</v>
       </c>
       <c r="Q51">
-        <v>0.19026974999997001</v>
+        <v>0.19513420800103601</v>
       </c>
       <c r="R51" t="e">
         <f t="shared" si="1"/>
@@ -3826,7 +3826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>9</v>
       </c>
@@ -3842,45 +3842,45 @@
       <c r="E52" s="2">
         <v>126</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F52">
         <v>3658</v>
       </c>
       <c r="G52">
         <v>10</v>
       </c>
       <c r="H52">
-        <v>522.74138639523801</v>
+        <v>2215432.1141809798</v>
       </c>
       <c r="I52">
-        <v>1.7620208000153001E-2</v>
-      </c>
-      <c r="J52" s="1">
+        <v>1.8260792001456101E-2</v>
+      </c>
+      <c r="J52">
         <v>230</v>
       </c>
       <c r="K52">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L52">
-        <v>41.882475058996398</v>
+        <v>2105605.3664561701</v>
       </c>
       <c r="M52">
-        <v>7.0658399999949998E-4</v>
-      </c>
-      <c r="N52" s="1">
+        <v>8.0204199912249999E-4</v>
+      </c>
+      <c r="N52">
         <v>400</v>
       </c>
       <c r="O52">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P52">
-        <v>41.882475058996</v>
+        <v>2686889.44769195</v>
       </c>
       <c r="Q52">
-        <v>6.0836458000267102E-2</v>
-      </c>
-      <c r="R52" t="e">
+        <v>0.16728270800012901</v>
+      </c>
+      <c r="R52">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>0.21280603927927744</v>
       </c>
       <c r="S52" s="1"/>
       <c r="T52">
@@ -3888,7 +3888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>9</v>
       </c>
@@ -3904,7 +3904,7 @@
       <c r="E53" s="2">
         <v>71</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F53">
         <v>232</v>
       </c>
       <c r="G53">
@@ -3914,21 +3914,21 @@
         <v>450.43785842526103</v>
       </c>
       <c r="I53">
-        <v>9.5099999998630004E-4</v>
-      </c>
-      <c r="J53" s="1">
+        <v>9.2308399871389999E-4</v>
+      </c>
+      <c r="J53">
         <v>1156</v>
       </c>
       <c r="K53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L53">
         <v>500.57053026950302</v>
       </c>
       <c r="M53">
-        <v>2.6201670007138999E-3</v>
-      </c>
-      <c r="N53" s="1">
+        <v>2.6844169988179999E-3</v>
+      </c>
+      <c r="N53">
         <v>400</v>
       </c>
       <c r="O53">
@@ -3938,7 +3938,7 @@
         <v>458.52154843444703</v>
       </c>
       <c r="Q53">
-        <v>0.10939058400026599</v>
+        <v>0.10918195900012501</v>
       </c>
       <c r="R53" t="e">
         <f t="shared" si="1"/>
@@ -3950,7 +3950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>9</v>
       </c>
@@ -3966,41 +3966,41 @@
       <c r="E54" s="2">
         <v>71</v>
       </c>
-      <c r="F54" s="1">
+      <c r="F54">
         <v>232</v>
       </c>
       <c r="G54">
         <v>8</v>
       </c>
       <c r="H54">
-        <v>51.543704643035802</v>
+        <v>10824.5568498634</v>
       </c>
       <c r="I54">
-        <v>1.0318749991710999E-3</v>
-      </c>
-      <c r="J54" s="1">
+        <v>1.0666250000213001E-3</v>
+      </c>
+      <c r="J54">
         <v>121</v>
       </c>
       <c r="K54">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L54">
-        <v>30.677626344310202</v>
+        <v>9110.4982211476399</v>
       </c>
       <c r="M54">
-        <v>3.991670000687E-4</v>
-      </c>
-      <c r="N54" s="1">
+        <v>4.481659998418E-4</v>
+      </c>
+      <c r="N54">
         <v>400</v>
       </c>
       <c r="O54">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P54">
-        <v>23.302874231689099</v>
+        <v>20012.6258028673</v>
       </c>
       <c r="Q54">
-        <v>5.9309167000264999E-2</v>
+        <v>7.9274708999946597E-2</v>
       </c>
       <c r="R54" t="e">
         <f t="shared" si="1"/>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>9</v>
       </c>
@@ -4028,7 +4028,7 @@
       <c r="E55" s="2">
         <v>71</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F55">
         <v>232</v>
       </c>
       <c r="G55">
@@ -4038,21 +4038,21 @@
         <v>387.41182708830797</v>
       </c>
       <c r="I55">
-        <v>9.342080011265E-4</v>
-      </c>
-      <c r="J55" s="1">
+        <v>9.4924999939389998E-4</v>
+      </c>
+      <c r="J55">
         <v>1503</v>
       </c>
       <c r="K55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L55">
         <v>458.27952521002197</v>
       </c>
       <c r="M55">
-        <v>3.4212079990538001E-3</v>
-      </c>
-      <c r="N55" s="1">
+        <v>3.4458749996701E-3</v>
+      </c>
+      <c r="N55">
         <v>400</v>
       </c>
       <c r="O55">
@@ -4062,7 +4062,7 @@
         <v>396.58083365493002</v>
       </c>
       <c r="Q55">
-        <v>9.0664708000076602E-2</v>
+        <v>9.0133916999547994E-2</v>
       </c>
       <c r="R55" t="e">
         <f t="shared" si="1"/>
@@ -4074,7 +4074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -4090,41 +4090,41 @@
       <c r="E56" s="2">
         <v>71</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F56">
         <v>232</v>
       </c>
       <c r="G56">
         <v>8</v>
       </c>
       <c r="H56">
-        <v>33.130250213412602</v>
+        <v>4114.7454736081299</v>
       </c>
       <c r="I56">
-        <v>1.0313750008208E-3</v>
-      </c>
-      <c r="J56" s="1">
-        <v>120</v>
+        <v>1.0997499994118E-3</v>
+      </c>
+      <c r="J56">
+        <v>147</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L56">
-        <v>6.1059345123766597</v>
+        <v>3472.2323724237799</v>
       </c>
       <c r="M56">
-        <v>3.732080003828E-4</v>
-      </c>
-      <c r="N56" s="1">
+        <v>4.8545800018469999E-4</v>
+      </c>
+      <c r="N56">
         <v>400</v>
       </c>
       <c r="O56">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P56">
-        <v>6.1059345123744198</v>
+        <v>3625.53834281647</v>
       </c>
       <c r="Q56">
-        <v>3.1468041999687502E-2</v>
+        <v>8.3258583001224906E-2</v>
       </c>
       <c r="R56" t="e">
         <f t="shared" si="1"/>
@@ -4136,7 +4136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>9</v>
       </c>
@@ -4152,7 +4152,7 @@
       <c r="E57" s="2">
         <v>71</v>
       </c>
-      <c r="F57" s="1">
+      <c r="F57">
         <v>232</v>
       </c>
       <c r="G57">
@@ -4162,21 +4162,21 @@
         <v>459.96076712762903</v>
       </c>
       <c r="I57">
-        <v>9.7879199893209992E-4</v>
-      </c>
-      <c r="J57" s="1">
+        <v>9.4366600023930002E-4</v>
+      </c>
+      <c r="J57">
         <v>1167</v>
       </c>
       <c r="K57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L57">
         <v>509.03530897036501</v>
       </c>
       <c r="M57">
-        <v>2.6698330002544999E-3</v>
-      </c>
-      <c r="N57" s="1">
+        <v>2.6542499999777001E-3</v>
+      </c>
+      <c r="N57">
         <v>400</v>
       </c>
       <c r="O57">
@@ -4186,7 +4186,7 @@
         <v>464.482797689569</v>
       </c>
       <c r="Q57">
-        <v>8.1516166999790501E-2</v>
+        <v>8.1695625000065705E-2</v>
       </c>
       <c r="R57" t="e">
         <f t="shared" si="1"/>
@@ -4198,7 +4198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>9</v>
       </c>
@@ -4214,41 +4214,41 @@
       <c r="E58" s="2">
         <v>71</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F58">
         <v>232</v>
       </c>
       <c r="G58">
         <v>8</v>
       </c>
       <c r="H58">
-        <v>60.886257111228602</v>
+        <v>16258.050208762001</v>
       </c>
       <c r="I58">
-        <v>1.0450000008859E-3</v>
-      </c>
-      <c r="J58" s="1">
-        <v>120</v>
+        <v>1.0813750013767001E-3</v>
+      </c>
+      <c r="J58">
+        <v>122</v>
       </c>
       <c r="K58">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L58">
-        <v>17.500498384772101</v>
+        <v>12520.8522644599</v>
       </c>
       <c r="M58">
-        <v>3.7545800114449998E-4</v>
-      </c>
-      <c r="N58" s="1">
+        <v>4.1691700062069999E-4</v>
+      </c>
+      <c r="N58">
         <v>400</v>
       </c>
       <c r="O58">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P58">
-        <v>17.5004983847715</v>
+        <v>19005.353585021501</v>
       </c>
       <c r="Q58">
-        <v>3.2420416000149999E-2</v>
+        <v>6.50142089998553E-2</v>
       </c>
       <c r="R58" t="e">
         <f t="shared" si="1"/>
@@ -4260,7 +4260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>9</v>
       </c>
@@ -4276,7 +4276,7 @@
       <c r="E59" s="2">
         <v>71</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F59">
         <v>232</v>
       </c>
       <c r="G59">
@@ -4286,21 +4286,21 @@
         <v>540.53443981439204</v>
       </c>
       <c r="I59">
-        <v>9.4416700085269995E-4</v>
-      </c>
-      <c r="J59" s="1">
+        <v>9.1312499898770004E-4</v>
+      </c>
+      <c r="J59">
         <v>1525</v>
       </c>
       <c r="K59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L59">
         <v>596.302177540564</v>
       </c>
       <c r="M59">
-        <v>3.4311670005990002E-3</v>
-      </c>
-      <c r="N59" s="1">
+        <v>3.4542920002421998E-3</v>
+      </c>
+      <c r="N59">
         <v>400</v>
       </c>
       <c r="O59">
@@ -4310,7 +4310,7 @@
         <v>581.64616476453205</v>
       </c>
       <c r="Q59">
-        <v>9.2703209000319406E-2</v>
+        <v>9.31100420002621E-2</v>
       </c>
       <c r="R59" t="e">
         <f t="shared" si="1"/>
@@ -4322,7 +4322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>9</v>
       </c>
@@ -4338,41 +4338,41 @@
       <c r="E60" s="2">
         <v>71</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F60">
         <v>232</v>
       </c>
       <c r="G60">
         <v>8</v>
       </c>
       <c r="H60">
-        <v>113.349495401045</v>
+        <v>47585.287872294299</v>
       </c>
       <c r="I60">
-        <v>1.0385000005044001E-3</v>
-      </c>
-      <c r="J60" s="1">
-        <v>120</v>
+        <v>1.0694169995986E-3</v>
+      </c>
+      <c r="J60">
+        <v>122</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L60">
-        <v>15.938366781648799</v>
+        <v>40901.734583231198</v>
       </c>
       <c r="M60">
-        <v>3.933340012736E-4</v>
-      </c>
-      <c r="N60" s="1">
+        <v>4.3054100024159998E-4</v>
+      </c>
+      <c r="N60">
         <v>400</v>
       </c>
       <c r="O60">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P60">
-        <v>15.938366781650499</v>
+        <v>49033.9944147961</v>
       </c>
       <c r="Q60">
-        <v>3.1038916999932501E-2</v>
+        <v>8.0660125000576899E-2</v>
       </c>
       <c r="R60" t="e">
         <f t="shared" si="1"/>
@@ -4384,7 +4384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -4400,7 +4400,7 @@
       <c r="E61" s="2">
         <v>120</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F61">
         <v>3043</v>
       </c>
       <c r="G61">
@@ -4410,21 +4410,21 @@
         <v>1786.9845091484799</v>
       </c>
       <c r="I61">
-        <v>1.3585499998953299E-2</v>
-      </c>
-      <c r="J61" s="1">
+        <v>1.36995409993687E-2</v>
+      </c>
+      <c r="J61">
         <v>475</v>
       </c>
       <c r="K61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61">
         <v>1819.1989045335499</v>
       </c>
       <c r="M61">
-        <v>1.1531670006661001E-3</v>
-      </c>
-      <c r="N61" s="1">
+        <v>1.1733330011338E-3</v>
+      </c>
+      <c r="N61">
         <v>400</v>
       </c>
       <c r="O61">
@@ -4434,7 +4434,7 @@
         <v>1819.1989045335499</v>
       </c>
       <c r="Q61">
-        <v>7.5487624999823297E-2</v>
+        <v>8.0342082999777603E-2</v>
       </c>
       <c r="R61" t="e">
         <f t="shared" si="1"/>
@@ -4446,7 +4446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>9</v>
       </c>
@@ -4462,41 +4462,41 @@
       <c r="E62" s="2">
         <v>120</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F62">
         <v>3043</v>
       </c>
       <c r="G62">
         <v>10</v>
       </c>
       <c r="H62">
-        <v>4000.3929917128598</v>
+        <v>78114240.486692399</v>
       </c>
       <c r="I62">
-        <v>1.46728340005211E-2</v>
-      </c>
-      <c r="J62" s="1">
+        <v>1.5033416999358401E-2</v>
+      </c>
+      <c r="J62">
         <v>218</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62">
-        <v>175.84147826557</v>
+        <v>40645691.946688302</v>
       </c>
       <c r="M62">
-        <v>6.6449999940229999E-4</v>
-      </c>
-      <c r="N62" s="1">
+        <v>7.0724999932280004E-4</v>
+      </c>
+      <c r="N62">
         <v>400</v>
       </c>
       <c r="O62">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P62">
-        <v>175.84147826557</v>
+        <v>77062138.563849106</v>
       </c>
       <c r="Q62">
-        <v>5.6404792000193903E-2</v>
+        <v>0.16642608300025999</v>
       </c>
       <c r="R62" t="e">
         <f t="shared" si="1"/>
@@ -4508,7 +4508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>48</v>
       </c>
@@ -4524,7 +4524,7 @@
       <c r="E63" s="2">
         <v>126</v>
       </c>
-      <c r="F63" s="1">
+      <c r="F63">
         <v>3658</v>
       </c>
       <c r="G63">
@@ -4534,21 +4534,21 @@
         <v>1189.48196931864</v>
       </c>
       <c r="I63">
-        <v>1.75852499996835E-2</v>
-      </c>
-      <c r="J63" s="1">
+        <v>1.7930957999851602E-2</v>
+      </c>
+      <c r="J63">
         <v>4071</v>
       </c>
       <c r="K63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L63">
         <v>1371.61975136554</v>
       </c>
       <c r="M63">
-        <v>9.2457089995150003E-3</v>
-      </c>
-      <c r="N63" s="1">
+        <v>8.9517500000510994E-3</v>
+      </c>
+      <c r="N63">
         <v>400</v>
       </c>
       <c r="O63">
@@ -4558,7 +4558,7 @@
         <v>1196.2922916704499</v>
       </c>
       <c r="Q63">
-        <v>0.28444370799979801</v>
+        <v>0.28249949999917501</v>
       </c>
       <c r="R63" t="e">
         <f t="shared" si="1"/>
@@ -4570,7 +4570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>48</v>
       </c>
@@ -4586,41 +4586,41 @@
       <c r="E64" s="2">
         <v>126</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F64">
         <v>3658</v>
       </c>
       <c r="G64">
         <v>10</v>
       </c>
       <c r="H64">
-        <v>243.45017386389</v>
+        <v>461964.02772322099</v>
       </c>
       <c r="I64">
-        <v>1.75187499989988E-2</v>
-      </c>
-      <c r="J64" s="1">
-        <v>231</v>
+        <v>1.82332080003106E-2</v>
+      </c>
+      <c r="J64">
+        <v>230</v>
       </c>
       <c r="K64">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L64">
-        <v>124.087143554593</v>
+        <v>394179.16099193197</v>
       </c>
       <c r="M64">
-        <v>7.0791699909019995E-4</v>
-      </c>
-      <c r="N64" s="1">
+        <v>7.7837500066379995E-4</v>
+      </c>
+      <c r="N64">
         <v>400</v>
       </c>
       <c r="O64">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P64">
-        <v>150.75703693435599</v>
+        <v>583506.99851844402</v>
       </c>
       <c r="Q64">
-        <v>0.18333408399985199</v>
+        <v>0.218617124999582</v>
       </c>
       <c r="R64" t="e">
         <f t="shared" si="1"/>
@@ -4632,7 +4632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>48</v>
       </c>
@@ -4648,7 +4648,7 @@
       <c r="E65" s="2">
         <v>111</v>
       </c>
-      <c r="F65" s="1">
+      <c r="F65">
         <v>2188</v>
       </c>
       <c r="G65">
@@ -4658,21 +4658,21 @@
         <v>1300.28079069093</v>
       </c>
       <c r="I65">
-        <v>9.5443329992121999E-3</v>
-      </c>
-      <c r="J65" s="1">
+        <v>9.5406249984079997E-3</v>
+      </c>
+      <c r="J65">
         <v>2647</v>
       </c>
       <c r="K65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L65">
         <v>1412.4797426438799</v>
       </c>
       <c r="M65">
-        <v>5.9364999997342004E-3</v>
-      </c>
-      <c r="N65" s="1">
+        <v>6.0713750008288998E-3</v>
+      </c>
+      <c r="N65">
         <v>400</v>
       </c>
       <c r="O65">
@@ -4682,7 +4682,7 @@
         <v>1375.9214917992999</v>
       </c>
       <c r="Q65">
-        <v>0.21408041699987701</v>
+        <v>0.21021466700040001</v>
       </c>
       <c r="R65" t="e">
         <f t="shared" si="1"/>
@@ -4694,7 +4694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>48</v>
       </c>
@@ -4710,41 +4710,41 @@
       <c r="E66" s="2">
         <v>111</v>
       </c>
-      <c r="F66" s="1">
+      <c r="F66">
         <v>2188</v>
       </c>
       <c r="G66">
         <v>10</v>
       </c>
       <c r="H66">
-        <v>1280.03027432115</v>
+        <v>16415998.7825213</v>
       </c>
       <c r="I66">
-        <v>1.00625830000353E-2</v>
-      </c>
-      <c r="J66" s="1">
+        <v>1.0387708000052899E-2</v>
+      </c>
+      <c r="J66">
         <v>200</v>
       </c>
       <c r="K66">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L66">
-        <v>418.16057244954999</v>
+        <v>16213545.0827196</v>
       </c>
       <c r="M66">
-        <v>6.2612500005340005E-4</v>
-      </c>
-      <c r="N66" s="1">
+        <v>7.3208399953719999E-4</v>
+      </c>
+      <c r="N66">
         <v>400</v>
       </c>
       <c r="O66">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="P66">
-        <v>1031.5486451408201</v>
+        <v>16479193.3115055</v>
       </c>
       <c r="Q66">
-        <v>0.152203542000279</v>
+        <v>0.17715504100124199</v>
       </c>
       <c r="R66" t="e">
         <f t="shared" si="1"/>
@@ -4756,7 +4756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>48</v>
       </c>
@@ -4772,7 +4772,7 @@
       <c r="E67" s="2">
         <v>115</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F67">
         <v>2558</v>
       </c>
       <c r="G67">
@@ -4782,21 +4782,21 @@
         <v>931.723500984363</v>
       </c>
       <c r="I67">
-        <v>1.10621669991815E-2</v>
-      </c>
-      <c r="J67" s="1">
+        <v>1.11281250010506E-2</v>
+      </c>
+      <c r="J67">
         <v>2394</v>
       </c>
       <c r="K67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L67">
         <v>985.39166772190197</v>
       </c>
       <c r="M67">
-        <v>5.3026669993413997E-3</v>
-      </c>
-      <c r="N67" s="1">
+        <v>5.3587909987982E-3</v>
+      </c>
+      <c r="N67">
         <v>400</v>
       </c>
       <c r="O67">
@@ -4806,7 +4806,7 @@
         <v>958.25285532728606</v>
       </c>
       <c r="Q67">
-        <v>0.158123624999916</v>
+        <v>0.155751333999432</v>
       </c>
       <c r="R67" t="e">
         <f t="shared" si="1"/>
@@ -4818,7 +4818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>48</v>
       </c>
@@ -4834,41 +4834,41 @@
       <c r="E68" s="2">
         <v>115</v>
       </c>
-      <c r="F68" s="1">
+      <c r="F68">
         <v>2558</v>
       </c>
       <c r="G68">
         <v>10</v>
       </c>
       <c r="H68">
-        <v>139.339677348127</v>
+        <v>96655.893924084099</v>
       </c>
       <c r="I68">
-        <v>1.1937458000829701E-2</v>
-      </c>
-      <c r="J68" s="1">
-        <v>208</v>
+        <v>1.24721249994763E-2</v>
+      </c>
+      <c r="J68">
+        <v>209</v>
       </c>
       <c r="K68">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L68">
-        <v>9.5227543280621294</v>
+        <v>98551.121210789206</v>
       </c>
       <c r="M68">
-        <v>6.3308400058300002E-4</v>
-      </c>
-      <c r="N68" s="1">
+        <v>7.0450000021079996E-4</v>
+      </c>
+      <c r="N68">
         <v>400</v>
       </c>
       <c r="O68">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P68">
-        <v>9.5227543280357594</v>
+        <v>111300.206786426</v>
       </c>
       <c r="Q68">
-        <v>5.2448833000198598E-2</v>
+        <v>0.17224775000067799</v>
       </c>
       <c r="R68" t="e">
         <f t="shared" ref="R68:R131" si="3">IF(O68=G68,(P68-H68)/H68,NA())</f>
@@ -4880,7 +4880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>48</v>
       </c>
@@ -4896,7 +4896,7 @@
       <c r="E69" s="2">
         <v>122</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F69">
         <v>3244</v>
       </c>
       <c r="G69">
@@ -4906,21 +4906,21 @@
         <v>1238.03234706644</v>
       </c>
       <c r="I69">
-        <v>1.46065000008093E-2</v>
-      </c>
-      <c r="J69" s="1">
+        <v>1.45649589994718E-2</v>
+      </c>
+      <c r="J69">
         <v>2478</v>
       </c>
       <c r="K69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L69">
         <v>1401.69122069022</v>
       </c>
       <c r="M69">
-        <v>5.6899169994721003E-3</v>
-      </c>
-      <c r="N69" s="1">
+        <v>5.6089999998221E-3</v>
+      </c>
+      <c r="N69">
         <v>400</v>
       </c>
       <c r="O69">
@@ -4930,7 +4930,7 @@
         <v>1305.0818163065701</v>
       </c>
       <c r="Q69">
-        <v>0.19659437500013099</v>
+        <v>0.19755254200026601</v>
       </c>
       <c r="R69" t="e">
         <f t="shared" si="3"/>
@@ -4942,7 +4942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>48</v>
       </c>
@@ -4958,41 +4958,41 @@
       <c r="E70" s="2">
         <v>122</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F70">
         <v>3244</v>
       </c>
       <c r="G70">
         <v>10</v>
       </c>
       <c r="H70">
-        <v>411.48273921183198</v>
+        <v>2070250.1479766199</v>
       </c>
       <c r="I70">
-        <v>1.5521541999987599E-2</v>
-      </c>
-      <c r="J70" s="1">
+        <v>1.58907499990164E-2</v>
+      </c>
+      <c r="J70">
         <v>222</v>
       </c>
       <c r="K70">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L70">
-        <v>160.28592989290999</v>
+        <v>2215131.0865964298</v>
       </c>
       <c r="M70">
-        <v>6.8883399944750004E-4</v>
-      </c>
-      <c r="N70" s="1">
+        <v>8.1437500011809997E-4</v>
+      </c>
+      <c r="N70">
         <v>400</v>
       </c>
       <c r="O70">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P70">
-        <v>330.49641326308603</v>
+        <v>2219282.6686471398</v>
       </c>
       <c r="Q70">
-        <v>0.14848445899997301</v>
+        <v>0.17162245799954601</v>
       </c>
       <c r="R70" t="e">
         <f t="shared" si="3"/>
@@ -5004,7 +5004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>48</v>
       </c>
@@ -5020,7 +5020,7 @@
       <c r="E71" s="2">
         <v>735</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F71">
         <v>253348</v>
       </c>
       <c r="G71">
@@ -5030,21 +5030,21 @@
         <v>5440.7021329514901</v>
       </c>
       <c r="I71">
-        <v>2.48874450000039</v>
-      </c>
-      <c r="J71" s="1">
+        <v>2.51493483300146</v>
+      </c>
+      <c r="J71">
         <v>22120</v>
       </c>
       <c r="K71">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L71">
         <v>4440.2728923094701</v>
       </c>
       <c r="M71">
-        <v>5.5187291000038302E-2</v>
-      </c>
-      <c r="N71" s="1">
+        <v>5.6169250001403201E-2</v>
+      </c>
+      <c r="N71">
         <v>400</v>
       </c>
       <c r="O71">
@@ -5054,7 +5054,7 @@
         <v>3963.7235949573501</v>
       </c>
       <c r="Q71">
-        <v>2.9134759580001601</v>
+        <v>2.9447854579993802</v>
       </c>
       <c r="R71" t="e">
         <f t="shared" si="3"/>
@@ -5066,7 +5066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>48</v>
       </c>
@@ -5082,41 +5082,41 @@
       <c r="E72" s="2">
         <v>735</v>
       </c>
-      <c r="F72" s="1">
+      <c r="F72">
         <v>253348</v>
       </c>
       <c r="G72">
         <v>10</v>
       </c>
       <c r="H72">
-        <v>27.6105030652989</v>
+        <v>159756.80109332799</v>
       </c>
       <c r="I72">
-        <v>2.6532067499992902</v>
-      </c>
-      <c r="J72" s="1">
-        <v>1455</v>
+        <v>2.63040854200153</v>
+      </c>
+      <c r="J72">
+        <v>1768</v>
       </c>
       <c r="K72">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="L72">
-        <v>51.859168811490903</v>
+        <v>45897.899325161001</v>
       </c>
       <c r="M72">
-        <v>4.5707910012423997E-3</v>
-      </c>
-      <c r="N72" s="1">
+        <v>6.4295000011043001E-3</v>
+      </c>
+      <c r="N72">
         <v>400</v>
       </c>
       <c r="O72">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="P72">
-        <v>16.951850113484301</v>
+        <v>65094.909890348499</v>
       </c>
       <c r="Q72">
-        <v>0.71025987499979204</v>
+        <v>2.3668349580002501</v>
       </c>
       <c r="R72" t="e">
         <f t="shared" si="3"/>
@@ -5128,7 +5128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>48</v>
       </c>
@@ -5144,7 +5144,7 @@
       <c r="E73" s="2">
         <v>136</v>
       </c>
-      <c r="F73" s="1">
+      <c r="F73">
         <v>4763</v>
       </c>
       <c r="G73">
@@ -5154,21 +5154,21 @@
         <v>1327.73514340783</v>
       </c>
       <c r="I73">
-        <v>2.3380915999950899E-2</v>
-      </c>
-      <c r="J73" s="1">
+        <v>2.4079167000309099E-2</v>
+      </c>
+      <c r="J73">
         <v>3083</v>
       </c>
       <c r="K73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L73">
         <v>1415.3597817375601</v>
       </c>
       <c r="M73">
-        <v>7.0712079996155001E-3</v>
-      </c>
-      <c r="N73" s="1">
+        <v>6.9386249997478002E-3</v>
+      </c>
+      <c r="N73">
         <v>400</v>
       </c>
       <c r="O73">
@@ -5178,7 +5178,7 @@
         <v>1345.8224238970799</v>
       </c>
       <c r="Q73">
-        <v>0.25321458300004401</v>
+        <v>0.25347516699912298</v>
       </c>
       <c r="R73">
         <f t="shared" si="3"/>
@@ -5190,7 +5190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>48</v>
       </c>
@@ -5206,41 +5206,41 @@
       <c r="E74" s="2">
         <v>136</v>
       </c>
-      <c r="F74" s="1">
+      <c r="F74">
         <v>4763</v>
       </c>
       <c r="G74">
         <v>10</v>
       </c>
       <c r="H74">
-        <v>278.01964572696102</v>
+        <v>2771588.3404962802</v>
       </c>
       <c r="I74">
-        <v>2.36000830009288E-2</v>
-      </c>
-      <c r="J74" s="1">
-        <v>250</v>
+        <v>2.5001542000609299E-2</v>
+      </c>
+      <c r="J74">
+        <v>251</v>
       </c>
       <c r="K74">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L74">
-        <v>47.766076107605699</v>
+        <v>3035177.0418911302</v>
       </c>
       <c r="M74">
-        <v>7.5141600063939997E-4</v>
-      </c>
-      <c r="N74" s="1">
+        <v>8.6237499999690002E-4</v>
+      </c>
+      <c r="N74">
         <v>400</v>
       </c>
       <c r="O74">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="P74">
-        <v>47.766076107605699</v>
+        <v>3097731.0785584198</v>
       </c>
       <c r="Q74">
-        <v>6.4283041999715296E-2</v>
+        <v>0.24281333300132199</v>
       </c>
       <c r="R74" t="e">
         <f t="shared" si="3"/>
@@ -5252,7 +5252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>48</v>
       </c>
@@ -5268,7 +5268,7 @@
       <c r="E75" s="2">
         <v>116</v>
       </c>
-      <c r="F75" s="1">
+      <c r="F75">
         <v>2653</v>
       </c>
       <c r="G75">
@@ -5278,21 +5278,21 @@
         <v>518.34831617008797</v>
       </c>
       <c r="I75">
-        <v>1.1779959000705199E-2</v>
-      </c>
-      <c r="J75" s="1">
+        <v>1.15955410001333E-2</v>
+      </c>
+      <c r="J75">
         <v>2063</v>
       </c>
       <c r="K75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L75">
         <v>668.45667378733106</v>
       </c>
       <c r="M75">
-        <v>4.7998749996622002E-3</v>
-      </c>
-      <c r="N75" s="1">
+        <v>4.8716250003053001E-3</v>
+      </c>
+      <c r="N75">
         <v>400</v>
       </c>
       <c r="O75">
@@ -5302,7 +5302,7 @@
         <v>601.120202069426</v>
       </c>
       <c r="Q75">
-        <v>0.18443308299993</v>
+        <v>0.18682537499989799</v>
       </c>
       <c r="R75" t="e">
         <f t="shared" si="3"/>
@@ -5314,7 +5314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>48</v>
       </c>
@@ -5330,53 +5330,53 @@
       <c r="E76" s="2">
         <v>116</v>
       </c>
-      <c r="F76" s="1">
+      <c r="F76">
         <v>2653</v>
       </c>
       <c r="G76">
         <v>10</v>
       </c>
       <c r="H76">
-        <v>37.780207245815397</v>
+        <v>13588.339085126499</v>
       </c>
       <c r="I76">
-        <v>1.2403624999933501E-2</v>
-      </c>
-      <c r="J76" s="1">
-        <v>212</v>
+        <v>1.34996670003602E-2</v>
+      </c>
+      <c r="J76">
+        <v>521</v>
       </c>
       <c r="K76">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L76">
-        <v>50.434940462628198</v>
+        <v>13588.339085126499</v>
       </c>
       <c r="M76">
-        <v>6.5466700107199996E-4</v>
-      </c>
-      <c r="N76" s="1">
+        <v>1.6224589999183001E-3</v>
+      </c>
+      <c r="N76">
         <v>400</v>
       </c>
       <c r="O76">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="P76">
-        <v>39.416464198626997</v>
+        <v>29331.651240426199</v>
       </c>
       <c r="Q76">
-        <v>0.117447874999925</v>
-      </c>
-      <c r="R76" t="e">
+        <v>0.14531579100003</v>
+      </c>
+      <c r="R76">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>1.1585898803873673</v>
       </c>
       <c r="S76" s="1"/>
       <c r="T76">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>48</v>
       </c>
@@ -5392,7 +5392,7 @@
       <c r="E77" s="2">
         <v>123</v>
       </c>
-      <c r="F77" s="1">
+      <c r="F77">
         <v>3346</v>
       </c>
       <c r="G77">
@@ -5402,21 +5402,21 @@
         <v>1335.6099523795999</v>
       </c>
       <c r="I77">
-        <v>1.7157791999125E-2</v>
-      </c>
-      <c r="J77" s="1">
+        <v>1.81891660013207E-2</v>
+      </c>
+      <c r="J77">
         <v>2116</v>
       </c>
       <c r="K77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L77">
         <v>1461.7521017951999</v>
       </c>
       <c r="M77">
-        <v>4.7672919990872998E-3</v>
-      </c>
-      <c r="N77" s="1">
+        <v>4.7165830001176003E-3</v>
+      </c>
+      <c r="N77">
         <v>400</v>
       </c>
       <c r="O77">
@@ -5426,7 +5426,7 @@
         <v>1329.1768687296501</v>
       </c>
       <c r="Q77">
-        <v>0.20745704199998699</v>
+        <v>0.21196224999948701</v>
       </c>
       <c r="R77" t="e">
         <f t="shared" si="3"/>
@@ -5438,7 +5438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>48</v>
       </c>
@@ -5454,41 +5454,41 @@
       <c r="E78" s="2">
         <v>123</v>
       </c>
-      <c r="F78" s="1">
+      <c r="F78">
         <v>3346</v>
       </c>
       <c r="G78">
         <v>10</v>
       </c>
       <c r="H78">
-        <v>781.14457615011997</v>
+        <v>5881539.8103872798</v>
       </c>
       <c r="I78">
-        <v>1.5989916999387701E-2</v>
-      </c>
-      <c r="J78" s="1">
+        <v>1.6561832999286701E-2</v>
+      </c>
+      <c r="J78">
         <v>224</v>
       </c>
       <c r="K78">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L78">
-        <v>546.70127664785105</v>
+        <v>5765924.48832718</v>
       </c>
       <c r="M78">
-        <v>7.0254099955489998E-4</v>
-      </c>
-      <c r="N78" s="1">
+        <v>8.0274999891109995E-4</v>
+      </c>
+      <c r="N78">
         <v>400</v>
       </c>
       <c r="O78">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P78">
-        <v>912.06545788685105</v>
+        <v>16123058.864799701</v>
       </c>
       <c r="Q78">
-        <v>0.15224995800008401</v>
+        <v>0.15703524999844301</v>
       </c>
       <c r="R78" t="e">
         <f t="shared" si="3"/>
@@ -5500,7 +5500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>48</v>
       </c>
@@ -5516,7 +5516,7 @@
       <c r="E79" s="2">
         <v>117</v>
       </c>
-      <c r="F79" s="1">
+      <c r="F79">
         <v>2749</v>
       </c>
       <c r="G79">
@@ -5526,21 +5526,21 @@
         <v>690.47822581320702</v>
       </c>
       <c r="I79">
-        <v>1.21261250005773E-2</v>
-      </c>
-      <c r="J79" s="1">
+        <v>1.46194999997533E-2</v>
+      </c>
+      <c r="J79">
         <v>2674</v>
       </c>
       <c r="K79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L79">
         <v>813.83722281161795</v>
       </c>
       <c r="M79">
-        <v>6.1164580001786002E-3</v>
-      </c>
-      <c r="N79" s="1">
+        <v>6.1504579989558996E-3</v>
+      </c>
+      <c r="N79">
         <v>400</v>
       </c>
       <c r="O79">
@@ -5550,7 +5550,7 @@
         <v>716.12168373569898</v>
       </c>
       <c r="Q79">
-        <v>0.190566042000227</v>
+        <v>0.19168558300043501</v>
       </c>
       <c r="R79" t="e">
         <f t="shared" si="3"/>
@@ -5562,7 +5562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>48</v>
       </c>
@@ -5578,41 +5578,41 @@
       <c r="E80" s="2">
         <v>117</v>
       </c>
-      <c r="F80" s="1">
+      <c r="F80">
         <v>2749</v>
       </c>
       <c r="G80">
         <v>10</v>
       </c>
       <c r="H80">
-        <v>46.984978331236299</v>
+        <v>10437.016941493201</v>
       </c>
       <c r="I80">
-        <v>1.27968750002764E-2</v>
-      </c>
-      <c r="J80" s="1">
-        <v>212</v>
+        <v>1.3296958999490001E-2</v>
+      </c>
+      <c r="J80">
+        <v>219</v>
       </c>
       <c r="K80">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L80">
-        <v>10.855460221071199</v>
+        <v>10353.745308117301</v>
       </c>
       <c r="M80">
-        <v>6.3795799906070003E-4</v>
-      </c>
-      <c r="N80" s="1">
+        <v>7.2916699900810004E-4</v>
+      </c>
+      <c r="N80">
         <v>400</v>
       </c>
       <c r="O80">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P80">
-        <v>10.855460221071599</v>
+        <v>10967.4455344998</v>
       </c>
       <c r="Q80">
-        <v>5.42672500000662E-2</v>
+        <v>0.150139249999483</v>
       </c>
       <c r="R80" t="e">
         <f t="shared" si="3"/>
@@ -5624,7 +5624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>48</v>
       </c>
@@ -5640,7 +5640,7 @@
       <c r="E81" s="2">
         <v>738</v>
       </c>
-      <c r="F81" s="1">
+      <c r="F81">
         <v>255496</v>
       </c>
       <c r="G81">
@@ -5650,21 +5650,21 @@
         <v>6334.8321570067501</v>
       </c>
       <c r="I81">
-        <v>2.5048156669999999</v>
-      </c>
-      <c r="J81" s="1">
+        <v>2.5634080420004399</v>
+      </c>
+      <c r="J81">
         <v>30032</v>
       </c>
       <c r="K81">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L81">
         <v>5857.1387548229204</v>
       </c>
       <c r="M81">
-        <v>7.1511624999402501E-2</v>
-      </c>
-      <c r="N81" s="1">
+        <v>7.2176790999947102E-2</v>
+      </c>
+      <c r="N81">
         <v>400</v>
       </c>
       <c r="O81">
@@ -5674,7 +5674,7 @@
         <v>5207.1798242390596</v>
       </c>
       <c r="Q81">
-        <v>2.69349258300007</v>
+        <v>2.7135004999999999</v>
       </c>
       <c r="R81" t="e">
         <f t="shared" si="3"/>
@@ -5686,7 +5686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>48</v>
       </c>
@@ -5702,41 +5702,41 @@
       <c r="E82" s="2">
         <v>738</v>
       </c>
-      <c r="F82" s="1">
+      <c r="F82">
         <v>255496</v>
       </c>
       <c r="G82">
         <v>10</v>
       </c>
       <c r="H82">
-        <v>46.950659417740503</v>
+        <v>570627.45859698998</v>
       </c>
       <c r="I82">
-        <v>2.61326641699997</v>
-      </c>
-      <c r="J82" s="1">
-        <v>1454</v>
+        <v>2.6186703330004</v>
+      </c>
+      <c r="J82">
+        <v>1485</v>
       </c>
       <c r="K82">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="L82">
-        <v>25.176102248208199</v>
+        <v>248455.88442945501</v>
       </c>
       <c r="M82">
-        <v>4.4033329995727E-3</v>
-      </c>
-      <c r="N82" s="1">
+        <v>5.8432500009075001E-3</v>
+      </c>
+      <c r="N82">
         <v>400</v>
       </c>
       <c r="O82">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="P82">
-        <v>42.585251652796302</v>
+        <v>345366.15851823997</v>
       </c>
       <c r="Q82">
-        <v>0.73086650000004705</v>
+        <v>2.3555539579992901</v>
       </c>
       <c r="R82" t="e">
         <f t="shared" si="3"/>
@@ -5748,7 +5748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>48</v>
       </c>
@@ -5764,7 +5764,7 @@
       <c r="E83" s="2">
         <v>162</v>
       </c>
-      <c r="F83" s="1">
+      <c r="F83">
         <v>8104</v>
       </c>
       <c r="G83">
@@ -5774,21 +5774,21 @@
         <v>1298.74977702859</v>
       </c>
       <c r="I83">
-        <v>4.1746083999896599E-2</v>
-      </c>
-      <c r="J83" s="1">
+        <v>4.2590000000927802E-2</v>
+      </c>
+      <c r="J83">
         <v>5477</v>
       </c>
       <c r="K83">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L83">
         <v>1417.4123663767</v>
       </c>
       <c r="M83">
-        <v>1.26722090008115E-2</v>
-      </c>
-      <c r="N83" s="1">
+        <v>1.2621375000890099E-2</v>
+      </c>
+      <c r="N83">
         <v>400</v>
       </c>
       <c r="O83">
@@ -5798,7 +5798,7 @@
         <v>1345.46760113249</v>
       </c>
       <c r="Q83">
-        <v>0.36215595900011899</v>
+        <v>0.35822929200003201</v>
       </c>
       <c r="R83" t="e">
         <f t="shared" si="3"/>
@@ -5810,7 +5810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>48</v>
       </c>
@@ -5826,41 +5826,41 @@
       <c r="E84" s="2">
         <v>162</v>
       </c>
-      <c r="F84" s="1">
+      <c r="F84">
         <v>8104</v>
       </c>
       <c r="G84">
         <v>10</v>
       </c>
       <c r="H84">
-        <v>98.178665337066406</v>
+        <v>187834.30239375899</v>
       </c>
       <c r="I84">
-        <v>4.3787542001154998E-2</v>
-      </c>
-      <c r="J84" s="1">
-        <v>303</v>
+        <v>7.1406708000722505E-2</v>
+      </c>
+      <c r="J84">
+        <v>309</v>
       </c>
       <c r="K84">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L84">
-        <v>43.455069017886203</v>
+        <v>194752.82594536099</v>
       </c>
       <c r="M84">
-        <v>9.2241699894649997E-4</v>
-      </c>
-      <c r="N84" s="1">
+        <v>1.0329590004403001E-3</v>
+      </c>
+      <c r="N84">
         <v>400</v>
       </c>
       <c r="O84">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="P84">
-        <v>35.2057406919469</v>
+        <v>193411.83337867199</v>
       </c>
       <c r="Q84">
-        <v>0.14835104200028501</v>
+        <v>0.2910204589989</v>
       </c>
       <c r="R84" t="e">
         <f t="shared" si="3"/>
@@ -5872,7 +5872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>48</v>
       </c>
@@ -5888,7 +5888,7 @@
       <c r="E85" s="2">
         <v>122</v>
       </c>
-      <c r="F85" s="1">
+      <c r="F85">
         <v>3244</v>
       </c>
       <c r="G85">
@@ -5898,21 +5898,21 @@
         <v>965.12750272286098</v>
       </c>
       <c r="I85">
-        <v>1.44393330010643E-2</v>
-      </c>
-      <c r="J85" s="1">
+        <v>1.6020625000237401E-2</v>
+      </c>
+      <c r="J85">
         <v>2024</v>
       </c>
       <c r="K85">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L85">
         <v>1059.57164559994</v>
       </c>
       <c r="M85">
-        <v>4.6762500005569996E-3</v>
-      </c>
-      <c r="N85" s="1">
+        <v>4.7190409986796996E-3</v>
+      </c>
+      <c r="N85">
         <v>400</v>
       </c>
       <c r="O85">
@@ -5922,7 +5922,7 @@
         <v>994.32620874364295</v>
       </c>
       <c r="Q85">
-        <v>0.189811333000307</v>
+        <v>0.19228029100122501</v>
       </c>
       <c r="R85">
         <f t="shared" si="3"/>
@@ -5934,7 +5934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>48</v>
       </c>
@@ -5950,45 +5950,45 @@
       <c r="E86" s="2">
         <v>122</v>
       </c>
-      <c r="F86" s="1">
+      <c r="F86">
         <v>3244</v>
       </c>
       <c r="G86">
         <v>10</v>
       </c>
       <c r="H86">
-        <v>133.33143692173601</v>
+        <v>242191.319265745</v>
       </c>
       <c r="I86">
-        <v>1.53465830007917E-2</v>
-      </c>
-      <c r="J86" s="1">
+        <v>1.6131915999721899E-2</v>
+      </c>
+      <c r="J86">
         <v>222</v>
       </c>
       <c r="K86">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L86">
-        <v>88.469596112994793</v>
+        <v>240062.14194676801</v>
       </c>
       <c r="M86">
-        <v>7.0929100002100004E-4</v>
-      </c>
-      <c r="N86" s="1">
+        <v>7.6295799954090001E-4</v>
+      </c>
+      <c r="N86">
         <v>400</v>
       </c>
       <c r="O86">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P86">
-        <v>127.208106478768</v>
+        <v>274166.65840898198</v>
       </c>
       <c r="Q86">
-        <v>0.14625358300008801</v>
-      </c>
-      <c r="R86" t="e">
+        <v>0.17993949999981801</v>
+      </c>
+      <c r="R86">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>0.13202512476573103</v>
       </c>
       <c r="S86" s="1"/>
       <c r="T86">
@@ -5996,7 +5996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>48</v>
       </c>
@@ -6012,7 +6012,7 @@
       <c r="E87" s="2">
         <v>118</v>
       </c>
-      <c r="F87" s="1">
+      <c r="F87">
         <v>2846</v>
       </c>
       <c r="G87">
@@ -6022,21 +6022,21 @@
         <v>1615.66433617185</v>
       </c>
       <c r="I87">
-        <v>1.2730582999210999E-2</v>
-      </c>
-      <c r="J87" s="1">
+        <v>1.5362000000095501E-2</v>
+      </c>
+      <c r="J87">
         <v>769</v>
       </c>
       <c r="K87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87">
         <v>1634.5698089182299</v>
       </c>
       <c r="M87">
-        <v>1.775415999873E-3</v>
-      </c>
-      <c r="N87" s="1">
+        <v>1.8280000003868999E-3</v>
+      </c>
+      <c r="N87">
         <v>400</v>
       </c>
       <c r="O87">
@@ -6046,7 +6046,7 @@
         <v>1615.14548495494</v>
       </c>
       <c r="Q87">
-        <v>0.131512166999982</v>
+        <v>0.133961457999248</v>
       </c>
       <c r="R87" t="e">
         <f t="shared" si="3"/>
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>48</v>
       </c>
@@ -6074,41 +6074,41 @@
       <c r="E88" s="2">
         <v>118</v>
       </c>
-      <c r="F88" s="1">
+      <c r="F88">
         <v>2846</v>
       </c>
       <c r="G88">
         <v>10</v>
       </c>
       <c r="H88">
-        <v>2126.2918803257098</v>
+        <v>20839208.884853899</v>
       </c>
       <c r="I88">
-        <v>1.32818749989382E-2</v>
-      </c>
-      <c r="J88" s="1">
+        <v>1.3743625000643E-2</v>
+      </c>
+      <c r="J88">
         <v>214</v>
       </c>
       <c r="K88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88">
-        <v>92.190011850326599</v>
+        <v>10894084.826228</v>
       </c>
       <c r="M88">
-        <v>6.4641599965390003E-4</v>
-      </c>
-      <c r="N88" s="1">
+        <v>7.0983300065560002E-4</v>
+      </c>
+      <c r="N88">
         <v>400</v>
       </c>
       <c r="O88">
         <v>1</v>
       </c>
       <c r="P88">
-        <v>92.190011850326997</v>
+        <v>10894084.826228101</v>
       </c>
       <c r="Q88">
-        <v>5.4346875000192002E-2</v>
+        <v>5.9264707999318399E-2</v>
       </c>
       <c r="R88" t="e">
         <f t="shared" si="3"/>
@@ -6120,7 +6120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>48</v>
       </c>
@@ -6136,7 +6136,7 @@
       <c r="E89" s="2">
         <v>153</v>
       </c>
-      <c r="F89" s="1">
+      <c r="F89">
         <v>6871</v>
       </c>
       <c r="G89">
@@ -6146,21 +6146,21 @@
         <v>1693.43957576093</v>
       </c>
       <c r="I89">
-        <v>3.3439708000514601E-2</v>
-      </c>
-      <c r="J89" s="1">
+        <v>3.6782042001504998E-2</v>
+      </c>
+      <c r="J89">
         <v>4371</v>
       </c>
       <c r="K89">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L89">
         <v>1848.80154283243</v>
       </c>
       <c r="M89">
-        <v>1.0029082999608301E-2</v>
-      </c>
-      <c r="N89" s="1">
+        <v>9.9598750002769E-3</v>
+      </c>
+      <c r="N89">
         <v>400</v>
       </c>
       <c r="O89">
@@ -6170,7 +6170,7 @@
         <v>1676.8048763280599</v>
       </c>
       <c r="Q89">
-        <v>0.304965208999874</v>
+        <v>0.30712337500153802</v>
       </c>
       <c r="R89" t="e">
         <f t="shared" si="3"/>
@@ -6182,7 +6182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>48</v>
       </c>
@@ -6198,41 +6198,41 @@
       <c r="E90" s="2">
         <v>153</v>
       </c>
-      <c r="F90" s="1">
+      <c r="F90">
         <v>6871</v>
       </c>
       <c r="G90">
         <v>10</v>
       </c>
       <c r="H90">
-        <v>601.24608871710302</v>
+        <v>13958184.3749853</v>
       </c>
       <c r="I90">
-        <v>3.6575750000338303E-2</v>
-      </c>
-      <c r="J90" s="1">
-        <v>284</v>
+        <v>3.8037750000512398E-2</v>
+      </c>
+      <c r="J90">
+        <v>285</v>
       </c>
       <c r="K90">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L90">
-        <v>344.14980110208199</v>
+        <v>14417794.706991</v>
       </c>
       <c r="M90">
-        <v>8.4733299991050001E-4</v>
-      </c>
-      <c r="N90" s="1">
+        <v>1.0035839986812E-3</v>
+      </c>
+      <c r="N90">
         <v>400</v>
       </c>
       <c r="O90">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="P90">
-        <v>431.02843107384803</v>
+        <v>14716503.7844752</v>
       </c>
       <c r="Q90">
-        <v>0.164598750000095</v>
+        <v>0.27262125000015602</v>
       </c>
       <c r="R90" t="e">
         <f t="shared" si="3"/>
@@ -6244,7 +6244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>48</v>
       </c>
@@ -6260,7 +6260,7 @@
       <c r="E91" s="2">
         <v>737</v>
       </c>
-      <c r="F91" s="1">
+      <c r="F91">
         <v>254779</v>
       </c>
       <c r="G91">
@@ -6270,21 +6270,21 @@
         <v>7675.3270040017096</v>
       </c>
       <c r="I91">
-        <v>2.5470750000004001</v>
-      </c>
-      <c r="J91" s="1">
+        <v>2.60958020799989</v>
+      </c>
+      <c r="J91">
         <v>44306</v>
       </c>
       <c r="K91">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L91">
         <v>7675.3270040017096</v>
       </c>
       <c r="M91">
-        <v>0.10297012499904599</v>
-      </c>
-      <c r="N91" s="1">
+        <v>0.101832625001407</v>
+      </c>
+      <c r="N91">
         <v>400</v>
       </c>
       <c r="O91">
@@ -6294,7 +6294,7 @@
         <v>7369.2627301625098</v>
       </c>
       <c r="Q91">
-        <v>2.79242370800011</v>
+        <v>2.79756645899942</v>
       </c>
       <c r="R91" t="e">
         <f t="shared" si="3"/>
@@ -6303,10 +6303,10 @@
       <c r="S91" s="1"/>
       <c r="T91">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>48</v>
       </c>
@@ -6322,41 +6322,41 @@
       <c r="E92" s="2">
         <v>737</v>
       </c>
-      <c r="F92" s="1">
+      <c r="F92">
         <v>254779</v>
       </c>
       <c r="G92">
         <v>10</v>
       </c>
       <c r="H92">
-        <v>144.17979866435201</v>
+        <v>3251509.3920501</v>
       </c>
       <c r="I92">
-        <v>2.5610721670000198</v>
-      </c>
-      <c r="J92" s="1">
+        <v>2.7451325000001798</v>
+      </c>
+      <c r="J92">
         <v>1452</v>
       </c>
       <c r="K92">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="L92">
-        <v>43.292122264550699</v>
+        <v>3590688.05461891</v>
       </c>
       <c r="M92">
-        <v>4.2252499988535003E-3</v>
-      </c>
-      <c r="N92" s="1">
+        <v>5.2070419988011997E-3</v>
+      </c>
+      <c r="N92">
         <v>400</v>
       </c>
       <c r="O92">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="P92">
-        <v>43.292122264550002</v>
+        <v>3988194.1042792299</v>
       </c>
       <c r="Q92">
-        <v>0.36309829099991398</v>
+        <v>2.3879118749991899</v>
       </c>
       <c r="R92" t="e">
         <f t="shared" si="3"/>
@@ -6368,7 +6368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>48</v>
       </c>
@@ -6384,7 +6384,7 @@
       <c r="E93" s="2">
         <v>164</v>
       </c>
-      <c r="F93" s="1">
+      <c r="F93">
         <v>8389</v>
       </c>
       <c r="G93">
@@ -6394,21 +6394,21 @@
         <v>1922.4030860863099</v>
       </c>
       <c r="I93">
-        <v>7.3760666000453001E-2</v>
-      </c>
-      <c r="J93" s="1">
+        <v>4.3381584000599098E-2</v>
+      </c>
+      <c r="J93">
         <v>8341</v>
       </c>
       <c r="K93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93">
         <v>2140.5476767314999</v>
       </c>
       <c r="M93">
-        <v>1.8690457998672999E-2</v>
-      </c>
-      <c r="N93" s="1">
+        <v>1.85707910004566E-2</v>
+      </c>
+      <c r="N93">
         <v>400</v>
       </c>
       <c r="O93">
@@ -6418,7 +6418,7 @@
         <v>1904.1694456559601</v>
       </c>
       <c r="Q93">
-        <v>0.343501833000118</v>
+        <v>0.351733999999851</v>
       </c>
       <c r="R93" t="e">
         <f t="shared" si="3"/>
@@ -6430,7 +6430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>48</v>
       </c>
@@ -6446,41 +6446,41 @@
       <c r="E94" s="2">
         <v>164</v>
       </c>
-      <c r="F94" s="1">
+      <c r="F94">
         <v>8389</v>
       </c>
       <c r="G94">
         <v>10</v>
       </c>
       <c r="H94">
-        <v>676.33554143159995</v>
+        <v>4574415.7148281401</v>
       </c>
       <c r="I94">
-        <v>4.6103167000183E-2</v>
-      </c>
-      <c r="J94" s="1">
+        <v>4.7245249999832498E-2</v>
+      </c>
+      <c r="J94">
         <v>306</v>
       </c>
       <c r="K94">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L94">
-        <v>52.663975985546401</v>
+        <v>3707822.78610542</v>
       </c>
       <c r="M94">
-        <v>9.2208399837540001E-4</v>
-      </c>
-      <c r="N94" s="1">
+        <v>1.0991249982907E-3</v>
+      </c>
+      <c r="N94">
         <v>400</v>
       </c>
       <c r="O94">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="P94">
-        <v>202.69712285897899</v>
+        <v>4839323.5736514898</v>
       </c>
       <c r="Q94">
-        <v>0.179851625000083</v>
+        <v>0.27969687500080898</v>
       </c>
       <c r="R94" t="e">
         <f t="shared" si="3"/>
@@ -6492,7 +6492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>48</v>
       </c>
@@ -6508,7 +6508,7 @@
       <c r="E95" s="2">
         <v>126</v>
       </c>
-      <c r="F95" s="1">
+      <c r="F95">
         <v>3658</v>
       </c>
       <c r="G95">
@@ -6518,21 +6518,21 @@
         <v>1642.53533727271</v>
       </c>
       <c r="I95">
-        <v>1.7988915999012499E-2</v>
-      </c>
-      <c r="J95" s="1">
+        <v>1.6662666999764E-2</v>
+      </c>
+      <c r="J95">
         <v>2636</v>
       </c>
       <c r="K95">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L95">
         <v>1716.9244751204401</v>
       </c>
       <c r="M95">
-        <v>6.0456669998529E-3</v>
-      </c>
-      <c r="N95" s="1">
+        <v>6.0594999995372996E-3</v>
+      </c>
+      <c r="N95">
         <v>400</v>
       </c>
       <c r="O95">
@@ -6542,7 +6542,7 @@
         <v>1686.2915469219199</v>
       </c>
       <c r="Q95">
-        <v>0.25130312500004898</v>
+        <v>0.25402337500054201</v>
       </c>
       <c r="R95" t="e">
         <f t="shared" si="3"/>
@@ -6554,7 +6554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>48</v>
       </c>
@@ -6570,41 +6570,41 @@
       <c r="E96" s="2">
         <v>126</v>
       </c>
-      <c r="F96" s="1">
+      <c r="F96">
         <v>3658</v>
       </c>
       <c r="G96">
         <v>10</v>
       </c>
       <c r="H96">
-        <v>1600.3477926399801</v>
+        <v>22350610.1865598</v>
       </c>
       <c r="I96">
-        <v>1.7575583999132501E-2</v>
-      </c>
-      <c r="J96" s="1">
+        <v>2.05195419985102E-2</v>
+      </c>
+      <c r="J96">
         <v>230</v>
       </c>
       <c r="K96">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L96">
-        <v>228.198733552666</v>
+        <v>23013859.6172686</v>
       </c>
       <c r="M96">
-        <v>6.9699999949069996E-4</v>
-      </c>
-      <c r="N96" s="1">
+        <v>8.0400000115330003E-4</v>
+      </c>
+      <c r="N96">
         <v>400</v>
       </c>
       <c r="O96">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="P96">
-        <v>563.21273391730494</v>
+        <v>25185563.973614801</v>
       </c>
       <c r="Q96">
-        <v>0.105672666999907</v>
+        <v>0.206648041999869</v>
       </c>
       <c r="R96" t="e">
         <f t="shared" si="3"/>
@@ -6616,7 +6616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>48</v>
       </c>
@@ -6632,7 +6632,7 @@
       <c r="E97" s="2">
         <v>118</v>
       </c>
-      <c r="F97" s="1">
+      <c r="F97">
         <v>2846</v>
       </c>
       <c r="G97">
@@ -6642,21 +6642,21 @@
         <v>517.32380025205202</v>
       </c>
       <c r="I97">
-        <v>1.5243874999214301E-2</v>
-      </c>
-      <c r="J97" s="1">
+        <v>1.2693791000856399E-2</v>
+      </c>
+      <c r="J97">
         <v>1940</v>
       </c>
       <c r="K97">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L97">
         <v>611.77363789921003</v>
       </c>
       <c r="M97">
-        <v>4.4632089993682997E-3</v>
-      </c>
-      <c r="N97" s="1">
+        <v>4.4457089989009E-3</v>
+      </c>
+      <c r="N97">
         <v>400</v>
       </c>
       <c r="O97">
@@ -6666,7 +6666,7 @@
         <v>560.87647316776395</v>
       </c>
       <c r="Q97">
-        <v>0.233867207999992</v>
+        <v>0.23886374999892701</v>
       </c>
       <c r="R97" t="e">
         <f t="shared" si="3"/>
@@ -6678,7 +6678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>48</v>
       </c>
@@ -6694,41 +6694,41 @@
       <c r="E98" s="2">
         <v>118</v>
       </c>
-      <c r="F98" s="1">
+      <c r="F98">
         <v>2846</v>
       </c>
       <c r="G98">
         <v>10</v>
       </c>
       <c r="H98">
-        <v>21.9758937463675</v>
+        <v>2942.3367061792201</v>
       </c>
       <c r="I98">
-        <v>1.3504500000635701E-2</v>
-      </c>
-      <c r="J98" s="1">
-        <v>214</v>
+        <v>4.18959580001683E-2</v>
+      </c>
+      <c r="J98">
+        <v>297</v>
       </c>
       <c r="K98">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L98">
-        <v>7.3441115753513699</v>
+        <v>3060.2202154548499</v>
       </c>
       <c r="M98">
-        <v>6.5629200071270002E-4</v>
-      </c>
-      <c r="N98" s="1">
+        <v>9.6695799948060001E-4</v>
+      </c>
+      <c r="N98">
         <v>400</v>
       </c>
       <c r="O98">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P98">
-        <v>7.9772418496673998</v>
+        <v>4077.2916080452301</v>
       </c>
       <c r="Q98">
-        <v>5.5338334000225503E-2</v>
+        <v>0.19391029199869</v>
       </c>
       <c r="R98" t="e">
         <f t="shared" si="3"/>
@@ -6740,7 +6740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>48</v>
       </c>
@@ -6756,7 +6756,7 @@
       <c r="E99" s="2">
         <v>126</v>
       </c>
-      <c r="F99" s="1">
+      <c r="F99">
         <v>3658</v>
       </c>
       <c r="G99">
@@ -6766,21 +6766,21 @@
         <v>275.77164276639797</v>
       </c>
       <c r="I99">
-        <v>1.90152089999173E-2</v>
-      </c>
-      <c r="J99" s="1">
+        <v>1.6631250000500499E-2</v>
+      </c>
+      <c r="J99">
         <v>1929</v>
       </c>
       <c r="K99">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L99">
         <v>286.71840157676098</v>
       </c>
       <c r="M99">
-        <v>4.5352090000959997E-3</v>
-      </c>
-      <c r="N99" s="1">
+        <v>4.4076249996577999E-3</v>
+      </c>
+      <c r="N99">
         <v>400</v>
       </c>
       <c r="O99">
@@ -6790,7 +6790,7 @@
         <v>388.12526355409602</v>
       </c>
       <c r="Q99">
-        <v>0.218287000000145</v>
+        <v>0.21959095900092501</v>
       </c>
       <c r="R99" t="e">
         <f t="shared" si="3"/>
@@ -6802,7 +6802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>48</v>
       </c>
@@ -6818,41 +6818,41 @@
       <c r="E100" s="2">
         <v>126</v>
       </c>
-      <c r="F100" s="1">
+      <c r="F100">
         <v>3658</v>
       </c>
       <c r="G100">
         <v>10</v>
       </c>
       <c r="H100">
-        <v>6.3210067981650502</v>
+        <v>429.98661829485701</v>
       </c>
       <c r="I100">
-        <v>1.7674709000857498E-2</v>
-      </c>
-      <c r="J100" s="1">
-        <v>262</v>
+        <v>1.8288749999555799E-2</v>
+      </c>
+      <c r="J100">
+        <v>588</v>
       </c>
       <c r="K100">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L100">
-        <v>5.6075204929450102</v>
+        <v>387.67754023511401</v>
       </c>
       <c r="M100">
-        <v>7.9166600153250004E-4</v>
-      </c>
-      <c r="N100" s="1">
+        <v>1.8927080000139E-3</v>
+      </c>
+      <c r="N100">
         <v>400</v>
       </c>
       <c r="O100">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="P100">
-        <v>6.0832689685003896</v>
+        <v>937.55602934188198</v>
       </c>
       <c r="Q100">
-        <v>0.104198167000049</v>
+        <v>0.17415162499855699</v>
       </c>
       <c r="R100" t="e">
         <f t="shared" si="3"/>
@@ -6864,7 +6864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>48</v>
       </c>
@@ -6880,7 +6880,7 @@
       <c r="E101" s="2">
         <v>866</v>
       </c>
-      <c r="F101" s="1">
+      <c r="F101">
         <v>355528</v>
       </c>
       <c r="G101">
@@ -6890,21 +6890,21 @@
         <v>7621.7787993363199</v>
       </c>
       <c r="I101">
-        <v>3.8025400839997001</v>
-      </c>
-      <c r="J101" s="1">
+        <v>3.6947780000009498</v>
+      </c>
+      <c r="J101">
         <v>22877</v>
       </c>
       <c r="K101">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L101">
         <v>5666.6210366209798</v>
       </c>
       <c r="M101">
-        <v>5.83667080009036E-2</v>
-      </c>
-      <c r="N101" s="1">
+        <v>5.7958792000135803E-2</v>
+      </c>
+      <c r="N101">
         <v>400</v>
       </c>
       <c r="O101">
@@ -6914,7 +6914,7 @@
         <v>4958.1175009170302</v>
       </c>
       <c r="Q101">
-        <v>3.3223813749996198</v>
+        <v>3.3303402500005101</v>
       </c>
       <c r="R101" t="e">
         <f t="shared" si="3"/>
@@ -6926,7 +6926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>48</v>
       </c>
@@ -6942,41 +6942,41 @@
       <c r="E102" s="2">
         <v>866</v>
       </c>
-      <c r="F102" s="1">
+      <c r="F102">
         <v>355528</v>
       </c>
       <c r="G102">
         <v>10</v>
       </c>
       <c r="H102">
-        <v>68.391035456461196</v>
+        <v>995949.94339209795</v>
       </c>
       <c r="I102">
-        <v>3.9219677500004702</v>
-      </c>
-      <c r="J102" s="1">
-        <v>1718</v>
+        <v>4.0321652080001504</v>
+      </c>
+      <c r="J102">
+        <v>2167</v>
       </c>
       <c r="K102">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="L102">
-        <v>188.30204150458701</v>
+        <v>176969.67107313001</v>
       </c>
       <c r="M102">
-        <v>5.4688330001226E-3</v>
-      </c>
-      <c r="N102" s="1">
+        <v>8.2115830009569998E-3</v>
+      </c>
+      <c r="N102">
         <v>400</v>
       </c>
       <c r="O102">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="P102">
-        <v>89.969319743593104</v>
+        <v>205639.833685077</v>
       </c>
       <c r="Q102">
-        <v>1.44918491699991</v>
+        <v>2.6778262080006199</v>
       </c>
       <c r="R102" t="e">
         <f t="shared" si="3"/>
@@ -6988,7 +6988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>48</v>
       </c>
@@ -7004,7 +7004,7 @@
       <c r="E103" s="2">
         <v>109</v>
       </c>
-      <c r="F103" s="1">
+      <c r="F103">
         <v>2009</v>
       </c>
       <c r="G103">
@@ -7014,21 +7014,21 @@
         <v>1334.0476184132399</v>
       </c>
       <c r="I103">
-        <v>8.6948329990263994E-3</v>
-      </c>
-      <c r="J103" s="1">
+        <v>8.5193750001053004E-3</v>
+      </c>
+      <c r="J103">
         <v>2882</v>
       </c>
       <c r="K103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L103">
         <v>1496.2857787288799</v>
       </c>
       <c r="M103">
-        <v>6.4778329997352002E-3</v>
-      </c>
-      <c r="N103" s="1">
+        <v>6.5283330004603998E-3</v>
+      </c>
+      <c r="N103">
         <v>400</v>
       </c>
       <c r="O103">
@@ -7038,7 +7038,7 @@
         <v>1360.24728174401</v>
       </c>
       <c r="Q103">
-        <v>0.16401224999981401</v>
+        <v>0.16579783300039699</v>
       </c>
       <c r="R103" t="e">
         <f t="shared" si="3"/>
@@ -7050,7 +7050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>48</v>
       </c>
@@ -7066,41 +7066,41 @@
       <c r="E104" s="2">
         <v>109</v>
       </c>
-      <c r="F104" s="1">
+      <c r="F104">
         <v>2009</v>
       </c>
       <c r="G104">
         <v>10</v>
       </c>
       <c r="H104">
-        <v>1266.58576081827</v>
+        <v>8959122.5550174396</v>
       </c>
       <c r="I104">
-        <v>9.2424579997896009E-3</v>
-      </c>
-      <c r="J104" s="1">
+        <v>1.23827919996983E-2</v>
+      </c>
+      <c r="J104">
         <v>196</v>
       </c>
       <c r="K104">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L104">
-        <v>181.44301899822199</v>
+        <v>8883783.8575011399</v>
       </c>
       <c r="M104">
-        <v>6.0170799952170004E-4</v>
-      </c>
-      <c r="N104" s="1">
+        <v>6.6754100043899998E-4</v>
+      </c>
+      <c r="N104">
         <v>400</v>
       </c>
       <c r="O104">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P104">
-        <v>181.44301899822199</v>
+        <v>9105213.7015461102</v>
       </c>
       <c r="Q104">
-        <v>4.9911916999917497E-2</v>
+        <v>0.150081124998905</v>
       </c>
       <c r="R104" t="e">
         <f t="shared" si="3"/>
@@ -7112,7 +7112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>48</v>
       </c>
@@ -7128,7 +7128,7 @@
       <c r="E105" s="2">
         <v>106</v>
       </c>
-      <c r="F105" s="1">
+      <c r="F105">
         <v>1748</v>
       </c>
       <c r="G105">
@@ -7138,21 +7138,21 @@
         <v>1074.39090906209</v>
       </c>
       <c r="I105">
-        <v>7.3594999994384003E-3</v>
-      </c>
-      <c r="J105" s="1">
+        <v>7.1997080012805997E-3</v>
+      </c>
+      <c r="J105">
         <v>2480</v>
       </c>
       <c r="K105">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L105">
         <v>1158.33857010322</v>
       </c>
       <c r="M105">
-        <v>5.5822920003265001E-3</v>
-      </c>
-      <c r="N105" s="1">
+        <v>5.5388330001732997E-3</v>
+      </c>
+      <c r="N105">
         <v>400</v>
       </c>
       <c r="O105">
@@ -7162,7 +7162,7 @@
         <v>1107.7196266475501</v>
       </c>
       <c r="Q105">
-        <v>0.157255207999696</v>
+        <v>0.159196915999928</v>
       </c>
       <c r="R105" t="e">
         <f t="shared" si="3"/>
@@ -7174,7 +7174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>48</v>
       </c>
@@ -7190,53 +7190,53 @@
       <c r="E106" s="2">
         <v>106</v>
       </c>
-      <c r="F106" s="1">
+      <c r="F106">
         <v>1748</v>
       </c>
       <c r="G106">
         <v>10</v>
       </c>
       <c r="H106">
-        <v>370.95796179889498</v>
+        <v>1208080.1432394299</v>
       </c>
       <c r="I106">
-        <v>7.8649580009367993E-3</v>
-      </c>
-      <c r="J106" s="1">
+        <v>8.1929170009970992E-3</v>
+      </c>
+      <c r="J106">
         <v>190</v>
       </c>
       <c r="K106">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L106">
-        <v>39.913512995688102</v>
+        <v>1213276.9471205601</v>
       </c>
       <c r="M106">
-        <v>6.2350000007420001E-4</v>
-      </c>
-      <c r="N106" s="1">
+        <v>6.4683399978089997E-4</v>
+      </c>
+      <c r="N106">
         <v>400</v>
       </c>
       <c r="O106">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P106">
-        <v>39.913512995688002</v>
+        <v>1352927.13428351</v>
       </c>
       <c r="Q106">
-        <v>4.9229124999783297E-2</v>
-      </c>
-      <c r="R106" t="e">
+        <v>0.13555308299874</v>
+      </c>
+      <c r="R106">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>0.11989849502507122</v>
       </c>
       <c r="S106" s="1"/>
       <c r="T106">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>48</v>
       </c>
@@ -7252,7 +7252,7 @@
       <c r="E107" s="2">
         <v>106</v>
       </c>
-      <c r="F107" s="1">
+      <c r="F107">
         <v>1748</v>
       </c>
       <c r="G107">
@@ -7262,21 +7262,21 @@
         <v>1415.2243072554099</v>
       </c>
       <c r="I107">
-        <v>7.3283330002595001E-3</v>
-      </c>
-      <c r="J107" s="1">
+        <v>1.13460420016053E-2</v>
+      </c>
+      <c r="J107">
         <v>2743</v>
       </c>
       <c r="K107">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L107">
         <v>1526.8630593258899</v>
       </c>
       <c r="M107">
-        <v>6.3494590012850996E-3</v>
-      </c>
-      <c r="N107" s="1">
+        <v>6.2580420017183998E-3</v>
+      </c>
+      <c r="N107">
         <v>400</v>
       </c>
       <c r="O107">
@@ -7286,7 +7286,7 @@
         <v>1456.0348662611</v>
       </c>
       <c r="Q107">
-        <v>0.17317312499972101</v>
+        <v>0.17591474999971901</v>
       </c>
       <c r="R107" t="e">
         <f t="shared" si="3"/>
@@ -7298,7 +7298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>48</v>
       </c>
@@ -7314,53 +7314,53 @@
       <c r="E108" s="2">
         <v>106</v>
       </c>
-      <c r="F108" s="1">
+      <c r="F108">
         <v>1748</v>
       </c>
       <c r="G108">
         <v>10</v>
       </c>
       <c r="H108">
-        <v>2216.8803313418798</v>
+        <v>20985709.426562</v>
       </c>
       <c r="I108">
-        <v>7.8615410002384999E-3</v>
-      </c>
-      <c r="J108" s="1">
+        <v>8.3407920010357996E-3</v>
+      </c>
+      <c r="J108">
         <v>190</v>
       </c>
       <c r="K108">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L108">
-        <v>246.87412328324501</v>
+        <v>21426511.751203801</v>
       </c>
       <c r="M108">
-        <v>5.7733399989949997E-4</v>
-      </c>
-      <c r="N108" s="1">
+        <v>6.7466600012260004E-4</v>
+      </c>
+      <c r="N108">
         <v>400</v>
       </c>
       <c r="O108">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="P108">
-        <v>483.39780466249601</v>
+        <v>24682744.249527302</v>
       </c>
       <c r="Q108">
-        <v>8.8207582999984796E-2</v>
-      </c>
-      <c r="R108" t="e">
+        <v>0.16499945800023799</v>
+      </c>
+      <c r="R108">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>0.1761691610142041</v>
       </c>
       <c r="S108" s="1"/>
       <c r="T108">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>48</v>
       </c>
@@ -7376,7 +7376,7 @@
       <c r="E109" s="2">
         <v>106</v>
       </c>
-      <c r="F109" s="1">
+      <c r="F109">
         <v>1748</v>
       </c>
       <c r="G109">
@@ -7386,21 +7386,21 @@
         <v>774.64378807948503</v>
       </c>
       <c r="I109">
-        <v>7.3723330006031998E-3</v>
-      </c>
-      <c r="J109" s="1">
+        <v>7.4559589993441E-3</v>
+      </c>
+      <c r="J109">
         <v>2240</v>
       </c>
       <c r="K109">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L109">
         <v>841.78181360803296</v>
       </c>
       <c r="M109">
-        <v>5.1075829996989003E-3</v>
-      </c>
-      <c r="N109" s="1">
+        <v>5.1154579996364E-3</v>
+      </c>
+      <c r="N109">
         <v>400</v>
       </c>
       <c r="O109">
@@ -7410,7 +7410,7 @@
         <v>794.85705125657</v>
       </c>
       <c r="Q109">
-        <v>0.17343179099998399</v>
+        <v>0.172138124999037</v>
       </c>
       <c r="R109" t="e">
         <f t="shared" si="3"/>
@@ -7422,7 +7422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>48</v>
       </c>
@@ -7438,45 +7438,45 @@
       <c r="E110" s="2">
         <v>106</v>
       </c>
-      <c r="F110" s="1">
+      <c r="F110">
         <v>1748</v>
       </c>
       <c r="G110">
         <v>10</v>
       </c>
       <c r="H110">
-        <v>100.041473366574</v>
+        <v>66276.420242691704</v>
       </c>
       <c r="I110">
-        <v>7.9517920003127004E-3</v>
-      </c>
-      <c r="J110" s="1">
-        <v>190</v>
+        <v>1.14113330000691E-2</v>
+      </c>
+      <c r="J110">
+        <v>193</v>
       </c>
       <c r="K110">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L110">
-        <v>47.035346974325599</v>
+        <v>67241.295391424501</v>
       </c>
       <c r="M110">
-        <v>6.0233299882379995E-4</v>
-      </c>
-      <c r="N110" s="1">
+        <v>7.0312500065479997E-4</v>
+      </c>
+      <c r="N110">
         <v>400</v>
       </c>
       <c r="O110">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P110">
-        <v>37.670246521769499</v>
+        <v>89855.458408307895</v>
       </c>
       <c r="Q110">
-        <v>4.8555583000052097E-2</v>
-      </c>
-      <c r="R110" t="e">
+        <v>0.14095133400041901</v>
+      </c>
+      <c r="R110">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>0.35576813109812233</v>
       </c>
       <c r="S110" s="1"/>
       <c r="T110">
@@ -7484,7 +7484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>48</v>
       </c>
@@ -7500,7 +7500,7 @@
       <c r="E111" s="2">
         <v>737</v>
       </c>
-      <c r="F111" s="1">
+      <c r="F111">
         <v>254779</v>
       </c>
       <c r="G111">
@@ -7510,21 +7510,21 @@
         <v>7671.1611359237604</v>
       </c>
       <c r="I111">
-        <v>2.4850994580010499</v>
-      </c>
-      <c r="J111" s="1">
+        <v>2.5524319169999199</v>
+      </c>
+      <c r="J111">
         <v>44319</v>
       </c>
       <c r="K111">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L111">
         <v>7705.1575888161797</v>
       </c>
       <c r="M111">
-        <v>0.101176124999255</v>
-      </c>
-      <c r="N111" s="1">
+        <v>0.100018709001233</v>
+      </c>
+      <c r="N111">
         <v>400</v>
       </c>
       <c r="O111">
@@ -7534,7 +7534,7 @@
         <v>7513.1110637427801</v>
       </c>
       <c r="Q111">
-        <v>2.6376498750000699</v>
+        <v>2.65592745899994</v>
       </c>
       <c r="R111" t="e">
         <f t="shared" si="3"/>
@@ -7546,7 +7546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>48</v>
       </c>
@@ -7562,41 +7562,41 @@
       <c r="E112" s="2">
         <v>737</v>
       </c>
-      <c r="F112" s="1">
+      <c r="F112">
         <v>254779</v>
       </c>
       <c r="G112">
         <v>10</v>
       </c>
       <c r="H112">
-        <v>167.17021201364599</v>
+        <v>2787610.2967467401</v>
       </c>
       <c r="I112">
-        <v>2.6352581249993801</v>
-      </c>
-      <c r="J112" s="1">
-        <v>1452</v>
+        <v>2.6747141670002699</v>
+      </c>
+      <c r="J112">
+        <v>1454</v>
       </c>
       <c r="K112">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L112">
-        <v>35.111863265892701</v>
+        <v>3434311.9051685701</v>
       </c>
       <c r="M112">
-        <v>4.3562920000113003E-3</v>
-      </c>
-      <c r="N112" s="1">
+        <v>4.9132909989565996E-3</v>
+      </c>
+      <c r="N112">
         <v>400</v>
       </c>
       <c r="O112">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="P112">
-        <v>35.111863265897099</v>
+        <v>3536258.4454641701</v>
       </c>
       <c r="Q112">
-        <v>0.36071208400016902</v>
+        <v>2.1281067499985502</v>
       </c>
       <c r="R112" t="e">
         <f t="shared" si="3"/>
@@ -7608,7 +7608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>48</v>
       </c>
@@ -7624,7 +7624,7 @@
       <c r="E113" s="2">
         <v>180</v>
       </c>
-      <c r="F113" s="1">
+      <c r="F113">
         <v>10813</v>
       </c>
       <c r="G113">
@@ -7634,21 +7634,21 @@
         <v>1476.27561241121</v>
       </c>
       <c r="I113">
-        <v>5.6542667000030598E-2</v>
-      </c>
-      <c r="J113" s="1">
+        <v>5.6387874999927499E-2</v>
+      </c>
+      <c r="J113">
         <v>5402</v>
       </c>
       <c r="K113">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L113">
         <v>1553.7848638042999</v>
       </c>
       <c r="M113">
-        <v>1.25853329991514E-2</v>
-      </c>
-      <c r="N113" s="1">
+        <v>1.23395410009834E-2</v>
+      </c>
+      <c r="N113">
         <v>400</v>
       </c>
       <c r="O113">
@@ -7658,7 +7658,7 @@
         <v>1418.9909539201501</v>
       </c>
       <c r="Q113">
-        <v>0.41035629200041501</v>
+        <v>0.43207233399880302</v>
       </c>
       <c r="R113" t="e">
         <f t="shared" si="3"/>
@@ -7670,7 +7670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>48</v>
       </c>
@@ -7686,41 +7686,41 @@
       <c r="E114" s="2">
         <v>180</v>
       </c>
-      <c r="F114" s="1">
+      <c r="F114">
         <v>10813</v>
       </c>
       <c r="G114">
         <v>10</v>
       </c>
       <c r="H114">
-        <v>115.245823407811</v>
+        <v>157151.94048456699</v>
       </c>
       <c r="I114">
-        <v>6.1424458001056302E-2</v>
-      </c>
-      <c r="J114" s="1">
-        <v>338</v>
+        <v>6.3325166000140598E-2</v>
+      </c>
+      <c r="J114">
+        <v>339</v>
       </c>
       <c r="K114">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L114">
-        <v>14.4660112169864</v>
+        <v>142804.583143436</v>
       </c>
       <c r="M114">
-        <v>1.0060839995276001E-3</v>
-      </c>
-      <c r="N114" s="1">
+        <v>1.2338750002526999E-3</v>
+      </c>
+      <c r="N114">
         <v>400</v>
       </c>
       <c r="O114">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="P114">
-        <v>14.466011216986301</v>
+        <v>175958.62411410999</v>
       </c>
       <c r="Q114">
-        <v>8.3525084000029795E-2</v>
+        <v>0.43314124999960701</v>
       </c>
       <c r="R114" t="e">
         <f t="shared" si="3"/>
@@ -7732,7 +7732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>48</v>
       </c>
@@ -7748,7 +7748,7 @@
       <c r="E115" s="2">
         <v>177</v>
       </c>
-      <c r="F115" s="1">
+      <c r="F115">
         <v>10339</v>
       </c>
       <c r="G115">
@@ -7758,21 +7758,21 @@
         <v>1553.17603289257</v>
       </c>
       <c r="I115">
-        <v>5.4170375000467098E-2</v>
-      </c>
-      <c r="J115" s="1">
+        <v>5.5189332999361698E-2</v>
+      </c>
+      <c r="J115">
         <v>6475</v>
       </c>
       <c r="K115">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L115">
         <v>1676.8045600518401</v>
       </c>
       <c r="M115">
-        <v>1.4806999999564099E-2</v>
-      </c>
-      <c r="N115" s="1">
+        <v>1.4555916999597599E-2</v>
+      </c>
+      <c r="N115">
         <v>400</v>
       </c>
       <c r="O115">
@@ -7782,7 +7782,7 @@
         <v>1570.4285128218801</v>
       </c>
       <c r="Q115">
-        <v>0.376424208000116</v>
+        <v>0.38097362500047799</v>
       </c>
       <c r="R115">
         <f t="shared" si="3"/>
@@ -7794,7 +7794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>48</v>
       </c>
@@ -7810,41 +7810,41 @@
       <c r="E116" s="2">
         <v>177</v>
       </c>
-      <c r="F116" s="1">
+      <c r="F116">
         <v>10339</v>
       </c>
       <c r="G116">
         <v>10</v>
       </c>
       <c r="H116">
-        <v>128.786431472667</v>
+        <v>775151.62264202302</v>
       </c>
       <c r="I116">
-        <v>5.73184160002711E-2</v>
-      </c>
-      <c r="J116" s="1">
-        <v>332</v>
+        <v>5.91149169995333E-2</v>
+      </c>
+      <c r="J116">
+        <v>338</v>
       </c>
       <c r="K116">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L116">
-        <v>27.463453212112501</v>
+        <v>796464.18539917096</v>
       </c>
       <c r="M116">
-        <v>9.9341699933569992E-4</v>
-      </c>
-      <c r="N116" s="1">
+        <v>1.1134159994980999E-3</v>
+      </c>
+      <c r="N116">
         <v>400</v>
       </c>
       <c r="O116">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="P116">
-        <v>27.463453212112601</v>
+        <v>795897.75115152798</v>
       </c>
       <c r="Q116">
-        <v>8.4417250000115004E-2</v>
+        <v>0.30141066699980001</v>
       </c>
       <c r="R116" t="e">
         <f t="shared" si="3"/>
@@ -7856,7 +7856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>48</v>
       </c>
@@ -7872,7 +7872,7 @@
       <c r="E117" s="2">
         <v>122</v>
       </c>
-      <c r="F117" s="1">
+      <c r="F117">
         <v>3244</v>
       </c>
       <c r="G117">
@@ -7882,21 +7882,21 @@
         <v>989.08860591427504</v>
       </c>
       <c r="I117">
-        <v>1.56105000005482E-2</v>
-      </c>
-      <c r="J117" s="1">
+        <v>1.58440830000472E-2</v>
+      </c>
+      <c r="J117">
         <v>4256</v>
       </c>
       <c r="K117">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L117">
         <v>1073.5211729928601</v>
       </c>
       <c r="M117">
-        <v>9.6866250005405007E-3</v>
-      </c>
-      <c r="N117" s="1">
+        <v>9.7726250005507002E-3</v>
+      </c>
+      <c r="N117">
         <v>400</v>
       </c>
       <c r="O117">
@@ -7906,7 +7906,7 @@
         <v>1012.71740909291</v>
       </c>
       <c r="Q117">
-        <v>0.28683883299981899</v>
+        <v>0.294031709001501</v>
       </c>
       <c r="R117" t="e">
         <f t="shared" si="3"/>
@@ -7918,7 +7918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>48</v>
       </c>
@@ -7934,41 +7934,41 @@
       <c r="E118" s="2">
         <v>122</v>
       </c>
-      <c r="F118" s="1">
+      <c r="F118">
         <v>3244</v>
       </c>
       <c r="G118">
         <v>10</v>
       </c>
       <c r="H118">
-        <v>142.29827236113701</v>
+        <v>205473.98951876001</v>
       </c>
       <c r="I118">
-        <v>1.53073330002371E-2</v>
-      </c>
-      <c r="J118" s="1">
-        <v>222</v>
+        <v>1.60829589985951E-2</v>
+      </c>
+      <c r="J118">
+        <v>225</v>
       </c>
       <c r="K118">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L118">
-        <v>22.332284112650999</v>
+        <v>207735.91215526499</v>
       </c>
       <c r="M118">
-        <v>6.9558300128839999E-4</v>
-      </c>
-      <c r="N118" s="1">
+        <v>7.6537499990080005E-4</v>
+      </c>
+      <c r="N118">
         <v>400</v>
       </c>
       <c r="O118">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="P118">
-        <v>21.849971013340902</v>
+        <v>227903.02318594101</v>
       </c>
       <c r="Q118">
-        <v>0.109649208000064</v>
+        <v>0.26067970800067902</v>
       </c>
       <c r="R118" t="e">
         <f t="shared" si="3"/>
@@ -7977,10 +7977,10 @@
       <c r="S118" s="1"/>
       <c r="T118">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>48</v>
       </c>
@@ -7996,7 +7996,7 @@
       <c r="E119" s="2">
         <v>122</v>
       </c>
-      <c r="F119" s="1">
+      <c r="F119">
         <v>3244</v>
       </c>
       <c r="G119">
@@ -8006,21 +8006,21 @@
         <v>512.30950924021204</v>
       </c>
       <c r="I119">
-        <v>1.6786041998784602E-2</v>
-      </c>
-      <c r="J119" s="1">
+        <v>1.6857707998497E-2</v>
+      </c>
+      <c r="J119">
         <v>2549</v>
       </c>
       <c r="K119">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L119">
         <v>599.15468542375697</v>
       </c>
       <c r="M119">
-        <v>5.8954169999195999E-3</v>
-      </c>
-      <c r="N119" s="1">
+        <v>5.9347919996071002E-3</v>
+      </c>
+      <c r="N119">
         <v>400</v>
       </c>
       <c r="O119">
@@ -8030,7 +8030,7 @@
         <v>573.19248410796297</v>
       </c>
       <c r="Q119">
-        <v>0.20702670799983</v>
+        <v>0.20866454099996101</v>
       </c>
       <c r="R119">
         <f t="shared" si="3"/>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>48</v>
       </c>
@@ -8058,41 +8058,41 @@
       <c r="E120" s="2">
         <v>122</v>
       </c>
-      <c r="F120" s="1">
+      <c r="F120">
         <v>3244</v>
       </c>
       <c r="G120">
         <v>10</v>
       </c>
       <c r="H120">
-        <v>22.499136017949802</v>
+        <v>5272.1118713323203</v>
       </c>
       <c r="I120">
-        <v>1.52427920002082E-2</v>
-      </c>
-      <c r="J120" s="1">
-        <v>231</v>
+        <v>1.6250332999334201E-2</v>
+      </c>
+      <c r="J120">
+        <v>381</v>
       </c>
       <c r="K120">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L120">
-        <v>25.418307739140499</v>
+        <v>5159.1864858405897</v>
       </c>
       <c r="M120">
-        <v>7.4354100070190003E-4</v>
-      </c>
-      <c r="N120" s="1">
+        <v>1.2358749991108E-3</v>
+      </c>
+      <c r="N120">
         <v>400</v>
       </c>
       <c r="O120">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P120">
-        <v>9.4444748485060508</v>
+        <v>14069.922926065599</v>
       </c>
       <c r="Q120">
-        <v>5.7954207999955501E-2</v>
+        <v>0.17613574999995699</v>
       </c>
       <c r="R120" t="e">
         <f t="shared" si="3"/>
@@ -8104,7 +8104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>48</v>
       </c>
@@ -8120,7 +8120,7 @@
       <c r="E121" s="2">
         <v>701</v>
       </c>
-      <c r="F121" s="1">
+      <c r="F121">
         <v>229633</v>
       </c>
       <c r="G121">
@@ -8130,21 +8130,21 @@
         <v>5609.7369338859198</v>
       </c>
       <c r="I121">
-        <v>2.2448151669996101</v>
-      </c>
-      <c r="J121" s="1">
+        <v>2.2481368329990801</v>
+      </c>
+      <c r="J121">
         <v>18293</v>
       </c>
       <c r="K121">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L121">
         <v>4685.8555701611704</v>
       </c>
       <c r="M121">
-        <v>4.4345540998619898E-2</v>
-      </c>
-      <c r="N121" s="1">
+        <v>4.4194249998326898E-2</v>
+      </c>
+      <c r="N121">
         <v>400</v>
       </c>
       <c r="O121">
@@ -8154,7 +8154,7 @@
         <v>4195.5930763914603</v>
       </c>
       <c r="Q121">
-        <v>2.4590465410001299</v>
+        <v>2.5108152920001801</v>
       </c>
       <c r="R121" t="e">
         <f t="shared" si="3"/>
@@ -8166,7 +8166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>48</v>
       </c>
@@ -8182,41 +8182,41 @@
       <c r="E122" s="2">
         <v>701</v>
       </c>
-      <c r="F122" s="1">
+      <c r="F122">
         <v>229633</v>
       </c>
       <c r="G122">
         <v>10</v>
       </c>
       <c r="H122">
-        <v>57.455558031181397</v>
+        <v>356330.19618493301</v>
       </c>
       <c r="I122">
-        <v>2.32647041699965</v>
-      </c>
-      <c r="J122" s="1">
-        <v>1381</v>
+        <v>2.3879585409995299</v>
+      </c>
+      <c r="J122">
+        <v>1440</v>
       </c>
       <c r="K122">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="L122">
-        <v>70.301732663863604</v>
+        <v>148926.77253953399</v>
       </c>
       <c r="M122">
-        <v>4.3157090003659998E-3</v>
-      </c>
-      <c r="N122" s="1">
+        <v>5.5850829994596998E-3</v>
+      </c>
+      <c r="N122">
         <v>400</v>
       </c>
       <c r="O122">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="P122">
-        <v>44.195286503525899</v>
+        <v>161904.06919469</v>
       </c>
       <c r="Q122">
-        <v>1.1796033339996901</v>
+        <v>1.99164983300033</v>
       </c>
       <c r="R122" t="e">
         <f t="shared" si="3"/>
@@ -8225,10 +8225,10 @@
       <c r="S122" s="1"/>
       <c r="T122">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>85</v>
       </c>
@@ -8244,7 +8244,7 @@
       <c r="E123" s="2">
         <v>253</v>
       </c>
-      <c r="F123" s="1">
+      <c r="F123">
         <v>25121</v>
       </c>
       <c r="G123">
@@ -8254,21 +8254,21 @@
         <v>237.49599195056999</v>
       </c>
       <c r="I123">
-        <v>0.17698612499953001</v>
-      </c>
-      <c r="J123" s="1">
+        <v>0.170647667000594</v>
+      </c>
+      <c r="J123">
         <v>9120</v>
       </c>
       <c r="K123">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L123">
         <v>341.68928982818898</v>
       </c>
       <c r="M123">
-        <v>2.04869579993101E-2</v>
-      </c>
-      <c r="N123" s="1">
+        <v>2.0753750000949301E-2</v>
+      </c>
+      <c r="N123">
         <v>400</v>
       </c>
       <c r="O123">
@@ -8278,7 +8278,7 @@
         <v>122.851925663873</v>
       </c>
       <c r="Q123">
-        <v>0.65202587499970799</v>
+        <v>0.65055866600050605</v>
       </c>
       <c r="R123" t="e">
         <f t="shared" si="3"/>
@@ -8290,7 +8290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>85</v>
       </c>
@@ -8306,41 +8306,41 @@
       <c r="E124" s="2">
         <v>253</v>
       </c>
-      <c r="F124" s="1">
+      <c r="F124">
         <v>25121</v>
       </c>
       <c r="G124">
         <v>10</v>
       </c>
       <c r="H124">
-        <v>2.6444225106603598</v>
+        <v>121.354726755931</v>
       </c>
       <c r="I124">
-        <v>0.15549454200117899</v>
-      </c>
-      <c r="J124" s="1">
-        <v>484</v>
+        <v>0.16023991600013601</v>
+      </c>
+      <c r="J124">
+        <v>6965</v>
       </c>
       <c r="K124">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L124">
-        <v>0.51316327665553096</v>
+        <v>219.79655551245401</v>
       </c>
       <c r="M124">
-        <v>1.3788329997623E-3</v>
-      </c>
-      <c r="N124" s="1">
+        <v>1.9466374998955802E-2</v>
+      </c>
+      <c r="N124">
         <v>400</v>
       </c>
       <c r="O124">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="P124">
-        <v>0.51316327665538497</v>
+        <v>114.861941912517</v>
       </c>
       <c r="Q124">
-        <v>0.122825334000026</v>
+        <v>0.55017324999971595</v>
       </c>
       <c r="R124" t="e">
         <f t="shared" si="3"/>
@@ -8352,7 +8352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>85</v>
       </c>
@@ -8368,7 +8368,7 @@
       <c r="E125" s="2">
         <v>265</v>
       </c>
-      <c r="F125" s="1">
+      <c r="F125">
         <v>27983</v>
       </c>
       <c r="G125">
@@ -8378,21 +8378,21 @@
         <v>509.48857112803501</v>
       </c>
       <c r="I125">
-        <v>0.19948004199977701</v>
-      </c>
-      <c r="J125" s="1">
+        <v>0.19512833399858201</v>
+      </c>
+      <c r="J125">
         <v>9470</v>
       </c>
       <c r="K125">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L125">
         <v>573.13358557472395</v>
       </c>
       <c r="M125">
-        <v>2.15393329999642E-2</v>
-      </c>
-      <c r="N125" s="1">
+        <v>2.15293750006821E-2</v>
+      </c>
+      <c r="N125">
         <v>400</v>
       </c>
       <c r="O125">
@@ -8402,7 +8402,7 @@
         <v>379.66581982989601</v>
       </c>
       <c r="Q125">
-        <v>0.75518312500025697</v>
+        <v>0.752228833000117</v>
       </c>
       <c r="R125" t="e">
         <f t="shared" si="3"/>
@@ -8414,7 +8414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>85</v>
       </c>
@@ -8430,41 +8430,41 @@
       <c r="E126" s="2">
         <v>265</v>
       </c>
-      <c r="F126" s="1">
+      <c r="F126">
         <v>27983</v>
       </c>
       <c r="G126">
         <v>10</v>
       </c>
       <c r="H126">
-        <v>4.03804049163492</v>
+        <v>311.89933779787998</v>
       </c>
       <c r="I126">
-        <v>0.179928333000134</v>
-      </c>
-      <c r="J126" s="1">
-        <v>508</v>
+        <v>0.18206545800057899</v>
+      </c>
+      <c r="J126">
+        <v>3463</v>
       </c>
       <c r="K126">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L126">
-        <v>0.55770480110248</v>
+        <v>348.12222852562297</v>
       </c>
       <c r="M126">
-        <v>1.4672079996671001E-3</v>
-      </c>
-      <c r="N126" s="1">
+        <v>1.0191665998718199E-2</v>
+      </c>
+      <c r="N126">
         <v>400</v>
       </c>
       <c r="O126">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="P126">
-        <v>0.55770480110249698</v>
+        <v>258.17177124415502</v>
       </c>
       <c r="Q126">
-        <v>0.12633383299998899</v>
+        <v>0.59488224999950001</v>
       </c>
       <c r="R126" t="e">
         <f t="shared" si="3"/>
@@ -8476,7 +8476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>85</v>
       </c>
@@ -8492,7 +8492,7 @@
       <c r="E127" s="2">
         <v>253</v>
       </c>
-      <c r="F127" s="1">
+      <c r="F127">
         <v>25121</v>
       </c>
       <c r="G127">
@@ -8502,21 +8502,21 @@
         <v>-718.84661716963603</v>
       </c>
       <c r="I127">
-        <v>0.17840450000039701</v>
-      </c>
-      <c r="J127" s="1">
+        <v>0.172151374999884</v>
+      </c>
+      <c r="J127">
         <v>6436</v>
       </c>
       <c r="K127">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L127">
         <v>-651.70088755723998</v>
       </c>
       <c r="M127">
-        <v>1.8090666999341899E-2</v>
-      </c>
-      <c r="N127" s="1">
+        <v>1.4588250000088E-2</v>
+      </c>
+      <c r="N127">
         <v>400</v>
       </c>
       <c r="O127">
@@ -8526,7 +8526,7 @@
         <v>-829.23183815253003</v>
       </c>
       <c r="Q127">
-        <v>0.630409290999978</v>
+        <v>0.63747762499951899</v>
       </c>
       <c r="R127" t="e">
         <f t="shared" si="3"/>
@@ -8538,7 +8538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>85</v>
       </c>
@@ -8554,41 +8554,41 @@
       <c r="E128" s="2">
         <v>253</v>
       </c>
-      <c r="F128" s="1">
+      <c r="F128">
         <v>25121</v>
       </c>
       <c r="G128">
         <v>10</v>
       </c>
       <c r="H128">
-        <v>0.36288176229595598</v>
+        <v>2.4719298978798498</v>
       </c>
       <c r="I128">
-        <v>0.15874199999961999</v>
-      </c>
-      <c r="J128" s="1">
-        <v>484</v>
+        <v>0.16022316599992301</v>
+      </c>
+      <c r="J128">
+        <v>12083</v>
       </c>
       <c r="K128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128">
-        <v>8.7045744624384996E-2</v>
+        <v>30.491295109388201</v>
       </c>
       <c r="M128">
-        <v>1.3988749997224E-3</v>
-      </c>
-      <c r="N128" s="1">
+        <v>3.3515582999825697E-2</v>
+      </c>
+      <c r="N128">
         <v>400</v>
       </c>
       <c r="O128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P128">
-        <v>8.7045744624383706E-2</v>
+        <v>8.3936601939250099</v>
       </c>
       <c r="Q128">
-        <v>0.120075874999656</v>
+        <v>0.25808033300017902</v>
       </c>
       <c r="R128" t="e">
         <f t="shared" si="3"/>
@@ -8600,7 +8600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>85</v>
       </c>
@@ -8616,7 +8616,7 @@
       <c r="E129" s="2">
         <v>253</v>
       </c>
-      <c r="F129" s="1">
+      <c r="F129">
         <v>25121</v>
       </c>
       <c r="G129">
@@ -8626,21 +8626,21 @@
         <v>-554.27495568354902</v>
       </c>
       <c r="I129">
-        <v>0.17979979099982299</v>
-      </c>
-      <c r="J129" s="1">
+        <v>0.174678499999572</v>
+      </c>
+      <c r="J129">
         <v>8079</v>
       </c>
       <c r="K129">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L129">
         <v>-417.95573293753</v>
       </c>
       <c r="M129">
-        <v>1.8318124999495901E-2</v>
-      </c>
-      <c r="N129" s="1">
+        <v>1.8568082999990999E-2</v>
+      </c>
+      <c r="N129">
         <v>400</v>
       </c>
       <c r="O129">
@@ -8650,7 +8650,7 @@
         <v>-649.95310368268895</v>
       </c>
       <c r="Q129">
-        <v>0.60547320800014803</v>
+        <v>0.62740616699920704</v>
       </c>
       <c r="R129" t="e">
         <f t="shared" si="3"/>
@@ -8662,7 +8662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>85</v>
       </c>
@@ -8678,41 +8678,41 @@
       <c r="E130" s="2">
         <v>253</v>
       </c>
-      <c r="F130" s="1">
+      <c r="F130">
         <v>25121</v>
       </c>
       <c r="G130">
         <v>10</v>
       </c>
       <c r="H130">
-        <v>0.48962739096646901</v>
+        <v>4.7405541244372698</v>
       </c>
       <c r="I130">
-        <v>0.15651754099963</v>
-      </c>
-      <c r="J130" s="1">
-        <v>484</v>
+        <v>0.16037424999922201</v>
+      </c>
+      <c r="J130">
+        <v>12846</v>
       </c>
       <c r="K130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130">
-        <v>9.9297726530906405E-2</v>
+        <v>39.678878832725097</v>
       </c>
       <c r="M130">
-        <v>1.3861669995094E-3</v>
-      </c>
-      <c r="N130" s="1">
+        <v>3.5732791999180301E-2</v>
+      </c>
+      <c r="N130">
         <v>400</v>
       </c>
       <c r="O130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P130">
-        <v>9.9297726530855696E-2</v>
+        <v>17.721135138708998</v>
       </c>
       <c r="Q130">
-        <v>0.124272667000241</v>
+        <v>0.25073212499955799</v>
       </c>
       <c r="R130" t="e">
         <f t="shared" si="3"/>
@@ -8724,7 +8724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>85</v>
       </c>
@@ -8740,7 +8740,7 @@
       <c r="E131" s="2">
         <v>253</v>
       </c>
-      <c r="F131" s="1">
+      <c r="F131">
         <v>25121</v>
       </c>
       <c r="G131">
@@ -8750,21 +8750,21 @@
         <v>-426.17317138350597</v>
       </c>
       <c r="I131">
-        <v>0.174524416999702</v>
-      </c>
-      <c r="J131" s="1">
+        <v>0.17450983299931899</v>
+      </c>
+      <c r="J131">
         <v>11039</v>
       </c>
       <c r="K131">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L131">
         <v>-271.06305628852903</v>
       </c>
       <c r="M131">
-        <v>2.45851250001578E-2</v>
-      </c>
-      <c r="N131" s="1">
+        <v>2.51189999999041E-2</v>
+      </c>
+      <c r="N131">
         <v>400</v>
       </c>
       <c r="O131">
@@ -8774,7 +8774,7 @@
         <v>-492.02303819033398</v>
       </c>
       <c r="Q131">
-        <v>0.65139420800005599</v>
+        <v>0.69338333300038302</v>
       </c>
       <c r="R131" t="e">
         <f t="shared" si="3"/>
@@ -8786,7 +8786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>85</v>
       </c>
@@ -8802,41 +8802,41 @@
       <c r="E132" s="2">
         <v>253</v>
       </c>
-      <c r="F132" s="1">
+      <c r="F132">
         <v>25121</v>
       </c>
       <c r="G132">
         <v>10</v>
       </c>
       <c r="H132">
-        <v>0.71463241557530399</v>
+        <v>8.0312346966949395</v>
       </c>
       <c r="I132">
-        <v>0.15579900000011501</v>
-      </c>
-      <c r="J132" s="1">
-        <v>484</v>
+        <v>0.16129962500053799</v>
+      </c>
+      <c r="J132">
+        <v>9593</v>
       </c>
       <c r="K132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132">
-        <v>8.6744994299066E-2</v>
+        <v>30.280959154573001</v>
       </c>
       <c r="M132">
-        <v>1.3917080013925E-3</v>
-      </c>
-      <c r="N132" s="1">
+        <v>2.66458749993034E-2</v>
+      </c>
+      <c r="N132">
         <v>400</v>
       </c>
       <c r="O132">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P132">
-        <v>8.67449942990592E-2</v>
+        <v>21.600494620328099</v>
       </c>
       <c r="Q132">
-        <v>0.120990667000114</v>
+        <v>0.31139179199999401</v>
       </c>
       <c r="R132" t="e">
         <f t="shared" ref="R132:R142" si="5">IF(O132=G132,(P132-H132)/H132,NA())</f>
@@ -8848,7 +8848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>85</v>
       </c>
@@ -8864,7 +8864,7 @@
       <c r="E133" s="2">
         <v>265</v>
       </c>
-      <c r="F133" s="1">
+      <c r="F133">
         <v>27983</v>
       </c>
       <c r="G133">
@@ -8874,21 +8874,21 @@
         <v>-411.60512030099397</v>
       </c>
       <c r="I133">
-        <v>0.16562833299940299</v>
-      </c>
-      <c r="J133" s="1">
+        <v>0.165206667001257</v>
+      </c>
+      <c r="J133">
         <v>8620</v>
       </c>
       <c r="K133">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L133">
         <v>-345.298861218497</v>
       </c>
       <c r="M133">
-        <v>1.9361624999874E-2</v>
-      </c>
-      <c r="N133" s="1">
+        <v>1.9437958999333201E-2</v>
+      </c>
+      <c r="N133">
         <v>400</v>
       </c>
       <c r="O133">
@@ -8898,7 +8898,7 @@
         <v>-528.201260866349</v>
       </c>
       <c r="Q133">
-        <v>0.72859187499989198</v>
+        <v>0.72986416599996995</v>
       </c>
       <c r="R133" t="e">
         <f t="shared" si="5"/>
@@ -8910,7 +8910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>85</v>
       </c>
@@ -8926,41 +8926,41 @@
       <c r="E134" s="2">
         <v>265</v>
       </c>
-      <c r="F134" s="1">
+      <c r="F134">
         <v>27983</v>
       </c>
       <c r="G134">
         <v>10</v>
       </c>
       <c r="H134">
-        <v>0.67534196107888</v>
+        <v>9.5433988660414997</v>
       </c>
       <c r="I134">
-        <v>0.17467441600092501</v>
-      </c>
-      <c r="J134" s="1">
-        <v>508</v>
+        <v>0.180053999998563</v>
+      </c>
+      <c r="J134">
+        <v>4007</v>
       </c>
       <c r="K134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134">
-        <v>7.66346057269119E-2</v>
+        <v>25.334869153359701</v>
       </c>
       <c r="M134">
-        <v>1.4427080004679E-3</v>
-      </c>
-      <c r="N134" s="1">
+        <v>1.12719589997141E-2</v>
+      </c>
+      <c r="N134">
         <v>400</v>
       </c>
       <c r="O134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P134">
-        <v>7.6634605726909402E-2</v>
+        <v>18.654892443572599</v>
       </c>
       <c r="Q134">
-        <v>0.12785075000010601</v>
+        <v>0.26350783400084699</v>
       </c>
       <c r="R134" t="e">
         <f t="shared" si="5"/>
@@ -8972,7 +8972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>85</v>
       </c>
@@ -8988,7 +8988,7 @@
       <c r="E135" s="2">
         <v>253</v>
       </c>
-      <c r="F135" s="1">
+      <c r="F135">
         <v>25121</v>
       </c>
       <c r="G135">
@@ -8998,21 +8998,21 @@
         <v>94.308233664354603</v>
       </c>
       <c r="I135">
-        <v>0.148520208000263</v>
-      </c>
-      <c r="J135" s="1">
+        <v>0.14541579199976601</v>
+      </c>
+      <c r="J135">
         <v>8882</v>
       </c>
       <c r="K135">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L135">
         <v>213.33504255518099</v>
       </c>
       <c r="M135">
-        <v>2.00979580004059E-2</v>
-      </c>
-      <c r="N135" s="1">
+        <v>2.0515917000011499E-2</v>
+      </c>
+      <c r="N135">
         <v>400</v>
       </c>
       <c r="O135">
@@ -9022,7 +9022,7 @@
         <v>27.336195059970301</v>
       </c>
       <c r="Q135">
-        <v>0.70501200000035102</v>
+        <v>0.72280020800098999</v>
       </c>
       <c r="R135" t="e">
         <f t="shared" si="5"/>
@@ -9034,7 +9034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>85</v>
       </c>
@@ -9050,41 +9050,41 @@
       <c r="E136" s="2">
         <v>253</v>
       </c>
-      <c r="F136" s="1">
+      <c r="F136">
         <v>25121</v>
       </c>
       <c r="G136">
         <v>10</v>
       </c>
       <c r="H136">
-        <v>1.9209836508743301</v>
+        <v>62.326287284932498</v>
       </c>
       <c r="I136">
-        <v>0.181083915998897</v>
-      </c>
-      <c r="J136" s="1">
-        <v>484</v>
+        <v>0.18658862499978501</v>
+      </c>
+      <c r="J136">
+        <v>7479</v>
       </c>
       <c r="K136">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L136">
-        <v>0.29300027570884102</v>
+        <v>112.787264074261</v>
       </c>
       <c r="M136">
-        <v>1.3975420006318E-3</v>
-      </c>
-      <c r="N136" s="1">
+        <v>2.0989165999708299E-2</v>
+      </c>
+      <c r="N136">
         <v>400</v>
       </c>
       <c r="O136">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P136">
-        <v>0.29300027570883003</v>
+        <v>83.339749435841</v>
       </c>
       <c r="Q136">
-        <v>0.12448458399967401</v>
+        <v>0.41209662500114003</v>
       </c>
       <c r="R136" t="e">
         <f t="shared" si="5"/>
@@ -9096,7 +9096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>85</v>
       </c>
@@ -9112,7 +9112,7 @@
       <c r="E137" s="2">
         <v>253</v>
       </c>
-      <c r="F137" s="1">
+      <c r="F137">
         <v>25121</v>
       </c>
       <c r="G137">
@@ -9122,21 +9122,21 @@
         <v>121.345629111354</v>
       </c>
       <c r="I137">
-        <v>0.14911933299845201</v>
-      </c>
-      <c r="J137" s="1">
+        <v>0.148017874998913</v>
+      </c>
+      <c r="J137">
         <v>8684</v>
       </c>
       <c r="K137">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L137">
         <v>238.995337271127</v>
       </c>
       <c r="M137">
-        <v>1.9321042000228699E-2</v>
-      </c>
-      <c r="N137" s="1">
+        <v>1.9552291998479601E-2</v>
+      </c>
+      <c r="N137">
         <v>400</v>
       </c>
       <c r="O137">
@@ -9146,7 +9146,7 @@
         <v>67.075420467215096</v>
       </c>
       <c r="Q137">
-        <v>0.63089312499960204</v>
+        <v>0.634146458000032</v>
       </c>
       <c r="R137" t="e">
         <f t="shared" si="5"/>
@@ -9158,7 +9158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>85</v>
       </c>
@@ -9174,45 +9174,45 @@
       <c r="E138" s="2">
         <v>253</v>
       </c>
-      <c r="F138" s="1">
+      <c r="F138">
         <v>25121</v>
       </c>
       <c r="G138">
         <v>10</v>
       </c>
       <c r="H138">
-        <v>1.9739321314465901</v>
+        <v>71.682617412609503</v>
       </c>
       <c r="I138">
-        <v>0.18409754200001699</v>
-      </c>
-      <c r="J138" s="1">
-        <v>484</v>
+        <v>0.18864387500070701</v>
+      </c>
+      <c r="J138">
+        <v>6122</v>
       </c>
       <c r="K138">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L138">
-        <v>0.39529448143753099</v>
+        <v>144.835718088768</v>
       </c>
       <c r="M138">
-        <v>1.4193329989211001E-3</v>
-      </c>
-      <c r="N138" s="1">
+        <v>1.70720419991994E-2</v>
+      </c>
+      <c r="N138">
         <v>400</v>
       </c>
       <c r="O138">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P138">
-        <v>0.395294481437517</v>
+        <v>81.342953369228098</v>
       </c>
       <c r="Q138">
-        <v>0.12427366699967</v>
-      </c>
-      <c r="R138" t="e">
+        <v>0.490335667000181</v>
+      </c>
+      <c r="R138">
         <f t="shared" si="5"/>
-        <v>#N/A</v>
+        <v>0.13476539090381026</v>
       </c>
       <c r="S138" s="1"/>
       <c r="T138">
@@ -9220,7 +9220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>85</v>
       </c>
@@ -9236,7 +9236,7 @@
       <c r="E139" s="2">
         <v>253</v>
       </c>
-      <c r="F139" s="1">
+      <c r="F139">
         <v>25121</v>
       </c>
       <c r="G139">
@@ -9246,21 +9246,21 @@
         <v>-487.78510779767998</v>
       </c>
       <c r="I139">
-        <v>0.14993870800026299</v>
-      </c>
-      <c r="J139" s="1">
+        <v>0.14737466599945001</v>
+      </c>
+      <c r="J139">
         <v>10260</v>
       </c>
       <c r="K139">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L139">
         <v>-390.94840042505098</v>
       </c>
       <c r="M139">
-        <v>2.3314500000196799E-2</v>
-      </c>
-      <c r="N139" s="1">
+        <v>2.3884457999884E-2</v>
+      </c>
+      <c r="N139">
         <v>400</v>
       </c>
       <c r="O139">
@@ -9270,7 +9270,7 @@
         <v>-677.50276723169895</v>
       </c>
       <c r="Q139">
-        <v>0.70432870800004799</v>
+        <v>0.70973420800146403</v>
       </c>
       <c r="R139" t="e">
         <f t="shared" si="5"/>
@@ -9282,7 +9282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>85</v>
       </c>
@@ -9298,41 +9298,41 @@
       <c r="E140" s="2">
         <v>253</v>
       </c>
-      <c r="F140" s="1">
+      <c r="F140">
         <v>25121</v>
       </c>
       <c r="G140">
         <v>10</v>
       </c>
       <c r="H140">
-        <v>0.589659790018496</v>
+        <v>6.5739036160314201</v>
       </c>
       <c r="I140">
-        <v>0.18454125000061999</v>
-      </c>
-      <c r="J140" s="1">
-        <v>484</v>
+        <v>0.194913082999846</v>
+      </c>
+      <c r="J140">
+        <v>3327</v>
       </c>
       <c r="K140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L140">
-        <v>8.0408618615301894E-2</v>
+        <v>26.018723394823201</v>
       </c>
       <c r="M140">
-        <v>1.4290830004028E-3</v>
-      </c>
-      <c r="N140" s="1">
+        <v>9.6661669995227999E-3</v>
+      </c>
+      <c r="N140">
         <v>400</v>
       </c>
       <c r="O140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P140">
-        <v>8.0408618615302394E-2</v>
+        <v>13.6800740177236</v>
       </c>
       <c r="Q140">
-        <v>0.125591583000186</v>
+        <v>0.249736582998593</v>
       </c>
       <c r="R140" t="e">
         <f t="shared" si="5"/>
@@ -9344,7 +9344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>85</v>
       </c>
@@ -9360,7 +9360,7 @@
       <c r="E141" s="2">
         <v>265</v>
       </c>
-      <c r="F141" s="1">
+      <c r="F141">
         <v>27983</v>
       </c>
       <c r="G141">
@@ -9370,21 +9370,21 @@
         <v>-313.549685215029</v>
       </c>
       <c r="I141">
-        <v>0.165621416999783</v>
-      </c>
-      <c r="J141" s="1">
+        <v>0.166779125000175</v>
+      </c>
+      <c r="J141">
         <v>11746</v>
       </c>
       <c r="K141">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L141">
         <v>-184.12480472781601</v>
       </c>
       <c r="M141">
-        <v>2.6730167001005601E-2</v>
-      </c>
-      <c r="N141" s="1">
+        <v>2.7209457999560899E-2</v>
+      </c>
+      <c r="N141">
         <v>400</v>
       </c>
       <c r="O141">
@@ -9394,7 +9394,7 @@
         <v>-411.42965717254202</v>
       </c>
       <c r="Q141">
-        <v>0.76504129200020499</v>
+        <v>0.766839583000546</v>
       </c>
       <c r="R141" t="e">
         <f t="shared" si="5"/>
@@ -9406,7 +9406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>85</v>
       </c>
@@ -9422,41 +9422,41 @@
       <c r="E142" s="2">
         <v>265</v>
       </c>
-      <c r="F142" s="1">
+      <c r="F142">
         <v>27983</v>
       </c>
       <c r="G142">
         <v>10</v>
       </c>
       <c r="H142">
-        <v>0.75070763448813305</v>
+        <v>19.534430142328102</v>
       </c>
       <c r="I142">
-        <v>0.20352366699989899</v>
-      </c>
-      <c r="J142" s="1">
-        <v>508</v>
+        <v>0.210806999999476</v>
+      </c>
+      <c r="J142">
+        <v>13032</v>
       </c>
       <c r="K142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142">
-        <v>0.131552070936343</v>
+        <v>74.6559092974923</v>
       </c>
       <c r="M142">
-        <v>1.51266700049745E-3</v>
-      </c>
-      <c r="N142" s="1">
+        <v>3.6159708999548401E-2</v>
+      </c>
+      <c r="N142">
         <v>400</v>
       </c>
       <c r="O142">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P142">
-        <v>0.13155207093633101</v>
+        <v>29.327707967740501</v>
       </c>
       <c r="Q142">
-        <v>0.12702475000014599</v>
+        <v>0.39077204200111698</v>
       </c>
       <c r="R142" t="e">
         <f t="shared" si="5"/>
